--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -13242,7 +13242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13302,57 +13302,57 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="A4" s="11" t="inlineStr"/>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>权威源从xlsx转仓库内YAML/CSV（可行级diff）；词表归一到单一源</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>已完成（field-source.yaml）</t>
-        </is>
-      </c>
+          <t>── 2026-07-07 导师评审引出的待对齐──</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>v1→v2 逐字段迁移映射（68字段去向，含quality_label/failure_modes/color_change落点）</t>
+          <t>【问俊杰·导师K75点名】§7『观察到的现象』粒度：现7项客观多选 vs 只记『生长/不生长』？可带折中案：一级『生长/未生长』必选＋二级现象细分可选（保失败溯源卖点）</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>不适用（批8整库重建，不迁移v1数据）</t>
+          <t>待对齐(问俊杰)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr"/>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>── 2026-07-07 导师评审引出的待对齐──</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr"/>
+          <t>【问俊杰】SEM覆盖率：组里习惯的叫法/量化方式/单位？（导师问『SEM占比是什么』，已先改名『SEM覆盖率(视场内材料面积占比,%)』）</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>待对齐(问俊杰)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>【问俊杰·导师K75点名】§7『观察到的现象』粒度：现7项客观多选 vs 只记『生长/不生长』？可带折中案：一级『生长/未生长』必选＋二级现象细分可选（保失败溯源卖点）</t>
+          <t>【问俊杰】堆垛类型实际可判到什么粒度（2H/3R？AA/AB/ABC？扭转角？）→ 决定自由文本还是下拉词表</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -13364,12 +13364,12 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>【问俊杰】SEM覆盖率：组里习惯的叫法/量化方式/单位？（导师问『SEM占比是什么』，已先改名『SEM覆盖率(视场内材料面积占比,%)』）</t>
+          <t>【问俊杰】前驱体『外观描述』词表：组里常用前驱体的形态 + 潮解/变质后的典型外观有哪些</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -13381,170 +13381,85 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>【问俊杰】堆垛类型实际可判到什么粒度（2H/3R？AA/AB/ABC？扭转角？）→ 决定自由文本还是下拉词表</t>
+          <t>【回导师】①SEM占比=SEM视场内材料面积覆盖占比（已改名并给定义）；②必填/选填已加图例行+字体强化，表单UI将用红星标必填</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>待对齐(问俊杰)</t>
+          <t>待回复</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>【问俊杰】前驱体『外观描述』词表：组里常用前驱体的形态 + 潮解/变质后的典型外观有哪些</t>
+          <t>【问俊杰】低压CVD的漏率是否逐炉记录，以及应归入装置校验还是实验过程</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>待对齐(问俊杰)</t>
+          <t>待对齐(本轮不记录漏率)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>【回导师】①SEM占比=SEM视场内材料面积覆盖占比（已改名并给定义）；②必填/选填已加图例行+字体强化，表单UI将用红星标必填</t>
+          <t>【问俊杰】多气体比例的组内标准名称；系统当前由同时间段各气体流量派生</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>待回复</t>
+          <t>待对齐(不另存重复比例)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>表单UI：必填红星/选填弱化等明显标识（导师B93提醒）</t>
+          <t>【问俊杰】掺杂体系“基体/主体/本征材料”的最终角色术语与常见括号化学式示例</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>待对齐(结构已支持)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>【已确认】实验前气体置换统一称“气氛置换”（2026-09-04）</t>
+          <t>【问俊杰】压片等前驱体处理方式的最小参数模板</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>待对齐(不阻塞结构实现)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】低压CVD的漏率是否逐炉记录，以及应归入装置校验还是实验过程</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(本轮不记录漏率)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】多气体比例的组内标准名称；系统当前由同时间段各气体流量派生</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(不另存重复比例)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】掺杂体系“基体/主体/本征材料”的最终角色术语与常见括号化学式示例</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(结构已支持)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】压片等前驱体处理方式的最小参数模板</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
           <t>待对齐(当前使用具名参数—值—单位)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>已定/已改：一等实体字段表 · 记录单元=炉次+样品 · 掺杂→结构类型+components · 观察现象词表 · 降温参数 · R0条件化(相态判别) · AP/LP校验 · v3.4导师评审回改</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>见『v2→v3变更说明』</t>
         </is>
       </c>
     </row>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -10,7 +10,6 @@
     <sheet name="字段草案" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="一等实体字段表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="v2→v3变更说明" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待明确清单" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11182,7 +11181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12134,7 +12133,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>表头下加必填级别图例行；必填/条件必填字体加粗着色（导师提醒B93）；表单UI红星标识记入待明确清单</t>
+          <t>表头下加必填级别图例行；必填/条件必填字体加粗着色（导师提醒B93）</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -12144,36 +12143,36 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>未改</t>
-        </is>
-      </c>
+      <c r="A47" s="11" t="inlineStr"/>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>§7</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>『观察到的现象』词表粒度（7项多选 vs 只记生长/不生长）——导师K75点名与俊杰确认后再定，见待明确清单#5</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>待俊杰对齐</t>
-        </is>
-      </c>
+          <t>── review→v3 回退存档（每条给去向）──</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr"/>
+      <c r="D47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr"/>
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>存档</t>
+        </is>
+      </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>── review→v3 回退存档（每条给去向）──</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr"/>
-      <c r="D48" s="11" t="inlineStr"/>
+          <t>湿度</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>回退备案</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -12183,12 +12182,12 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>湿度</t>
+          <t>装置加热区长/泵型号/MFC配置/PID</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
+          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -12205,12 +12204,12 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>装置加热区长/泵型号/MFC配置/PID</t>
+          <t>炉管履历</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -12227,12 +12226,12 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>炉管履历</t>
+          <t>时序四元组</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -12244,44 +12243,44 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>存档</t>
+          <t>v3.5a</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>时序四元组</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
+          <t>结构类型由下拉多选纠正为单选判别器；选择值驱动填写提示及组成明细显隐/条件必填</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>回退备案</t>
+          <t>用户走查修复</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>v3.5a</t>
+          <t>v3.6</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>全表/实体</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>结构类型由下拉多选纠正为单选判别器；选择值驱动填写提示及组成明细显隐/条件必填</t>
+          <t>科学契约加固：结构类型与组成明细纳入R0；补衬底批次引用、具名几何、其他气体名称、sccm参考状态及字段级数值边界</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复</t>
+          <t>全库审查修复</t>
         </is>
       </c>
     </row>
@@ -12293,12 +12292,12 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>全表/实体</t>
+          <t>§6–§7</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>科学契约加固：结构类型与组成明细纳入R0；补衬底批次引用、具名几何、其他气体名称、sccm参考状态及字段级数值边界</t>
+          <t>过程事件改为带UTC offset的绝对日期时间；实测层数、覆盖率、畴尺寸、成核密度拆为独立量，关键谱学指标改为带单位的结构化数组</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -12310,22 +12309,22 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>v3.6</t>
+          <t>v3.7</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>§6–§7</t>
+          <t>§1–§4</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>过程事件改为带UTC offset的绝对日期时间；实测层数、覆盖率、畴尺寸、成核密度拆为独立量，关键谱学指标改为带单位的结构化数组</t>
+          <t>按2026-07-24导师走查：温湿度与预检、目标形态升必填；删除粒子占位；批次引用升必填；前驱体与衬底处理改具名有序数组；衬底晶向、粗糙度、尺寸与倾角结构化</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>全库审查修复</t>
+          <t>导师走查整改</t>
         </is>
       </c>
     </row>
@@ -12337,12 +12336,12 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>§1–§4</t>
+          <t>§5–§6</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>按2026-07-24导师走查：温湿度与预检、目标形态升必填；删除粒子占位；批次引用升必填；前驱体与衬底处理改具名有序数组；衬底晶向、粗糙度、尺寸与倾角结构化</t>
+          <t>11阶段收敛为预处理、反应条件、具名其他记录；温度程序、实测文件、多气体时序、时长、降温、实际外场与事件附件全部改为可校验结构</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -12359,12 +12358,12 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>§5–§6</t>
+          <t>实体</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>11阶段收敛为预处理、反应条件、具名其他记录；温度程序、实测文件、多气体时序、时长、降温、实际外场与事件附件全部改为可校验结构</t>
+          <t>Setup删除sccm参考值、加热区长度、泵、MFC和PID，坐标系固定，新增温度传感器；炉管材质与形状拆入具名对象；MaterialLot新增瓶身或包装标签附件</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -12376,22 +12375,22 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>v3.7</t>
+          <t>v3.8</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>实体</t>
+          <t>§1–§5</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Setup删除sccm参考值、加热区长度、泵、MFC和PID，坐标系固定，新增温度传感器；炉管材质与形状拆入具名对象；MaterialLot新增瓶身或包装标签附件</t>
+          <t>用户走查修复：炉管和各舟履历改为每炉手填；炉管尺寸按圆/方/矩形条件展开；前驱体源温改为可选位置温度及依据；外场按等离子体/光/电展开明确参数</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>导师走查整改</t>
+          <t>用户走查修复</t>
         </is>
       </c>
     </row>
@@ -12403,12 +12402,12 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>§1–§5</t>
+          <t>§4/实体</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复：炉管和各舟履历改为每炉手填；炉管尺寸按圆/方/矩形条件展开；前驱体源温改为可选位置温度及依据；外场按等离子体/光/电展开明确参数</t>
+          <t>衬底稳定规格归MaterialLot：晶向抛光、偏切角与方向、氧化层及标称粗糙度由批次冻结带出；本片尺寸、放置、预处理和位置留在炉次；气瓶等级改为供应商原始标签选填</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -12425,12 +12424,12 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>§4/实体</t>
+          <t>术语/表征</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>衬底稳定规格归MaterialLot：晶向抛光、偏切角与方向、氧化层及标称粗糙度由批次冻结带出；本片尺寸、放置、预处理和位置留在炉次；气瓶等级改为供应商原始标签选填</t>
+          <t>装置与实际外场统一显示“等离子体”；体相空间群改用内置230项检索；“表征方法”与仪器引用分开，固定配置只记录稳定硬件能力</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -12442,127 +12441,127 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>v3.8</t>
+          <t>v3.9</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>术语/表征</t>
+          <t>§1/§4/实体</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>装置与实际外场统一显示“等离子体”；体相空间群改用内置230项检索；“表征方法”与仪器引用分开，固定配置只记录稳定硬件能力</t>
+          <t>按会议逐字稿删除悬浮粒子浓度；粗糙度允许明确记录供应商未提供；旧批次缺稳定字段时禁止在实验回填；区分来料尺寸与本次实际切片尺寸</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>v3.9</t>
+          <t>v3.10</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>§1/§4/实体</t>
+          <t>§3/§4/实体</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>按会议逐字稿删除悬浮粒子浓度；粗糙度允许明确记录供应商未提供；旧批次缺稳定字段时禁止在实验回填；区分来料尺寸与本次实际切片尺寸</t>
+          <t>补齐温区距离参照、条件不适用后端约束与旧等离子别名；粒径/形态按物料类别展开；晶向抛光和偏切以有规格、未提供、不适用三态记录，禁止用伪值或0代替未知</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-25终审收口</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>v3.10</t>
+          <t>v3.11</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>§3/§4/实体</t>
+          <t>§6/实体</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>补齐温区距离参照、条件不适用后端约束与旧等离子别名；粒径/形态按物料类别展开；晶向抛光和偏切以有规格、未提供、不适用三态记录，禁止用伪值或0代替未知</t>
+          <t>事件具体说明始终可选填写、终止原因=其他时升级为必填；仪器字段改称“适用表征方法”；补明热电偶距离与前驱体温区、炉管截面与尺寸的联动必填规则</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25终审收口</t>
+          <t>2026-07-25逐字稿与语义终审</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>v3.11</t>
+          <t>v3.12</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>§6/实体</t>
+          <t>§1–§5/实体</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明始终可选填写、终止原因=其他时升级为必填；仪器字段改称“适用表征方法”；补明热电偶距离与前驱体温区、炉管截面与尺寸的联动必填规则</t>
+          <t>制备终版整改：新记录固定CVD顶层方法；目标产物按掺杂、合金、材料层和区域填写；Setup逐温区只填传感器类型与温度测量误差；前驱体角色与样片标记必填；压力类别和值成对；反应删除伪循环派生</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25逐字稿与语义终审</t>
+          <t>2026-07-27终版整改</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>v3.12</t>
+          <t>v3.13</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>§1–§5/实体</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>制备终版整改：新记录固定CVD顶层方法；目标产物按掺杂、合金、材料层和区域填写；Setup逐温区只填传感器类型与温度测量误差；前驱体角色与样片标记必填；压力类别和值成对；反应删除伪循环派生</t>
+          <t>目标产物复核：化学式示例按结构类型变化；删除“普通数字”用户文案；掺杂区只显示掺杂元素；空间群按化学式给出经核对的常见体相候选并保留230项搜索；异质结构逐层或逐区域填写空间群</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>2026-07-27终版整改</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>v3.13</t>
+          <t>v3.15</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>实体/设备</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>目标产物复核：化学式示例按结构类型变化；删除“普通数字”用户文案；掺杂区只显示掺杂元素；空间群按化学式给出经核对的常见体相候选并保留230项搜索；异质结构逐层或逐区域填写空间群</t>
+          <t>温度传感器由热电偶分型号改为按测温原理选择类别：热电偶、热电阻（RTD）、红外测温仪、光纤温度传感器、热敏电阻、其他</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -12574,7 +12573,7 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>v3.15</t>
+          <t>v3.16</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -12584,7 +12583,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>温度传感器由热电偶分型号改为按测温原理选择类别：热电偶、热电阻（RTD）、红外测温仪、光纤温度传感器、热敏电阻、其他</t>
+          <t>Setup拆分制造商或品牌与型号，增加装置来源；实验室装置编号保持唯一但允许管理员通过新版本纠错；温区标称测温精度改为选填</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -12596,7 +12595,7 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>v3.16</t>
+          <t>v3.17</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -12606,7 +12605,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Setup拆分制造商或品牌与型号，增加装置来源；实验室装置编号保持唯一但允许管理员通过新版本纠错；温区标称测温精度改为选填</t>
+          <t>装置来源改为必填；商业设备显示制造商与型号，实验室自制显示设计或建造单位与内部型号，改造设备显示原设备制造商、原设备型号与改造内容；公共技术字段不变</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -12618,105 +12617,105 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>v3.17</t>
+          <t>v3.18</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>实体/设备</t>
+          <t>§3/实体</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>装置来源改为必填；商业设备显示制造商与型号，实验室自制显示设计或建造单位与内部型号，改造设备显示原设备制造商、原设备型号与改造内容；公共技术字段不变</t>
+          <t>前驱体先选本次使用形态再筛选批次；删除炉次中重复的名称化学式和CAS；用途、使用量、使用前状态、处理步骤按实际语义收敛；非气态按舟、坩埚、衬底表面或其他容器展开容器尺寸、履历与炉内位置</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
+          <t>2026-07-28前驱体首版复核</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>v3.18</t>
+          <t>v4.0-rc.1</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>§3/实体</t>
+          <t>科学对象/实体/结果</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>前驱体先选本次使用形态再筛选批次；删除炉次中重复的名称化学式和CAS；用途、使用量、使用前状态、处理步骤按实际语义收敛；非气态按舟、坩埚、衬底表面或其他容器展开容器尺寸、履历与炉内位置</t>
+          <t>引入正交TargetSpec、物理SourceLoad、统一ProcessTimeline、不可变RunRevision、样品转换图及MeasurementRun→AnalysisRun→PropertyValue/MaterialAssertion溯源链；物料、装置部件和仪器能力补齐归一化字段；PVD不进入发布契约</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28前驱体首版复核</t>
+          <t>2026-07-28深度审查整改</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>v4.0-rc.1</t>
+          <t>v4.0-alpha.2</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>科学对象/实体/结果</t>
+          <t>科学完整性复核</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>引入正交TargetSpec、物理SourceLoad、统一ProcessTimeline、不可变RunRevision、样品转换图及MeasurementRun→AnalysisRun→PropertyValue/MaterialAssertion溯源链；物料、装置部件和仪器能力补齐归一化字段；PVD不进入发布契约</t>
+          <t>关闭旧结果写入与手工派生入口；收紧审阅和转化权限；修正跨炉次转化溯源、过程单位归一化、不可变修订导出及数据集查询语义；冻结装料容器、测量时校准和样品—修订关联快照；状态降为内部验证</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查整改</t>
+          <t>2026-07-29二次复核整改</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.2</t>
+          <t>v4.0-alpha.3</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>科学完整性复核</t>
+          <t>§4 衬底</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>关闭旧结果写入与手工派生入口；收紧审阅和转化权限；修正跨炉次转化溯源、过程单位归一化、不可变修订导出及数据集查询语义；冻结装料容器、测量时校准和样品—修订关联快照；状态降为内部验证</t>
+          <t>产品简化界面增加本片轴向位置与备注；轴向位置为普通用户提交前必填，不暴露三维坐标</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29二次复核整改</t>
+          <t>2026-07-30产品简化</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.3</t>
+          <t>v4.0-alpha.4</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>§4 衬底</t>
+          <t>§7 表征</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>产品简化界面增加本片轴向位置与备注；轴向位置为普通用户提交前必填，不暴露三维坐标</t>
+          <t>表征方法拆分最小必填与更多测量参数，固定各方法常用结果项，并增加“其他”方法说明；科学对象仍由后端统一落库</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -12728,29 +12727,29 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.4</t>
+          <t>v4.0-alpha.5</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>§7 表征</t>
+          <t>实体/物料批次</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>表征方法拆分最小必填与更多测量参数，固定各方法常用结果项，并增加“其他”方法说明；科学对象仍由后端统一落库</t>
+          <t>CAS号与数值纯度改为有来源才选填；删除同义名、标识符、商业规格JSON、纯度基准/来源及D50四字段；供应商规格或等级按标签原文照录</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>2026-07-30产品简化</t>
+          <t>2026-08-02供应商资料复核与减负</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.5</t>
+          <t>v4.0-alpha.6</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -12760,19 +12759,19 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>CAS号与数值纯度改为有来源才选填；删除同义名、标识符、商业规格JSON、纯度基准/来源及D50四字段；供应商规格或等级按标签原文照录</t>
+          <t>物料表单文案正式化：常规字段说明改为简短占位示例，仅为纯度及衬底规格等易误录字段保留必要说明；统一字段名称、中文标点和中英文术语</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02供应商资料复核与减负</t>
+          <t>2026-08-02用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.6</t>
+          <t>v4.0-alpha.7</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -12782,19 +12781,19 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>物料表单文案正式化：常规字段说明改为简短占位示例，仅为纯度及衬底规格等易误录字段保留必要说明；统一字段名称、中文标点和中英文术语</t>
+          <t>化学式复用目标产物输入控件并提示元素与语法；货号与批号直接对应包装上的 Cat./Product No. 和 Lot/Batch No.，说明两者的产品与实物批次分工</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02用户界面复核</t>
+          <t>2026-08-06用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.7</t>
+          <t>v4.0-alpha.8</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -12804,7 +12803,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>化学式复用目标产物输入控件并提示元素与语法；货号与批号直接对应包装上的 Cat./Product No. 和 Lot/Batch No.，说明两者的产品与实物批次分工</t>
+          <t>删除化学式格式说明，只保留示例与即时元素/语法反馈</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
@@ -12816,7 +12815,7 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.8</t>
+          <t>v4.0-alpha.9</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -12826,7 +12825,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>删除化学式格式说明，只保留示例与即时元素/语法反馈</t>
+          <t>供应商“其他”改为明确的新增供应商与名称输入；供应商规格或等级改为产品等级（标签原文），说明资料未标注时留空</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -12838,17 +12837,17 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.9</t>
+          <t>v4.0-alpha.12</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>实体/物料批次</t>
+          <t>§5 生长条件</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>供应商“其他”改为明确的新增供应商与名称输入；供应商规格或等级改为产品等级（标签原文），说明资料未标注时留空</t>
+          <t>统一实验时间零点与有效生长窗口；补齐气体批次、流量来源、绝对压力、受控降温速率、实际外场参数和多条异常事件，并自动覆盖生长后的实验过程</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
@@ -12860,7 +12859,7 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.12</t>
+          <t>v4.0-alpha.13</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -12870,19 +12869,19 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>统一实验时间零点与有效生长窗口；补齐气体批次、流量来源、绝对压力、受控降温速率、实际外场参数和多条异常事件，并自动覆盖生长后的实验过程</t>
+          <t>将容易误解为管理制度的“压力制度/压力体系”统一改为“反应压力条件”，数据字段与校验规则不变</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06用户界面复核</t>
+          <t>2026-08-07用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.13</t>
+          <t>v4.0-alpha.14</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
@@ -12892,7 +12891,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>将容易误解为管理制度的“压力制度/压力体系”统一改为“反应压力条件”，数据字段与校验规则不变</t>
+          <t>改为按实际操作和持续时间录入，系统自动生成系统准备、升温与预处理、反应、反应后处理和降温时间轴；气体优先选择使用阶段，仅自定义时填写起止时间</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -12904,7 +12903,7 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.14</t>
+          <t>v4.0-alpha.15</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
@@ -12914,51 +12913,51 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>改为按实际操作和持续时间录入，系统自动生成系统准备、升温与预处理、反应、反应后处理和降温时间轴；气体优先选择使用阶段，仅自定义时填写起止时间</t>
+          <t>删除缺乏统一文献定义且无法直接观测的反应计时起点、反应开始前用时、反应时长及重复的反应后处理；实际过程由温度步骤、气体时段、系统准备、压力与降温记录</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户界面复核</t>
+          <t>2026-08-07用户界面复核与原始论文核对</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.15</t>
+          <t>v4.0-alpha.16</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>§5 生长条件</t>
+          <t>§3 前驱体装载</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>删除缺乏统一文献定义且无法直接观测的反应计时起点、反应开始前用时、反应时长及重复的反应后处理；实际过程由温度步骤、气体时段、系统准备、压力与降温记录</t>
+          <t>删除偏TMDC的必填单选作用，改为选填多选工艺作用；一次旋涂支持多段转速；衬底表面装载关联稳定衬底片；旋涂物料可成对记录溶液浓度与受控单位</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户界面复核与原始论文核对</t>
+          <t>2026-08-12师兄真实试填反馈</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.16</t>
+          <t>v4.0-alpha.17</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>§3 前驱体装载</t>
+          <t>§5 生长条件</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>删除偏TMDC的必填单选作用，改为选填多选工艺作用；一次旋涂支持多段转速；衬底表面装载关联稳定衬底片；旋涂物料可成对记录溶液浓度与受控单位</t>
+          <t>气体词表增加二氧化碳，启动混合气与置换气源契约收口</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -12970,496 +12969,242 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.17</t>
+          <t>v4.0-alpha.18</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>§5 生长条件</t>
+          <t>§1–§6科学修订契约·MaterialLot气瓶</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>气体词表增加二氧化碳，启动混合气与置换气源契约收口</t>
+          <t>气瓶版本结构化登记纯气或预混组成；置换引用实际气瓶版本；基本信息、目标材料、前驱体、过程事件与生长条件的发布字段改用当前不可变修订payload真实key和schema_path，旧扁平字段仅历史兼容</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-12师兄真实试填反馈</t>
+          <t>2026-08-13全链路契约复核</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.18</t>
+          <t>v4.0-alpha.19</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>§1–§6科学修订契约·MaterialLot气瓶</t>
+          <t>表征科学属性</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>气瓶版本结构化登记纯气或预混组成；置换引用实际气瓶版本；基本信息、目标材料、前驱体、过程事件与生长条件的发布字段改用当前不可变修订payload真实key和schema_path，旧扁平字段仅历史兼容</t>
+          <t>PropertyValue 补齐数值/文本表示类型与物理范围，并统一后端和前端的单一源校验</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13全链路契约复核</t>
+          <t>2026-08-31表征全链路独立审查</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.19</t>
+          <t>v4.0-alpha.20</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>表征科学属性</t>
+          <t>实体/物料批次</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>PropertyValue 补齐数值/文本表示类型与物理范围，并统一后端和前端的单一源校验</t>
+          <t>云母衬底增加白云母、金云母和氟金云母类型选择，并由系统生成理想化学式，避免选择材料后在表单顶部突然出现手填化学式</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31表征全链路独立审查</t>
+          <t>2026-09-01用户试填反馈</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.20</t>
+          <t>v4.0-alpha.21</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>实体/物料批次</t>
+          <t>实体/制备/样品与表征流程</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>云母衬底增加白云母、金云母和氟金云母类型选择，并由系统生成理想化学式，避免选择材料后在表单顶部突然出现手填化学式</t>
+          <t>仪器能力改为勾选、日期改为日期控件、装置使用身份标签、异常改为显式确认、表征入口保留样品上下文，并在编辑后清除旧校验错误</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01用户试填反馈</t>
+          <t>2026-09-01全表单交互复核</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.21</t>
+          <t>v4.0-alpha.22</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>实体/制备/样品与表征流程</t>
+          <t>§3/§5 生长条件与装置履历</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>仪器能力改为勾选、日期改为日期控件、装置使用身份标签、异常改为显式确认、表征入口保留样品上下文，并在编辑后清除旧校验错误</t>
+          <t>生长条件按实验前准备、温度、气体、反应压力、降温和异常分区；温度步骤移除待判断与初始温度伪时长；异常改为勾选框，并缩短温区和炉管履历文案</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01全表单交互复核</t>
+          <t>2026-09-02用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.22</t>
+          <t>v4.0-alpha.23</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>§3/§5 生长条件与装置履历</t>
+          <t>§1b/§3/§4/§5 制备记录填写体验</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>生长条件按实验前准备、温度、气体、反应压力、降温和异常分区；温度步骤移除待判断与初始温度伪时长；异常改为勾选框，并缩短温区和炉管履历文案</t>
+          <t>缩短晶体结构、实验目标、相对测温点位置、使用前处理、衬底处理和压力条件文案；明确必填空状态与提交检查，并减少气体首段录入步骤</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户界面复核</t>
+          <t>2026-09-02用户全流程复核</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.23</t>
+          <t>v4.0-alpha.24</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>§1b/§3/§4/§5 制备记录填写体验</t>
+          <t>§5 实验前准备</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>缩短晶体结构、实验目标、相对测温点位置、使用前处理、衬底处理和压力条件文案；明确必填空状态与提交检查，并减少气体首段录入步骤</t>
+          <t>抽真空优先记录终点绝对压力；有压力读数时持续时间改为选填，无压力读数时持续时间必填</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户全流程复核</t>
+          <t>2026-09-02用户实验前准备复核</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.24</t>
+          <t>v4.0-alpha.26</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>§5 实验前准备</t>
+          <t>§1b 目标材料</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>抽真空优先记录终点绝对压力；有压力读数时持续时间改为选填，无压力读数时持续时间必填</t>
+          <t>单一材料改为本征材料，原子层数改为材料层数；删除无法预知的目标覆盖状态和语义混淆的目标生长取向，以目标产物形态和条件平面轮廓表达预期形态</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户实验前准备复核</t>
+          <t>2026-09-03用户目标材料复核</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.26</t>
+          <t>v4.0-alpha.27</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>§1b 目标材料</t>
+          <t>装置与衬底</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>单一材料改为本征材料，原子层数改为材料层数；删除无法预知的目标覆盖状态和语义混淆的目标生长取向，以目标产物形态和条件平面轮廓表达预期形态</t>
+          <t>外场能力增加具名其他；衬底批号改为按标签提供情况条件填写并补生产日期；衬底处理合并为可展开溶剂清洗，并以紫外/臭氧处理替代笼统亲水处理</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户目标材料复核</t>
+          <t>2026-09-03用户装置与衬底复核</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.27</t>
+          <t>v4.0-alpha.35</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>装置与衬底</t>
+          <t>表征客观测量</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>外场能力增加具名其他；衬底批号改为按标签提供情况条件填写并补生产日期；衬底处理合并为可展开溶剂清洗，并以紫外/臭氧处理替代笼统亲水处理</t>
+          <t>新表征不分区域、不录入材料判定；谱峰按编号记录峰位、半高全宽和强度，区分未分析与未检出；AFM、电子显微镜、元素定量按方法与模式显示，历史判定不再自动汇总成整片样品结论</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户装置与衬底复核</t>
+          <t>2026-09-04用户表征复核</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.35</t>
+          <t>R0</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>表征客观测量</t>
+          <t>最小可复现核心(27项，含条件必填)</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>新表征不分区域、不录入材料判定；谱峰按编号记录峰位、半高全宽和强度，区分未分析与未检出；AFM、电子显微镜、元素定量按方法与模式显示，历史判定不再自动汇总成整片样品结论</t>
+          <t>过程R0以温度/气体/压力通道和降温条件为准；不再要求人工划分反应阶段或反应时长</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户表征复核</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>R0</t>
-        </is>
-      </c>
-      <c r="B96" s="11" t="inlineStr">
-        <is>
-          <t>最小可复现核心(27项，含条件必填)</t>
-        </is>
-      </c>
-      <c r="C96" s="11" t="inlineStr">
-        <is>
-          <t>过程R0以温度/气体/压力通道和降温条件为准；不再要求人工划分反应阶段或反应时长</t>
-        </is>
-      </c>
-      <c r="D96" s="11" t="inlineStr">
-        <is>
           <t>必填集</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>问题</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>化学式 / 异质结 标准写法（渲染规则，找国标或组内定）</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>待办</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>化学式录入：文本+元素校验/自动补全（建议，非周期表点选）</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>待办(技术)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr"/>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>── 2026-07-07 导师评审引出的待对齐──</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰·导师K75点名】§7『观察到的现象』粒度：现7项客观多选 vs 只记『生长/不生长』？可带折中案：一级『生长/未生长』必选＋二级现象细分可选（保失败溯源卖点）</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(问俊杰)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】SEM覆盖率：组里习惯的叫法/量化方式/单位？（导师问『SEM占比是什么』，已先改名『SEM覆盖率(视场内材料面积占比,%)』）</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(问俊杰)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】堆垛类型实际可判到什么粒度（2H/3R？AA/AB/ABC？扭转角？）→ 决定自由文本还是下拉词表</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(问俊杰)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】前驱体『外观描述』词表：组里常用前驱体的形态 + 潮解/变质后的典型外观有哪些</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(问俊杰)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>【回导师】①SEM占比=SEM视场内材料面积覆盖占比（已改名并给定义）；②必填/选填已加图例行+字体强化，表单UI将用红星标必填</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>待回复</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】低压CVD的漏率是否逐炉记录，以及应归入装置校验还是实验过程</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(本轮不记录漏率)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】多气体比例的组内标准名称；系统当前由同时间段各气体流量派生</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(不另存重复比例)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】掺杂体系“基体/主体/本征材料”的最终角色术语与常见括号化学式示例</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(结构已支持)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>【问俊杰】压片等前驱体处理方式的最小参数模板</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>待对齐(当前使用具名参数—值—单位)</t>
         </is>
       </c>
     </row>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3601,22 +3601,22 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>源容器</t>
+          <t>相对测温点位置</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>需要追溯具体舟、坩埚或其他源容器时，引用已登记容器实例</t>
+          <t>独立前驱体源相对所选温区测温点的有符号轴向距离</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>容器实例引用</t>
+          <t>源位置对象</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>ContainerInstance UUID</t>
+          <t>{reference: zone_thermocouple, axial_mm}</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -3624,24 +3624,24 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(装载方式=舟/坩埚/其他)</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>550e8400-e29b-41d4-a716-446655440000</t>
+          <t>{reference: zone_thermocouple, axial_mm: -20}</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>会议·科学修订契约</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>不为普通试填增加容器尺寸和履历负担；仅在课题组确实管理具体容器时引用</t>
+          <t>温区由heating_zone_ref单独保存；zone_thermocouple 为保留的历史机器码，当前指所选温区测温点，不限定传感器类型</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr"/>
@@ -3654,27 +3654,27 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>相对测温点位置</t>
+          <t>前驱体所在温区</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>独立前驱体源相对所选温区测温点的有符号轴向距离</t>
+          <t>独立前驱体源所属的加热温区，同时是轴向位置的测温点参照</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>源位置对象</t>
+          <t>温区选择</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>{reference: zone_thermocouple, axial_mm}</t>
+          <t>zone_1·zone_2·…</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -3684,90 +3684,86 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>{reference: zone_thermocouple, axial_mm: -20}</t>
+          <t>zone_2</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>会议·科学修订契约</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>温区由heating_zone_ref单独保存；zone_thermocouple 为保留的历史机器码，当前指所选温区测温点，不限定传感器类型</t>
+          <t>选择涂覆在衬底表面时继承关联衬底的温区与位置</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr"/>
     </row>
-    <row r="63">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>前驱体</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>前驱体所在温区</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>独立前驱体源所属的加热温区，同时是轴向位置的测温点参照</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>温区选择</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>zone_1·zone_2·…</t>
-        </is>
-      </c>
-      <c r="F63" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(装载方式=舟/坩埚/其他)</t>
-        </is>
-      </c>
-      <c r="H63" s="11" t="inlineStr">
-        <is>
-          <t>zone_2</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>选择涂覆在衬底表面时继承关联衬底的温区与位置</t>
-        </is>
-      </c>
-      <c r="K63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>§4 衬底（长在什么基底上，可多片）</t>
         </is>
       </c>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>衬底材料（来自批次）</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>SiO₂/Si</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -3777,22 +3773,22 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>衬底材料（来自批次）</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>引用衬底批号并冻结当时版本、规格与证据</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -3807,15 +3803,19 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>Sapphire-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>必须引用衬底类别的不可变物料版本</t>
+        </is>
+      </c>
       <c r="K65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
@@ -3826,22 +3826,22 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>本次样片标记</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>引用衬底批号并冻结当时版本、规格与证据</t>
+          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>实体版本引用</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>{entity_id, version, snapshot}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>Sapphire-B202（锁 v1）</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>必须引用衬底类别的不可变物料版本</t>
+          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr"/>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>本次样片标记</t>
+          <t>衬底化学式（来自批次）</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
+          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>标准化学式</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -3909,17 +3909,17 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>Al₂O₃</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
+          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr"/>
@@ -3932,22 +3932,22 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>衬底化学式（来自批次）</t>
+          <t>取向与抛光信息（来自批次）</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>标准化学式</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -3955,24 +3955,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G68" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Al₂O₃</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
+          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
@@ -3985,22 +3985,22 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光信息（来自批次）</t>
+          <t>标称晶面取向（来自批次）</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
+          <t>批次标称晶面、取向状态或供应商切型；SiO₂/Si指底层Si；历史混合文本保留原意</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>规范晶面指数或明确的未知/非晶/多晶状态</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填（批次有明确规格时只读带出）</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>(0 0 0 1)</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
+          <t>不与化学式或偏转角合并</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr"/>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>标称晶面取向（来自批次）</t>
+          <t>抛光状态（来自批次）</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>批次标称晶面、取向状态或供应商切型；SiO₂/Si指底层Si；历史混合文本保留原意</t>
+          <t>批次独立登记的抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>规范晶面指数或明确的未知/非晶/多晶状态</t>
+          <t>单面抛/双面抛/未抛光/未知</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -4063,22 +4063,22 @@
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>选填（批次有明确规格时只读带出）</t>
+          <t>选填（来自批次）</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>(0 0 0 1)</t>
+          <t>single_side_polished</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-09-09用户确认</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>不与化学式或偏转角合并</t>
+          <t>不从晶面或非晶状态推断抛光；旧记录的混合文本不重写</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr"/>
@@ -4091,22 +4091,22 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>抛光状态（来自批次）</t>
+          <t>偏切信息（来自批次）</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>批次独立登记的抛光规格；引用批次后只读</t>
+          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>单面抛/双面抛/未抛光/未知</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>选填（来自批次）</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>single_side_polished</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09用户确认</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>不从晶面或非晶状态推断抛光；旧记录的混合文本不重写</t>
+          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
         </is>
       </c>
       <c r="K71" s="11" t="inlineStr"/>
@@ -4144,27 +4144,27 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>偏切信息（来自批次）</t>
+          <t>偏切角（相对标称晶面，来自批次）</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
+          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -4184,10 +4184,14 @@
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
-        </is>
-      </c>
-      <c r="K72" s="11" t="inlineStr"/>
+          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -4197,17 +4201,17 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>偏切角（相对标称晶面，来自批次）</t>
+          <t>偏切方向（来自批次）</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
+          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -4217,7 +4221,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
@@ -4227,24 +4231,20 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>c面向a轴偏0.2°</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
-        </is>
-      </c>
-      <c r="K73" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -4254,50 +4254,50 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>偏切方向（来自批次）</t>
+          <t>氧化层厚度（来自批次）</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
+          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴偏0.2°</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr">
-        <is>
-          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
-        </is>
-      </c>
-      <c r="K74" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -4307,22 +4307,22 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度（来自批次）</t>
+          <t>标称表面粗糙度（来自批次）</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
+          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>正数</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -4330,27 +4330,27 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G75" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J75" s="11" t="inlineStr"/>
-      <c r="K75" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -4360,47 +4360,47 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>标称表面粗糙度（来自批次）</t>
+          <t>本片实际尺寸与姿态</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
+          <t>本次实验实际放入炉内的这一片衬底的本体尺寸与空间姿态；长度和宽度按样片自身尺寸记录，不随摆放方向换名</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, tilt_azimuth_deg?, upright_growth_face_direction?: 朝下游|朝上游|朝炉管左侧|朝炉管右侧, placement_other?}</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
+          <t>{length_mm: 10, width_mm: 5, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: -15, tilt_azimuth_deg: 180}</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-09-03用户复核</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；length_mm必须大于等于width_mm；placement=倾角时tilt_angle_deg和tilt_azimuth_deg同时条件必填，倾角大于-90°、小于90°且不等于0°，方位角大于等于0°且小于360°；placement=竖放时upright_growth_face_direction条件必填；placement=其他时placement_other条件必填</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr"/>
@@ -4413,22 +4413,22 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>本片实际尺寸与姿态</t>
+          <t>片间生长面相对关系</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际放入炉内的这一片衬底的本体尺寸与空间姿态；长度和宽度按样片自身尺寸记录，不随摆放方向换名</t>
+          <t>两片衬底的生长面相对摆放关系；与单片空间姿态分开记录</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>衬底尺寸放置对象</t>
+          <t>衬底片间关系数组</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, tilt_azimuth_deg?, upright_growth_face_direction?: 朝下游|朝上游|朝炉管左侧|朝炉管右侧, placement_other?}</t>
+          <t>[{piece_a_label, piece_b_label, gap_mm?}]</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4436,14 +4436,14 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>选填（仅多片衬底且存在该关系时）</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>{length_mm: 10, width_mm: 5, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: -15, tilt_azimuth_deg: 180}</t>
+          <t>[{piece_a_label: S1, piece_b_label: S2, gap_mm: 0}]</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>每片可能经过切割，故不得用批次来料尺寸替代；length_mm必须大于等于width_mm；placement=倾角时tilt_angle_deg和tilt_azimuth_deg同时条件必填，倾角大于-90°、小于90°且不等于0°，方位角大于等于0°且小于360°；placement=竖放时upright_growth_face_direction条件必填；placement=其他时placement_other条件必填</t>
+          <t>只在衬底片数不少于2且确实生长面相对时记录；两端必须引用本炉次不同的piece_label，同一无序对不得重复；gap_mm选填且大于等于0，0表示接触</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
@@ -4466,47 +4466,47 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>片间生长面相对关系</t>
+          <t>衬底处理（有序步骤）</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>两片衬底的生长面相对摆放关系；与单片空间姿态分开记录</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>衬底片间关系数组</t>
+          <t>衬底预处理步骤数组</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>[{piece_a_label, piece_b_label, gap_mm?}]</t>
+          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外/臭氧表面处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外/臭氧表面处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>选填（仅多片衬底且存在该关系时）</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>[{piece_a_label: S1, piece_b_label: S2, gap_mm: 0}]</t>
+          <t>[{type: 溶剂清洗, parameters: {solvent: 丙酮, cleaning_method: 超声, duration_min: 10}}, {type: 溶剂清洗, parameters: {solvent: 异丙醇, cleaning_method: 冲洗}}, {type: 氮气吹干}]</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>只在衬底片数不少于2且确实生长面相对时记录；两端必须引用本炉次不同的piece_label，同一无序对不得重复；gap_mm选填且大于等于0，0表示接触</t>
+          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外/臭氧表面处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr"/>
@@ -4519,50 +4519,54 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>衬底处理（有序步骤）</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>衬底预处理步骤数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外/臭氧表面处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外/臭氧表面处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>[{type: 溶剂清洗, parameters: {solvent: 丙酮, cleaning_method: 超声, duration_min: 10}}, {type: 溶剂清洗, parameters: {solvent: 异丙醇, cleaning_method: 冲洗}}, {type: 氮气吹干}]</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外/臭氧表面处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
-        </is>
-      </c>
-      <c r="K79" s="11" t="inlineStr"/>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -4572,27 +4576,27 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>预处理后等待时间</t>
+          <t>暴露环境</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>预处理结束到放入实验装置的时间</t>
+          <t>处理完成到放入实验装置期间所处环境</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>空气/氮气/真空/其他</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G80" s="13" t="inlineStr">
@@ -4602,24 +4606,20 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>空气</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>表面老化</t>
-        </is>
-      </c>
-      <c r="K80" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>与时间间隔独立保存</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -4629,47 +4629,47 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>暴露环境</t>
+          <t>所在温区与相对测温点位置</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>处理完成到放入实验装置期间所处环境</t>
+          <t>第几温区、距离(±)</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>温区距离对象</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>空气/氮气/真空/其他</t>
+          <t>{zone_index, distance_mm}</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>温区2，+15</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>与时间间隔独立保存</t>
+          <t>上游为负、下游为正</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr"/>
@@ -4682,22 +4682,22 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>所在温区与相对测温点位置</t>
+          <t>轴向位置</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>第几温区、距离(±)</t>
+          <t>本片衬底相对装置轴向原点的位置</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>温区距离对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, distance_mm}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
@@ -4705,24 +4705,24 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G82" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>温区2，+15</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-30产品简化</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>上游为负、下游为正</t>
+          <t>仅兼容旧记录；新记录统一填写所在温区与测温点距离，不再使用未定义物理原点的全局轴向位置</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr"/>
@@ -4735,17 +4735,17 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>轴向位置</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>本片衬底相对装置轴向原点的位置</t>
+          <t>本片衬底摆放或处理的补充说明</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>靠近气体入口</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -4773,128 +4773,128 @@
           <t>2026-07-30产品简化</t>
         </is>
       </c>
-      <c r="J83" s="11" t="inlineStr">
-        <is>
-          <t>仅兼容旧记录；新记录统一填写所在温区与测温点距离，不再使用未定义物理原点的全局轴向位置</t>
-        </is>
-      </c>
+      <c r="J83" s="11" t="inlineStr"/>
       <c r="K83" s="11" t="inlineStr"/>
     </row>
-    <row r="84">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>衬底</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
-        <is>
-          <t>本片衬底摆放或处理的补充说明</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G84" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H84" s="11" t="inlineStr">
-        <is>
-          <t>靠近气体入口</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-30产品简化</t>
-        </is>
-      </c>
-      <c r="J84" s="11" t="inlineStr"/>
-      <c r="K84" s="11" t="inlineStr"/>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
         </is>
       </c>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
-      <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
-      <c r="I85" s="8" t="n"/>
-      <c r="J85" s="8" t="n"/>
-      <c r="K85" s="8" t="n"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="8" t="n"/>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>过程步</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>过程阶段</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>兼容已有具名过程阶段；新记录可留空，实际时间由过程通道和操作派生</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>过程阶段数组</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>{segment_key, segment_type, sequence, start_s, end_s, label?, note?}</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>未发布（历史修订只读兼容）</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-07用户复核</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>不要求用户划分反应开始或手算阶段起止时间</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>过程通道</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>过程阶段</t>
+          <t>温度、气体与压力程序</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>兼容已有具名过程阶段；新记录可留空，实际时间由过程通道和操作派生</t>
+          <t>以统一实验时间零点记录每温区设定温度、每个实际气瓶供气区间及需要时的工作绝对压力</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>过程阶段数组</t>
+          <t>强类型过程通道数组</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>{segment_key, segment_type, sequence, start_s, end_s, label?, note?}</t>
+          <t>{channel_key, channel_type: temperature|flow|pressure|…, source_type, subject_type, subject_ref, subject_instance_ref, unit, data_kind, scalar_value?|series?|file_asset_id?, gas_lot_id?, gas_lot_version?, measurement_source?}</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G86" s="13" t="inlineStr">
-        <is>
-          <t>未发布（历史修订只读兼容）</t>
+          <t>按通道</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{channel_type: temperature, subject_ref: zone_1, unit: ℃, data_kind: interval_series, series: [{start_s: 0, value: 25}, {start_s: 1800, value: 750}]}]</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户复核</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>不要求用户划分反应开始或手算阶段起止时间</t>
+          <t>每个Setup温区必须有且仅有一条设定温度通道；至少一条正流量气体通道</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr"/>
@@ -4907,50 +4907,54 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>温度、气体与压力程序</t>
+          <t>过程总时长</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>以统一实验时间零点记录每温区设定温度、每个实际气瓶供气区间及需要时的工作绝对压力</t>
+          <t>从统一实验开始时间到本次制备过程结束的总时长，包含记录的降温与供气</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>强类型过程通道数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>{channel_key, channel_type: temperature|flow|pressure|…, source_type, subject_type, subject_ref, subject_instance_ref, unit, data_kind, scalar_value?|series?|file_asset_id?, gas_lot_id?, gas_lot_version?, measurement_source?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>按通道</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>必填</t>
+          <t>必填（历史记录可缺省，不推算补值）</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>[{channel_type: temperature, subject_ref: zone_1, unit: ℃, data_kind: interval_series, series: [{start_s: 0, value: 25}, {start_s: 1800, value: 750}]}]</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-09-04用户确认</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>每个Setup温区必须有且仅有一条设定温度通道；至少一条正流量气体通道</t>
-        </is>
-      </c>
-      <c r="K87" s="11" t="inlineStr"/>
+          <t>全程供气的起止为0至该时长；温度、供气、外场和事件不得超出，不以最后一个温度步骤代替过程终点</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -4960,79 +4964,75 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>过程总时长</t>
+          <t>本炉发生过异常</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>从统一实验开始时间到本次制备过程结束的总时长，包含记录的降温与供气</t>
+          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>勾选框</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>勾选=是；未勾选=否</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>必填（历史记录可缺省，不推算补值）</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>未勾选</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户确认</t>
+          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>全程供气的起止为0至该时长；温度、供气、外场和事件不得超出，不以最后一个温度步骤代替过程终点</t>
-        </is>
-      </c>
-      <c r="K88" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>勾选时至少填写一条过程异常事件</t>
+        </is>
+      </c>
+      <c r="K88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>过程通道</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>本炉发生过异常</t>
+          <t>反应压力条件</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
+          <t>相对于当地环境大气压的减压、常压或加压条件</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>勾选框</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>勾选=是；未勾选=否</t>
+          <t>atmospheric/low_pressure/high_pressure</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -5047,17 +5047,17 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>未勾选</t>
+          <t>low_pressure</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>勾选时至少填写一条过程异常事件</t>
+          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr"/>
@@ -5065,17 +5065,17 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件</t>
+          <t>降温方式</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>相对于当地环境大气压的减压、常压或加压条件</t>
+          <t>本炉实际采用的降温方式</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>atmospheric/low_pressure/high_pressure</t>
+          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/staged_cooling/other</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>low_pressure</t>
+          <t>furnace_cooling</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
+          <t>程序降温复用温度步骤；分段降温按cooling_sequence记录先后顺序；随炉冷却和移炉冷却不要求虚构速率</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr"/>
@@ -5123,22 +5123,22 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>降温方式</t>
+          <t>降温顺序</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>本炉实际采用的降温方式</t>
+          <t>两种或更多降温操作的实际先后顺序；程序降温的温度和时长仍只记录在温度程序</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>有序降温操作数组</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/staged_cooling/other</t>
+          <t>{method, lid_open_temperature_C?, other_name?}</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -5146,24 +5146,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G91" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G91" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=staged_cooling)</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling</t>
+          <t>[{method: controlled_cooling}, {method: furnace_cooling}]</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-09-04用户确认</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>程序降温复用温度步骤；分段降温按cooling_sequence记录先后顺序；随炉冷却和移炉冷却不要求虚构速率</t>
+          <t>至少两段；开盖段填写开盖温度，其他段填写名称；不自动推断未记录的自然冷却温度曲线</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr"/>
@@ -5176,22 +5176,22 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>降温顺序</t>
+          <t>其他降温方式</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>两种或更多降温操作的实际先后顺序；程序降温的温度和时长仍只记录在温度程序</t>
+          <t>降温方式选择其他时的具体操作</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>有序降温操作数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>{method, lid_open_temperature_C?, other_name?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -5201,22 +5201,22 @@
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>条件必填(降温方式=staged_cooling)</t>
+          <t>条件必填(降温方式=other)</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>[{method: controlled_cooling}, {method: furnace_cooling}]</t>
+          <t>打开保温层自然冷却</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户确认</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>至少两段；开盖段填写开盖温度，其他段填写名称；不自动推断未记录的自然冷却温度曲线</t>
+          <t>仅选择其他时保存</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr"/>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>其他降温方式</t>
+          <t>旧记录设定降温速率</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>降温方式选择其他时的具体操作</t>
+          <t>保留旧记录独立填写的设定降温速率；新记录按温度程序各降温段派生</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -5249,17 +5249,17 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G93" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=other)</t>
+          <t>℃/min</t>
+        </is>
+      </c>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>未发布（历史兼容）</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>打开保温层自然冷却</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -5269,10 +5269,14 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>仅选择其他时保存</t>
-        </is>
-      </c>
-      <c r="K93" s="11" t="inlineStr"/>
+          <t>不再要求新记录填写单一降温速率；旧记录保留，不解释为实测值</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -5282,12 +5286,12 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>旧记录设定降温速率</t>
+          <t>开盖温度</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>保留旧记录独立填写的设定降温速率；新记录按温度程序各降温段派生</t>
+          <t>开盖冷却时实际开盖的温度</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
@@ -5302,17 +5306,17 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>℃/min</t>
-        </is>
-      </c>
-      <c r="G94" s="13" t="inlineStr">
-        <is>
-          <t>未发布（历史兼容）</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=open_lid_cooling)</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -5322,64 +5326,60 @@
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>不再要求新记录填写单一降温速率；旧记录保留，不解释为实测值</t>
-        </is>
-      </c>
-      <c r="K94" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>仅开盖冷却时保存</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>开盖温度</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>开盖冷却时实际开盖的温度</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G95" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=open_lid_cooling)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>仅开盖冷却时保存</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr"/>
@@ -5392,22 +5392,22 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>实验前准备操作</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>按实际添加抽真空、气氛置换或其他操作；检漏属于设备操作规程，不设状态或自动确认。气氛置换按连续通气或抽空—回填展开，引用实际气瓶版本</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>{operation_type: pump_down|gas_exchange|other, exchange_mode?: continuous_flow|evacuation_backfill, duration_min?, target_absolute_pressure_Pa?, backfill_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, flow_sccm?, snapshot?}], other_name?}</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>[{operation_type: gas_exchange, exchange_mode: continuous_flow, duration_min: 10, gas_sources: [{material_lot_id: UUID, material_lot_version: 2, flow_sccm: 100}]}]</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-08-13师兄试填复核</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
+          <t>抽真空终点压力与时长至少一项；连续通气要求总时长，不填循环次数；抽空—回填要求循环次数，总时长和两端绝对压力选填，已知回填压力应高于抽空压力。流量按每瓶记录且选填，混气组成不重复录入。旧检漏转为具名其他且保留时长；旧置换方式不推断，编辑时需确认</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr"/>
@@ -5440,52 +5440,52 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>实验前准备操作</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>按实际添加抽真空、气氛置换或其他操作；检漏属于设备操作规程，不设状态或自动确认。气氛置换按连续通气或抽空—回填展开，引用实际气瓶版本</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>预处理操作数组</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>{operation_type: pump_down|gas_exchange|other, exchange_mode?: continuous_flow|evacuation_backfill, duration_min?, target_absolute_pressure_Pa?, backfill_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, flow_sccm?, snapshot?}], other_name?}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>[{operation_type: gas_exchange, exchange_mode: continuous_flow, duration_min: 10, gas_sources: [{material_lot_id: UUID, material_lot_version: 2, flow_sccm: 100}]}]</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13师兄试填复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>抽真空终点压力与时长至少一项；连续通气要求总时长，不填循环次数；抽空—回填要求循环次数，总时长和两端绝对压力选填，已知回填压力应高于抽空压力。流量按每瓶记录且选填，混气组成不重复录入。旧检漏转为具名其他且保留时长；旧置换方式不推断，编辑时需确认</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr"/>
@@ -5498,27 +5498,27 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
+          <t>℃ 随时间</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr"/>
@@ -5546,32 +5546,32 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
+          <t>min·sccm</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr"/>
@@ -5599,32 +5599,32 @@
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>反应压力条件与工作绝对压力</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>常压；或低压 500 Pa</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -5644,40 +5644,44 @@
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
-        </is>
-      </c>
-      <c r="K100" s="11" t="inlineStr"/>
+          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件与工作绝对压力</t>
+          <t>反应持续时间</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>从统一实验时间零点起计的反应条件持续时间</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{duration_min；旧记录可含cycle_count}</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -5687,54 +5691,50 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>常压；或低压 500 Pa</t>
+          <t>{duration_min: 45}</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K101" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
-        </is>
-      </c>
+          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>反应持续时间</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>从统一实验时间零点起计的反应条件持续时间</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>{duration_min；旧记录可含cycle_count}</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>℃·℃/min</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
@@ -5744,17 +5744,17 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45}</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
+          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr"/>
@@ -5762,42 +5762,42 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>附加能力使用记录</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>实际外场数组</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>{field_type: 等离子体|光|电|其他, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；其他[capability_name, 至少一个具名参数]；other_parameters?}</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
+          <t>按参数</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
+          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数；自定义能力名称须来自Setup版本快照列表；旧单名称兼容，不按标点猜拆</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr"/>
@@ -5815,52 +5815,52 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>附加能力使用记录</t>
+          <t>其他记录名称</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电|其他, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；其他[capability_name, 至少一个具名参数]；other_parameters?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>临时移动源舟</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数；自定义能力名称须来自Setup版本快照列表；旧单名称兼容，不按标点猜拆</t>
+          <t>禁止仅保存“其他”</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr"/>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>其他记录说明</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -5913,80 +5913,80 @@
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
       <c r="K105" s="11" t="inlineStr"/>
     </row>
-    <row r="106">
-      <c r="A106" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t>其他记录说明</t>
-        </is>
-      </c>
-      <c r="C106" s="11" t="inlineStr">
-        <is>
-          <t>说明该记录的时间、操作和必要参数</t>
-        </is>
-      </c>
-      <c r="D106" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E106" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F106" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G106" s="13" t="inlineStr">
-        <is>
-          <t>未发布（旧过程步兼容）</t>
-        </is>
-      </c>
-      <c r="H106" s="11" t="inlineStr">
-        <is>
-          <t>第30分钟将源舟向下游移动10 mm</t>
-        </is>
-      </c>
-      <c r="I106" s="11" t="inlineStr">
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（记录异常、中断与计划变更等客观事件；只记客观事实，不判成败）</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="8" t="n"/>
+      <c r="D106" s="8" t="n"/>
+      <c r="E106" s="8" t="n"/>
+      <c r="F106" s="8" t="n"/>
+      <c r="G106" s="8" t="n"/>
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="8" t="n"/>
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>事件标识</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>系统生成键</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>event_1</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
         <is>
           <t>2026-07-24整改</t>
         </is>
       </c>
-      <c r="J106" s="11" t="inlineStr">
-        <is>
-          <t>必须持久化，绝不静默过滤</t>
-        </is>
-      </c>
-      <c r="K106" s="11" t="inlineStr"/>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（记录异常、中断与计划变更等客观事件；只记客观事实，不判成败）</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="n"/>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-      <c r="J107" s="8" t="n"/>
-      <c r="K107" s="8" t="n"/>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>创建事件时生成，排序和编辑不得改变</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>事件标识</t>
+          <t>观察到的偏差</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+          <t>过程中直接观察到的异常或计划变更；人工干预、人工停止统一归为计划变更</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>系统生成键</t>
+          <t>多选+其他</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/设备报警/信号异常/计划变更/其他</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
+          <t>按供给中断、管路/压力、设备/信号、计划变更、其他排序；具体干预写采取的处理，是否终止写处理结果；旧类型读取时归并并保留原类型文字，不修改历史原文</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr"/>
@@ -6049,22 +6049,22 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差</t>
+          <t>受影响对象</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>过程中直接观察到的异常或计划变更；人工干预、人工停止统一归为计划变更</t>
+          <t>观察到的偏差涉及的实验对象</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>多选+其他</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/设备报警/信号异常/计划变更/其他</t>
+          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -6072,14 +6072,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G109" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>供气中断</t>
+          <t>气路</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>按供给中断、管路/压力、设备/信号、计划变更、其他排序；具体干预写采取的处理，是否终止写处理结果；旧类型读取时归并并保留原类型文字，不修改历史原文</t>
+          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr"/>
@@ -6102,37 +6102,37 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>受影响对象</t>
+          <t>开始时间</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差涉及的实验对象</t>
+          <t>相对本炉实验开始时刻的事件开始时间</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G110" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>气路</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="J110" s="11" t="inlineStr">
         <is>
-          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
+          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr"/>
@@ -6155,12 +6155,12 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>开始时间</t>
+          <t>结束时间</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件开始时间</t>
+          <t>相对本炉实验开始时刻的事件结束时间</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
@@ -6178,14 +6178,14 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G111" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
+          <t>填写时不得早于开始时间</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr"/>
@@ -6208,27 +6208,27 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>结束时间</t>
+          <t>处理结果</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件结束时间</t>
+          <t>异常发生后过程是否恢复或终止</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已恢复/部分恢复/实验终止/未知</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>已恢复</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="J112" s="11" t="inlineStr">
         <is>
-          <t>填写时不得早于开始时间</t>
+          <t>未知可显式记录，不等同于对产物成败的判定</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr"/>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>处理结果</t>
+          <t>对数据有效性的影响</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>异常发生后过程是否恢复或终止</t>
+          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>已恢复/部分恢复/实验终止/未知</t>
+          <t>不影响/部分影响/数据无效/未知</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>已恢复</t>
+          <t>部分影响</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>未知可显式记录，不等同于对产物成败的判定</t>
+          <t>只判断过程数据有效性，不判定产物成败</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr"/>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>对数据有效性的影响</t>
+          <t>怀疑原因</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
+          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>不影响/部分影响/数据无效/未知</t>
+          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>部分影响</t>
+          <t>设备故障</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="J114" s="11" t="inlineStr">
         <is>
-          <t>只判断过程数据有效性，不判定产物成败</t>
+          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr"/>
@@ -6367,22 +6367,22 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>怀疑原因</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -6392,22 +6392,22 @@
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>选填；观察到的偏差包含其他时必填</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>设备故障</t>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
+          <t>其他异常时必填；最多2048字符，容纳旧分类前缀。界面分开填写异常情况与采取的处理，保存沿用现有描述分隔格式；附件独立关联</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr"/>
@@ -6420,22 +6420,22 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>干预动作</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>事件发生后实际采取的操作</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
@@ -6445,22 +6445,22 @@
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>选填；观察到的偏差包含其他时必填</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>恢复供应</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr">
         <is>
-          <t>其他异常时必填；最多2048字符，容纳旧分类前缀。界面分开填写异常情况与采取的处理，保存沿用现有描述分隔格式；附件独立关联</t>
+          <t>与事件说明独立保存</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr"/>
@@ -6473,27 +6473,27 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>干预动作</t>
+          <t>排除的数据时间范围</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>事件发生后实际采取的操作</t>
+          <t>因该事件不应参与后续分析的时间区间</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>时间区间数组</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
+          <t>[{start_s, end_s}]</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>恢复供应</t>
+          <t>[{start_s: 1680, end_s: 1800}]</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr"/>
@@ -6526,27 +6526,27 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>排除的数据时间范围</t>
+          <t>事件附件</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>因该事件不应参与后续分析的时间区间</t>
+          <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>时间区间数组</t>
+          <t>FileAsset引用数组</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>[{start_s, end_s}]</t>
+          <t>FileAsset UUID列表</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
@@ -6556,90 +6556,90 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>[{start_s: 1680, end_s: 1800}]</t>
+          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr">
         <is>
-          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
+          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr"/>
     </row>
-    <row r="119">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t>事件附件</t>
-        </is>
-      </c>
-      <c r="C119" s="11" t="inlineStr">
-        <is>
-          <t>与本条事件直接关联的图片、日志或其他文件</t>
-        </is>
-      </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset引用数组</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset UUID列表</t>
-        </is>
-      </c>
-      <c r="F119" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G119" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H119" s="11" t="inlineStr">
-        <is>
-          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
-        </is>
-      </c>
-      <c r="I119" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J119" s="11" t="inlineStr">
-        <is>
-          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
-        </is>
-      </c>
-      <c r="K119" s="11" t="inlineStr"/>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="10" t="inlineStr">
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>§7 旧扁平结果字段（未发布；由 MeasurementRun → AnalysisRun → PropertyValue / MaterialAssertion 替代）</t>
         </is>
       </c>
-      <c r="B120" s="8" t="n"/>
-      <c r="C120" s="8" t="n"/>
-      <c r="D120" s="8" t="n"/>
-      <c r="E120" s="8" t="n"/>
-      <c r="F120" s="8" t="n"/>
-      <c r="G120" s="8" t="n"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="8" t="n"/>
-      <c r="J120" s="8" t="n"/>
-      <c r="K120" s="8" t="n"/>
+      <c r="B119" s="8" t="n"/>
+      <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="8" t="n"/>
+      <c r="F119" s="8" t="n"/>
+      <c r="G119" s="8" t="n"/>
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="8" t="n"/>
+      <c r="J119" s="8" t="n"/>
+      <c r="K119" s="8" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>表征</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>表征方法</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>Raman</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J120" s="15" t="inlineStr">
+        <is>
+          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
@@ -6649,22 +6649,22 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>表征方法</t>
+          <t>测试条件</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
+          <t>该表征的测试参数</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本/自由</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>激光532 nm；功率1 mW；物镜100×</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -6687,9 +6687,9 @@
           <t>会议</t>
         </is>
       </c>
-      <c r="J121" s="15" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
+      <c r="J121" s="11" t="inlineStr">
+        <is>
+          <t>随仪器导出</t>
         </is>
       </c>
       <c r="K121" s="11" t="inlineStr"/>
@@ -6702,17 +6702,17 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>测试条件</t>
+          <t>原始数据</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>该表征的测试参数</t>
+          <t>上传原始文件（留校验和）</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>文本/自由</t>
+          <t>附件</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
@@ -6732,45 +6732,41 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>激光532 nm；功率1 mW；物镜100×</t>
+          <t>raman.txt</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J122" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
-        </is>
-      </c>
+          <t>会议/复审</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr"/>
       <c r="K122" s="11" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>实测产物</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>观察到的现象</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>光镜可判的客观现象（非成败判断）</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>下拉+多选</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
@@ -6785,15 +6781,19 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>不连续覆盖</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
-        </is>
-      </c>
-      <c r="J123" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J123" s="15" t="inlineStr">
+        <is>
+          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+        </is>
+      </c>
       <c r="K123" s="11" t="inlineStr"/>
     </row>
     <row r="124">
@@ -6804,22 +6804,22 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>检出相、多型与堆垛</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>测到的物相/多型/堆垛类型</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr">
@@ -6834,17 +6834,17 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>2H-MoS₂；AB堆垛</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>复审/导师</t>
         </is>
       </c>
       <c r="J124" s="15" t="inlineStr">
         <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
+          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
         </is>
       </c>
       <c r="K124" s="11" t="inlineStr"/>
@@ -6857,17 +6857,17 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>实测层数</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>由表征方法判定的层数</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>层</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
@@ -6887,20 +6887,24 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J125" s="15" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
-        </is>
-      </c>
-      <c r="K125" s="11" t="inlineStr"/>
+          <t>复审/科学契约审查</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>历史字段，保留原记录；新表征不录入层数判定，也不将未检出写成层数 0</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -6910,12 +6914,12 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>覆盖率</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>明确视场或统计区域内材料面积占比</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
@@ -6930,7 +6934,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
@@ -6940,7 +6944,7 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -6950,12 +6954,12 @@
       </c>
       <c r="J126" s="11" t="inlineStr">
         <is>
-          <t>历史字段，保留原记录；新表征不录入层数判定，也不将未检出写成层数 0</t>
+          <t>量化口径仍须随表征条件记录</t>
         </is>
       </c>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0,"type":"integer"}</t>
+          <t>{"ge":0,"le":100}</t>
         </is>
       </c>
     </row>
@@ -6967,12 +6971,12 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>覆盖率</t>
+          <t>畴尺寸</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>明确视场或统计区域内材料面积占比</t>
+          <t>由指定统计方法得到的代表性畴尺寸</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -6987,7 +6991,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>μm</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
@@ -6997,7 +7001,7 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
@@ -7005,14 +7009,10 @@
           <t>复审/科学契约审查</t>
         </is>
       </c>
-      <c r="J127" s="11" t="inlineStr">
-        <is>
-          <t>量化口径仍须随表征条件记录</t>
-        </is>
-      </c>
+      <c r="J127" s="11" t="inlineStr"/>
       <c r="K127" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0,"le":100}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -7024,12 +7024,12 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>畴尺寸</t>
+          <t>成核密度</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
+          <t>指定统计区域内单位面积成核点数量</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>μm</t>
+          <t>cm⁻²</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -7065,7 +7065,7 @@
       <c r="J128" s="11" t="inlineStr"/>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0}</t>
+          <t>{"ge":0}</t>
         </is>
       </c>
     </row>
@@ -7077,27 +7077,27 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>成核密度</t>
+          <t>关键谱学指标</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>指定统计区域内单位面积成核点数量</t>
+          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>结构化指标数组</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>每条:{metric_code,value,unit}</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>cm⁻²</t>
+          <t>按指标</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
@@ -7107,94 +7107,90 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J129" s="11" t="inlineStr"/>
+          <t>复审/导师</t>
+        </is>
+      </c>
+      <c r="J129" s="15" t="inlineStr">
+        <is>
+          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
+        </is>
+      </c>
       <c r="K129" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t>实测产物</t>
-        </is>
-      </c>
-      <c r="B130" s="11" t="inlineStr">
-        <is>
-          <t>关键谱学指标</t>
-        </is>
-      </c>
-      <c r="C130" s="11" t="inlineStr">
-        <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
-        </is>
-      </c>
-      <c r="D130" s="11" t="inlineStr">
-        <is>
-          <t>结构化指标数组</t>
-        </is>
-      </c>
-      <c r="E130" s="11" t="inlineStr">
-        <is>
-          <t>每条:{metric_code,value,unit}</t>
-        </is>
-      </c>
-      <c r="F130" s="11" t="inlineStr">
-        <is>
-          <t>按指标</t>
-        </is>
-      </c>
-      <c r="G130" s="13" t="inlineStr">
+          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="n"/>
+      <c r="C130" s="8" t="n"/>
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="8" t="n"/>
+      <c r="G130" s="8" t="n"/>
+      <c r="H130" s="8" t="n"/>
+      <c r="I130" s="8" t="n"/>
+      <c r="J130" s="8" t="n"/>
+      <c r="K130" s="8" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>靶材（批次）</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>靶材化学身份 + 批次</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>引用</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>批次库</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
         <is>
           <t>未发布</t>
         </is>
       </c>
-      <c r="H130" s="11" t="inlineStr">
-        <is>
-          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
-        </is>
-      </c>
-      <c r="I130" s="11" t="inlineStr">
-        <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J130" s="15" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
-        </is>
-      </c>
-      <c r="K130" s="11" t="inlineStr">
-        <is>
-          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B131" s="8" t="n"/>
-      <c r="C131" s="8" t="n"/>
-      <c r="D131" s="8" t="n"/>
-      <c r="E131" s="8" t="n"/>
-      <c r="F131" s="8" t="n"/>
-      <c r="G131" s="8" t="n"/>
-      <c r="H131" s="8" t="n"/>
-      <c r="I131" s="8" t="n"/>
-      <c r="J131" s="8" t="n"/>
-      <c r="K131" s="8" t="n"/>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>MoS₂ 靶-T01</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J131" s="11" t="inlineStr"/>
+      <c r="K131" s="11" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -7204,27 +7200,27 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>靶材化学身份 + 批次</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
@@ -7234,7 +7230,7 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I132" s="11" t="inlineStr">
@@ -7243,7 +7239,11 @@
         </is>
       </c>
       <c r="J132" s="11" t="inlineStr"/>
-      <c r="K132" s="11" t="inlineStr"/>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
@@ -7292,11 +7292,7 @@
         </is>
       </c>
       <c r="J133" s="11" t="inlineStr"/>
-      <c r="K133" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K133" s="11" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
@@ -7306,27 +7302,27 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
@@ -7336,7 +7332,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -7345,7 +7341,11 @@
         </is>
       </c>
       <c r="J134" s="11" t="inlineStr"/>
-      <c r="K134" s="11" t="inlineStr"/>
+      <c r="K134" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
@@ -7355,27 +7355,27 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>等离子体气氛与工作气压</t>
+          <t>预溅射与挡板时序</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>预溅射时长、挡板开合时序</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>min·s</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>预溅 5 min</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
@@ -7396,7 +7396,7 @@
       <c r="J135" s="11" t="inlineStr"/>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0,"require_value":true}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -7408,12 +7408,12 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>沉积速率</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>速率（QCM 等）</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>nm/s</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -7453,70 +7453,17 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B137" s="11" t="inlineStr">
-        <is>
-          <t>沉积速率</t>
-        </is>
-      </c>
-      <c r="C137" s="11" t="inlineStr">
-        <is>
-          <t>速率（QCM 等）</t>
-        </is>
-      </c>
-      <c r="D137" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F137" s="11" t="inlineStr">
-        <is>
-          <t>nm/s</t>
-        </is>
-      </c>
-      <c r="G137" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H137" s="11" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="I137" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J137" s="11" t="inlineStr"/>
-      <c r="K137" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A131:K131"/>
+    <mergeCell ref="A119:K119"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A64:K64"/>
-    <mergeCell ref="A107:K107"/>
+    <mergeCell ref="A130:K130"/>
+    <mergeCell ref="A63:K63"/>
     <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="A84:K84"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A120:K120"/>
+    <mergeCell ref="A106:K106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7528,7 +7475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10588,75 +10535,71 @@
       <c r="J60" s="11" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr"/>
     </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>可更换部件绑定</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>当前Setup版本实际安装的炉管、传感器、MFC、压力计等部件</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>JSON数组</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>[{component_id,role,position?}]</t>
-        </is>
-      </c>
-      <c r="F61" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H61" s="11" t="inlineStr">
-        <is>
-          <t>[{"component_id":"UUID","role":"furnace_tube"}]</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr">
-        <is>
-          <t>部件身份、校准和维护走独立生命周期事件</t>
-        </is>
-      </c>
-      <c r="K61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
         </is>
       </c>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>仪器编号</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>唯一编号</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>RAMAN-1</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -10666,22 +10609,22 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -10696,15 +10639,19 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>API key 保持 name_type 以兼容现有数据；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
+        </is>
+      </c>
       <c r="K63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
@@ -10715,22 +10662,22 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>适用表征方法</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -10738,26 +10685,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
       <c r="K64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
@@ -10768,12 +10711,12 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -10798,7 +10741,7 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -10817,12 +10760,12 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -10840,14 +10783,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -10866,12 +10809,12 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>仪器持久标识</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -10901,10 +10844,14 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr"/>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
       <c r="K67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
@@ -10915,12 +10862,12 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>所在实验室与位置</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>物理位置</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -10945,19 +10892,15 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A305</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr"/>
       <c r="K68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
@@ -10968,22 +10911,22 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>其他固定配置说明</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -10998,15 +10941,19 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
       <c r="K69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
@@ -11017,22 +10964,22 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>其他固定配置说明</t>
+          <t>支持的表征方法</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>[{code,configuration}]；configuration.presets=[{name,conditions}]；code=other 时另有 method_names</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -11040,24 +10987,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>[{"code":"Raman","configuration":{}}]</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+          <t>每种方法可维护最多50套命名预设；名称去空白后1–128字符，同方法内忽略大小写唯一。conditions复用该方法结构化采集字段、单位及校验，至少一项，不要求整套测试必填参数齐全。表征主动选用后复制为本次实际条件，可调整；预设修改产生新仪器版本，不改历史记录。其他方法继续通过method_names具名；保留历史configuration内容。</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr"/>
@@ -11070,22 +11017,22 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>支持的表征方法</t>
+          <t>最近校准或维护日期</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
+          <t>校准/维护日期</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>[{code,configuration}]；configuration.presets=[{name,conditions}]；code=other 时另有 method_names</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -11093,82 +11040,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>[{"code":"Raman","configuration":{}}]</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr">
-        <is>
-          <t>每种方法可维护最多50套命名预设；名称去空白后1–128字符，同方法内忽略大小写唯一。conditions复用该方法结构化采集字段、单位及校验，至少一项，不要求整套测试必填参数齐全。表征主动选用后复制为本次实际条件，可调整；预设修改产生新仪器版本，不改历史记录。其他方法继续通过method_names具名；保留历史configuration内容。</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr"/>
       <c r="K71" s="11" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t>最近校准或维护日期</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>校准/维护日期</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H72" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="I72" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J72" s="11" t="inlineStr"/>
-      <c r="K72" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="A61:K61"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11181,7 +11075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11215,17 +11109,17 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.41</t>
+          <t>v4.0-alpha.49</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>制备目标、附加能力与溶液/衬底处理</t>
+          <t>前驱体源容器、装置部件绑定</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>目标按区域独立组成、掺杂、晶相和层数；几何形态与成膜形式分开；附加能力逐项具名并引用到使用参数；溶液用量按处理步骤记录一次，衬底补适用的可选参数。实验字段125、实体字段63；新增20260909_0016仅增形态投影列，旧载荷保留。</t>
+          <t>删除无录入入口的源容器实例引用与装置可更换部件绑定，以及仪器校准事件快照。</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -11237,17 +11131,17 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.40</t>
+          <t>v4.0-alpha.41</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>制备实验记录文案</t>
+          <t>制备目标、附加能力与溶液/衬底处理</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>删除重复提示，统一处理方式、外场和放置名称；明确设定温度与CSV时间原点，区分未选批次和批次未记录，按实际错误提示。仅调整界面文案，保留字段、校验规则和历史数据。</t>
+          <t>目标按区域独立组成、掺杂、晶相和层数；几何形态与成膜形式分开；附加能力逐项具名并引用到使用参数；溶液用量按处理步骤记录一次，衬底补适用的可选参数。实验字段125、实体字段63；新增20260909_0016仅增形态投影列，旧载荷保留。</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -11259,17 +11153,17 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.39</t>
+          <t>v4.0-alpha.40</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>表征仪器与峰参数</t>
+          <t>制备实验记录文案</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>仪器其他方法支持名称列表；峰状态下拉移除，空白不生成峰结果，仅显式勾选记录未检出，历史数据保留。</t>
+          <t>删除重复提示，统一处理方式、外场和放置名称；明确设定温度与CSV时间原点，区分未选批次和批次未记录，按实际错误提示。仅调整界面文案，保留字段、校验规则和历史数据。</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
@@ -11281,17 +11175,17 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.37</t>
+          <t>v4.0-alpha.39</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>界面文案</t>
+          <t>表征仪器与峰参数</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>去掉重复选填标识和功能说明；统一表征仪器、数据处理记录、统计方式与检出限依据文案；保留单位与参照定义，补齐现有条件必填标识，不改变必填规则和历史数据。</t>
+          <t>仪器其他方法支持名称列表；峰状态下拉移除，空白不生成峰结果，仅显式勾选记录未检出，历史数据保留。</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -11303,17 +11197,17 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.34</t>
+          <t>v4.0-alpha.37</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>§5–6 流量名称与异常分类</t>
+          <t>界面文案</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>流量测量方式统一显示浮子流量计（转子流量计）；异常选项按类别排序，人工干预和人工停止并入计划变更，复用采取的处理与处理结果，不增加填写字段；旧记录原类型保留可追溯文字。</t>
+          <t>去掉重复选填标识和功能说明；统一表征仪器、数据处理记录、统计方式与检出限依据文案；保留单位与参照定义，补齐现有条件必填标识，不改变必填规则和历史数据。</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -11325,17 +11219,17 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.31</t>
+          <t>v4.0-alpha.34</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>§3 前驱体</t>
+          <t>§5–6 流量名称与异常分类</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>删除工艺作用及其他工艺作用说明；新保存和常规导出不含推断性作用标签，历史原文保留。</t>
+          <t>流量测量方式统一显示浮子流量计（转子流量计）；异常选项按类别排序，人工干预和人工停止并入计划变更，复用采取的处理与处理结果，不增加填写字段；旧记录原类型保留可追溯文字。</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -11347,17 +11241,17 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.33</t>
+          <t>v4.0-alpha.31</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>§5 气体、压力与降温</t>
+          <t>§3 前驱体</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>气体程序、压力和降温按用户确认修改：浮子流量计保留原始读数与单位；预混气引用商用气瓶组成及总流量；过程总时长明确全程供气边界；减压包含真空并新增加压；程序降温复用温度步骤，分段降温保存有序操作，不将设定速率当实测值</t>
+          <t>删除工艺作用及其他工艺作用说明；新保存和常规导出不含推断性作用标签，历史原文保留。</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -11369,17 +11263,17 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.32</t>
+          <t>v4.0-alpha.33</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>§5 实验前准备</t>
+          <t>§5 气体、压力与降温</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>气路置换改为气氛置换，按连续通气/抽空—回填展开；检漏移出可选操作，不新增检漏状态或确认；精简提示，旧记录保留可追溯语义。</t>
+          <t>气体程序、压力和降温按用户确认修改：浮子流量计保留原始读数与单位；预混气引用商用气瓶组成及总流量；过程总时长明确全程供气边界；减压包含真空并新增加压；程序降温复用温度步骤，分段降温保存有序操作，不将设定速率当实测值</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -11391,29 +11285,29 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>v4.0-alpha.32</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>§1 基本信息</t>
+          <t>§5 实验前准备</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>新增「合成方法」字段（顶层 CVD/PVD 选择器，必填，决定PVD模块是否出现）</t>
+          <t>气路置换改为气氛置换，按连续通气/抽空—回填展开；检漏移出可选操作，不新增检漏状态或确认；精简提示，旧记录保留可追溯语义。</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>新增(我补)</t>
+          <t>用户确认</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -11423,41 +11317,41 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>环境湿度 选填→推荐</t>
+          <t>新增「合成方法」字段（顶层 CVD/PVD 选择器，必填，决定PVD模块是否出现）</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>必填级</t>
+          <t>新增(我补)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>§1b 目标产物</t>
+          <t>§1 基本信息</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>对称性字段落实批注：空间群系→体相空间群，选项简化为空间群号+单层结构说明</t>
+          <t>环境湿度 选填→推荐</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>落实批注</t>
+          <t>必填级</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -11467,7 +11361,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>手性/扭转角/堆垛类型 明确放『备注』</t>
+          <t>对称性字段落实批注：空间群系→体相空间群，选项简化为空间群号+单层结构说明</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -11479,29 +11373,29 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>§2 设备</t>
+          <t>§1b 目标产物</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>坐标系：逐次填『原点+轴向』→ 全局固定、不可编辑的定义项（上游负/下游正）</t>
+          <t>手性/扭转角/堆垛类型 明确放『备注』</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>会议决定</t>
+          <t>落实批注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -11511,73 +11405,73 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>炉管/舟履历：自由文本 → 重置次数 + 重置后使用次数（两个结构化数字）</t>
+          <t>坐标系：逐次填『原点+轴向』→ 全局固定、不可编辑的定义项（上游负/下游正）</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>落实批注</t>
+          <t>会议决定</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>§3 前驱体</t>
+          <t>§2 设备</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>用量 推荐→必填（纳入R0）</t>
+          <t>炉管/舟履历：自由文本 → 重置次数 + 重置后使用次数（两个结构化数字）</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>必填级</t>
+          <t>落实批注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>§5 反应条件</t>
+          <t>§3 前驱体</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>删除『估算衬底真温』行，温度只留 设定温度 + 实测温度</t>
+          <t>用量 推荐→必填（纳入R0）</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>会议决定</t>
+          <t>必填级</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>§6 过程事件</t>
+          <t>§5 反应条件</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>事件类型 与 关联对象 合并为一个细化下拉</t>
+          <t>删除『估算衬底真温』行，温度只留 设定温度 + 实测温度</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -11589,17 +11483,17 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>§7 表征</t>
+          <t>§6 过程事件</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>产物表征拆成独立表、用编号与实验记录关联</t>
+          <t>事件类型 与 关联对象 合并为一个细化下拉</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -11611,56 +11505,56 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
+          <t>§7 表征</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>产物表征拆成独立表、用编号与实验记录关联</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>会议决定</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
           <t>回退保留v2</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>§3『舟/坩埚』仍长×宽×高（未拆高）</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>未改</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr"/>
-      <c r="B21" s="11" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr"/>
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>── 2026-07-06 表头定稿修订 ──</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr"/>
-      <c r="D21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>v3.1</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>§1b</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>掺杂/合金/异质结自由文本 → 新增『结构类型』下拉多选（本征/掺杂/合金/垂直·横向异质结）；明细走化学式标准写法</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>定稿修订</t>
-        </is>
-      </c>
+      <c r="C22" s="11" t="inlineStr"/>
+      <c r="D22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -11670,12 +11564,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>§6</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>模块定名『过程事件 Process Events』；『事件类型(含关联对象)』→『事件/部位』</t>
+          <t>掺杂/合金/异质结自由文本 → 新增『结构类型』下拉多选（本征/掺杂/合金/垂直·横向异质结）；明细走化学式标准写法</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -11692,51 +11586,51 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
+          <t>§6</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>模块定名『过程事件 Process Events』；『事件类型(含关联对象)』→『事件/部位』</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>定稿修订</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>v3.1</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
           <t>§1b</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>目标性能保持轻量自由文本（性能+衡量方法）；严格『数值绑测试方法』落在§7实测侧</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>定稿修订</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr"/>
-      <c r="B25" s="11" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr"/>
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>── 2026-07-06 v3.2 评审回炉（Fable 独立评审）──</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr"/>
-      <c r="D25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>v3.2</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>§7</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>新增『观察到的现象』客观多选词表——录入端仍不判成败，但保留光镜可判的客观负结果（失败炉次最小结构化痕迹）</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>评审回炉</t>
-        </is>
-      </c>
+      <c r="C26" s="11" t="inlineStr"/>
+      <c r="D26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -11746,12 +11640,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>§7</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>化学式升R0；新增『组成明细 components[]』结构化掺杂/异质结，替代字符串承载；结构类型保留为判别器</t>
+          <t>新增『观察到的现象』客观多选词表——录入端仍不判成败，但保留光镜可判的客观负结果（失败炉次最小结构化痕迹）</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -11768,12 +11662,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>§5</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>补回降温段参数（方式/开盖温度/速率），条件必填(降温段)——review头部隐变量勿再漏</t>
+          <t>化学式升R0；新增『组成明细 components[]』结构化掺杂/异质结，替代字符串承载；结构类型保留为判别器</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -11790,12 +11684,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>R0</t>
+          <t>§5</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>按合成方法条件化：前驱体用量→条件必填(固态源)，气态源/PVD不逼填mg</t>
+          <t>补回降温段参数（方式/开盖温度/速率），条件必填(降温段)——review头部隐变量勿再漏</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -11812,51 +11706,51 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
+          <t>R0</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>按合成方法条件化：前驱体用量→条件必填(固态源)，气态源/PVD不逼填mg</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>评审回炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>v3.2</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
           <t>数据模型</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>记录最小单元拍板：炉次=记录单元、样品=关联主键、表征外键指向样品</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>评审回炉</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr"/>
-      <c r="B31" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr"/>
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>── v3.2b 二轮复审再修（Fable 第二轮）──</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr"/>
-      <c r="D31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>v3.2b</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>§3</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>新增前驱体『相态(固/气/液)』字段，为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>复审再修</t>
-        </is>
-      </c>
+      <c r="C32" s="11" t="inlineStr"/>
+      <c r="D32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -11866,12 +11760,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>§3</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>组成明细升为权威+条件必填(结构类型≠本征)、化学式复合体系以其为准；数量拆『浓度(at%)』『层序』；结构类型改必填（复审N2/③）</t>
+          <t>新增前驱体『相态(固/气/液)』字段，为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -11888,12 +11782,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>§7/§10</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>加生命周期规则：炉次终态而无任何现象/表征行→『结果缺失』待办，堵『失败炉次零痕迹』（复审①）</t>
+          <t>组成明细升为权威+条件必填(结构类型≠本征)、化学式复合体系以其为准；数量拆『浓度(at%)』『层序』；结构类型改必填（复审N2/③）</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -11910,51 +11804,51 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
+          <t>§7/§10</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>加生命周期规则：炉次终态而无任何现象/表征行→『结果缺失』待办，堵『失败炉次零痕迹』（复审①）</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>复审再修</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>v3.2b</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
           <t>§8/§10</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>PVD 暂不纳入 v2.0 合规判定（占位），R0 不校验 PVD 炉次，待 profile 落地（复审N3）</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>复审再修</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr"/>
-      <c r="B36" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr"/>
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>── v3.3 一等实体补齐（复审⑤/must-fix4-5）──</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr"/>
-      <c r="D36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>v3.3</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>实体表</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>新增『一等实体字段表』sheet：MaterialLot/装置Setup/表征仪器三张权威字段表（补齐半个数据模型）；§10 合规纳入（PVD 仍排除）</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>实体补齐</t>
-        </is>
-      </c>
+      <c r="C37" s="11" t="inlineStr"/>
+      <c r="D37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -11964,12 +11858,12 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>§5/§8.1</t>
+          <t>实体表</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>AP/LP 冗余二选一敲定：保留合成方法 AP/LP，以校验规则强制与反应压力条件一致（不再悬置）</t>
+          <t>新增『一等实体字段表』sheet：MaterialLot/装置Setup/表征仪器三张权威字段表（补齐半个数据模型）；§10 合规纳入（PVD 仍排除）</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -11981,56 +11875,56 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>v3.3</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>§5/§8.1</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>AP/LP 冗余二选一敲定：保留合成方法 AP/LP，以校验规则强制与反应压力条件一致（不再悬置）</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>实体补齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
           <t>v3.3b</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>冻结前收尾</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Fable三轮B1-B4：MaterialLot/Setup 加『版本号』(锁版使能)；§2属性=Setup快照【只读投影】声明；用量含液态(非气态条件、µL)；气瓶纯度与base分工注</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>冻结前收尾</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr"/>
-      <c r="B40" s="11" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr"/>
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>── 2026-07-07 导师书面评审回改（v3.4，FSS Re-副本 标黄9处+红字2处）──</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr"/>
-      <c r="D40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>v3.4</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>§1b</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>目标性能：可选项列补示例引导『光学属性-高荧光量子效率 / 电属性-高迁移率』（导师标黄E18）</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>导师评审</t>
-        </is>
-      </c>
+      <c r="C41" s="11" t="inlineStr"/>
+      <c r="D41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -12040,12 +11934,12 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>§3</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>新增『外观描述』字段：使用时性状，溯源判断潮解/变质；推荐(固态源)；放每炉次而非MaterialLot（导师批注K35）</t>
+          <t>目标性能：可选项列补示例引导『光学属性-高荧光量子效率 / 电属性-高迁移率』（导师标黄E18）</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -12062,12 +11956,12 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>§5</t>
+          <t>§3</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>外场参数 选填→条件必填(Setup有外场)；判别位=Setup.外场装置≠无，机器可校验（导师批注K65）</t>
+          <t>新增『外观描述』字段：使用时性状，溯源判断潮解/变质；推荐(固态源)；放每炉次而非MaterialLot（导师批注K35）</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -12084,12 +11978,12 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>§7</t>
+          <t>§5</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>检出相/多型→检出相/多型/堆垛，增记堆垛类型；示例加『AB堆垛』（导师红字B76）</t>
+          <t>外场参数 选填→条件必填(Setup有外场)；判别位=Setup.外场装置≠无，机器可校验（导师批注K65）</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -12111,7 +12005,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>关键谱学指标：PL补峰宽；『SEM占比』改名『SEM覆盖率(视场内材料面积占比,%)』并给定义（导师红字C79/问询K79）</t>
+          <t>检出相/多型→检出相/多型/堆垛，增记堆垛类型；示例加『AB堆垛』（导师红字B76）</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -12128,51 +12022,51 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
+          <t>§7</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>关键谱学指标：PL补峰宽；『SEM占比』改名『SEM覆盖率(视场内材料面积占比,%)』并给定义（导师红字C79/问询K79）</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>导师评审</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>v3.4</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
           <t>全表</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>表头下加必填级别图例行；必填/条件必填字体加粗着色（导师提醒B93）</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>导师评审</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr"/>
-      <c r="B47" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr"/>
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>── review→v3 回退存档（每条给去向）──</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr"/>
-      <c r="D47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>存档</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>湿度</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>回退备案</t>
-        </is>
-      </c>
+      <c r="C48" s="11" t="inlineStr"/>
+      <c r="D48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -12182,12 +12076,12 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>装置加热区长/泵型号/MFC配置/PID</t>
+          <t>湿度</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -12204,12 +12098,12 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>炉管履历</t>
+          <t>装置加热区长/泵型号/MFC配置/PID</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -12226,12 +12120,12 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>时序四元组</t>
+          <t>炉管履历</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
+          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -12243,44 +12137,44 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>v3.5a</t>
+          <t>存档</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>时序四元组</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>结构类型由下拉多选纠正为单选判别器；选择值驱动填写提示及组成明细显隐/条件必填</t>
+          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复</t>
+          <t>回退备案</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>v3.6</t>
+          <t>v3.5a</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>全表/实体</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>科学契约加固：结构类型与组成明细纳入R0；补衬底批次引用、具名几何、其他气体名称、sccm参考状态及字段级数值边界</t>
+          <t>结构类型由下拉多选纠正为单选判别器；选择值驱动填写提示及组成明细显隐/条件必填</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>全库审查修复</t>
+          <t>用户走查修复</t>
         </is>
       </c>
     </row>
@@ -12292,12 +12186,12 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>§6–§7</t>
+          <t>全表/实体</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>过程事件改为带UTC offset的绝对日期时间；实测层数、覆盖率、畴尺寸、成核密度拆为独立量，关键谱学指标改为带单位的结构化数组</t>
+          <t>科学契约加固：结构类型与组成明细纳入R0；补衬底批次引用、具名几何、其他气体名称、sccm参考状态及字段级数值边界</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -12309,22 +12203,22 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>v3.7</t>
+          <t>v3.6</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>§1–§4</t>
+          <t>§6–§7</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>按2026-07-24导师走查：温湿度与预检、目标形态升必填；删除粒子占位；批次引用升必填；前驱体与衬底处理改具名有序数组；衬底晶向、粗糙度、尺寸与倾角结构化</t>
+          <t>过程事件改为带UTC offset的绝对日期时间；实测层数、覆盖率、畴尺寸、成核密度拆为独立量，关键谱学指标改为带单位的结构化数组</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>导师走查整改</t>
+          <t>全库审查修复</t>
         </is>
       </c>
     </row>
@@ -12336,12 +12230,12 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>§5–§6</t>
+          <t>§1–§4</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>11阶段收敛为预处理、反应条件、具名其他记录；温度程序、实测文件、多气体时序、时长、降温、实际外场与事件附件全部改为可校验结构</t>
+          <t>按2026-07-24导师走查：温湿度与预检、目标形态升必填；删除粒子占位；批次引用升必填；前驱体与衬底处理改具名有序数组；衬底晶向、粗糙度、尺寸与倾角结构化</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -12358,12 +12252,12 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>实体</t>
+          <t>§5–§6</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Setup删除sccm参考值、加热区长度、泵、MFC和PID，坐标系固定，新增温度传感器；炉管材质与形状拆入具名对象；MaterialLot新增瓶身或包装标签附件</t>
+          <t>11阶段收敛为预处理、反应条件、具名其他记录；温度程序、实测文件、多气体时序、时长、降温、实际外场与事件附件全部改为可校验结构</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -12375,22 +12269,22 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>v3.8</t>
+          <t>v3.7</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>§1–§5</t>
+          <t>实体</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复：炉管和各舟履历改为每炉手填；炉管尺寸按圆/方/矩形条件展开；前驱体源温改为可选位置温度及依据；外场按等离子体/光/电展开明确参数</t>
+          <t>Setup删除sccm参考值、加热区长度、泵、MFC和PID，坐标系固定，新增温度传感器；炉管材质与形状拆入具名对象；MaterialLot新增瓶身或包装标签附件</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复</t>
+          <t>导师走查整改</t>
         </is>
       </c>
     </row>
@@ -12402,12 +12296,12 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>§4/实体</t>
+          <t>§1–§5</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>衬底稳定规格归MaterialLot：晶向抛光、偏切角与方向、氧化层及标称粗糙度由批次冻结带出；本片尺寸、放置、预处理和位置留在炉次；气瓶等级改为供应商原始标签选填</t>
+          <t>用户走查修复：炉管和各舟履历改为每炉手填；炉管尺寸按圆/方/矩形条件展开；前驱体源温改为可选位置温度及依据；外场按等离子体/光/电展开明确参数</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -12424,12 +12318,12 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>术语/表征</t>
+          <t>§4/实体</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>装置与实际外场统一显示“等离子体”；体相空间群改用内置230项检索；“表征方法”与仪器引用分开，固定配置只记录稳定硬件能力</t>
+          <t>衬底稳定规格归MaterialLot：晶向抛光、偏切角与方向、氧化层及标称粗糙度由批次冻结带出；本片尺寸、放置、预处理和位置留在炉次；气瓶等级改为供应商原始标签选填</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -12441,127 +12335,127 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>v3.9</t>
+          <t>v3.8</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>§1/§4/实体</t>
+          <t>术语/表征</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>按会议逐字稿删除悬浮粒子浓度；粗糙度允许明确记录供应商未提供；旧批次缺稳定字段时禁止在实验回填；区分来料尺寸与本次实际切片尺寸</t>
+          <t>装置与实际外场统一显示“等离子体”；体相空间群改用内置230项检索；“表征方法”与仪器引用分开，固定配置只记录稳定硬件能力</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>用户走查修复</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>v3.10</t>
+          <t>v3.9</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>§3/§4/实体</t>
+          <t>§1/§4/实体</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>补齐温区距离参照、条件不适用后端约束与旧等离子别名；粒径/形态按物料类别展开；晶向抛光和偏切以有规格、未提供、不适用三态记录，禁止用伪值或0代替未知</t>
+          <t>按会议逐字稿删除悬浮粒子浓度；粗糙度允许明确记录供应商未提供；旧批次缺稳定字段时禁止在实验回填；区分来料尺寸与本次实际切片尺寸</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25终审收口</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>v3.11</t>
+          <t>v3.10</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>§6/实体</t>
+          <t>§3/§4/实体</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明始终可选填写、终止原因=其他时升级为必填；仪器字段改称“适用表征方法”；补明热电偶距离与前驱体温区、炉管截面与尺寸的联动必填规则</t>
+          <t>补齐温区距离参照、条件不适用后端约束与旧等离子别名；粒径/形态按物料类别展开；晶向抛光和偏切以有规格、未提供、不适用三态记录，禁止用伪值或0代替未知</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25逐字稿与语义终审</t>
+          <t>2026-07-25终审收口</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>v3.12</t>
+          <t>v3.11</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>§1–§5/实体</t>
+          <t>§6/实体</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>制备终版整改：新记录固定CVD顶层方法；目标产物按掺杂、合金、材料层和区域填写；Setup逐温区只填传感器类型与温度测量误差；前驱体角色与样片标记必填；压力类别和值成对；反应删除伪循环派生</t>
+          <t>事件具体说明始终可选填写、终止原因=其他时升级为必填；仪器字段改称“适用表征方法”；补明热电偶距离与前驱体温区、炉管截面与尺寸的联动必填规则</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>2026-07-27终版整改</t>
+          <t>2026-07-25逐字稿与语义终审</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>v3.13</t>
+          <t>v3.12</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>§1–§5/实体</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>目标产物复核：化学式示例按结构类型变化；删除“普通数字”用户文案；掺杂区只显示掺杂元素；空间群按化学式给出经核对的常见体相候选并保留230项搜索；异质结构逐层或逐区域填写空间群</t>
+          <t>制备终版整改：新记录固定CVD顶层方法；目标产物按掺杂、合金、材料层和区域填写；Setup逐温区只填传感器类型与温度测量误差；前驱体角色与样片标记必填；压力类别和值成对；反应删除伪循环派生</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
+          <t>2026-07-27终版整改</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>v3.15</t>
+          <t>v3.13</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>实体/设备</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>温度传感器由热电偶分型号改为按测温原理选择类别：热电偶、热电阻（RTD）、红外测温仪、光纤温度传感器、热敏电阻、其他</t>
+          <t>目标产物复核：化学式示例按结构类型变化；删除“普通数字”用户文案；掺杂区只显示掺杂元素；空间群按化学式给出经核对的常见体相候选并保留230项搜索；异质结构逐层或逐区域填写空间群</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -12573,7 +12467,7 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>v3.16</t>
+          <t>v3.15</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -12583,7 +12477,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Setup拆分制造商或品牌与型号，增加装置来源；实验室装置编号保持唯一但允许管理员通过新版本纠错；温区标称测温精度改为选填</t>
+          <t>温度传感器由热电偶分型号改为按测温原理选择类别：热电偶、热电阻（RTD）、红外测温仪、光纤温度传感器、热敏电阻、其他</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -12595,7 +12489,7 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>v3.17</t>
+          <t>v3.16</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -12605,7 +12499,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>装置来源改为必填；商业设备显示制造商与型号，实验室自制显示设计或建造单位与内部型号，改造设备显示原设备制造商、原设备型号与改造内容；公共技术字段不变</t>
+          <t>Setup拆分制造商或品牌与型号，增加装置来源；实验室装置编号保持唯一但允许管理员通过新版本纠错；温区标称测温精度改为选填</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -12617,105 +12511,105 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>v3.18</t>
+          <t>v3.17</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>§3/实体</t>
+          <t>实体/设备</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>前驱体先选本次使用形态再筛选批次；删除炉次中重复的名称化学式和CAS；用途、使用量、使用前状态、处理步骤按实际语义收敛；非气态按舟、坩埚、衬底表面或其他容器展开容器尺寸、履历与炉内位置</t>
+          <t>装置来源改为必填；商业设备显示制造商与型号，实验室自制显示设计或建造单位与内部型号，改造设备显示原设备制造商、原设备型号与改造内容；公共技术字段不变</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28前驱体首版复核</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>v4.0-rc.1</t>
+          <t>v3.18</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>科学对象/实体/结果</t>
+          <t>§3/实体</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>引入正交TargetSpec、物理SourceLoad、统一ProcessTimeline、不可变RunRevision、样品转换图及MeasurementRun→AnalysisRun→PropertyValue/MaterialAssertion溯源链；物料、装置部件和仪器能力补齐归一化字段；PVD不进入发布契约</t>
+          <t>前驱体先选本次使用形态再筛选批次；删除炉次中重复的名称化学式和CAS；用途、使用量、使用前状态、处理步骤按实际语义收敛；非气态按舟、坩埚、衬底表面或其他容器展开容器尺寸、履历与炉内位置</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查整改</t>
+          <t>2026-07-28前驱体首版复核</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.2</t>
+          <t>v4.0-rc.1</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>科学完整性复核</t>
+          <t>科学对象/实体/结果</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>关闭旧结果写入与手工派生入口；收紧审阅和转化权限；修正跨炉次转化溯源、过程单位归一化、不可变修订导出及数据集查询语义；冻结装料容器、测量时校准和样品—修订关联快照；状态降为内部验证</t>
+          <t>引入正交TargetSpec、物理SourceLoad、统一ProcessTimeline、不可变RunRevision、样品转换图及MeasurementRun→AnalysisRun→PropertyValue/MaterialAssertion溯源链；物料、装置部件和仪器能力补齐归一化字段；PVD不进入发布契约</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29二次复核整改</t>
+          <t>2026-07-28深度审查整改</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.3</t>
+          <t>v4.0-alpha.2</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>§4 衬底</t>
+          <t>科学完整性复核</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>产品简化界面增加本片轴向位置与备注；轴向位置为普通用户提交前必填，不暴露三维坐标</t>
+          <t>关闭旧结果写入与手工派生入口；收紧审阅和转化权限；修正跨炉次转化溯源、过程单位归一化、不可变修订导出及数据集查询语义；冻结装料容器、测量时校准和样品—修订关联快照；状态降为内部验证</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>2026-07-30产品简化</t>
+          <t>2026-07-29二次复核整改</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.4</t>
+          <t>v4.0-alpha.3</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>§7 表征</t>
+          <t>§4 衬底</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>表征方法拆分最小必填与更多测量参数，固定各方法常用结果项，并增加“其他”方法说明；科学对象仍由后端统一落库</t>
+          <t>产品简化界面增加本片轴向位置与备注；轴向位置为普通用户提交前必填，不暴露三维坐标</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -12727,29 +12621,29 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.5</t>
+          <t>v4.0-alpha.4</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>实体/物料批次</t>
+          <t>§7 表征</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>CAS号与数值纯度改为有来源才选填；删除同义名、标识符、商业规格JSON、纯度基准/来源及D50四字段；供应商规格或等级按标签原文照录</t>
+          <t>表征方法拆分最小必填与更多测量参数，固定各方法常用结果项，并增加“其他”方法说明；科学对象仍由后端统一落库</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02供应商资料复核与减负</t>
+          <t>2026-07-30产品简化</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.6</t>
+          <t>v4.0-alpha.5</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -12759,19 +12653,19 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>物料表单文案正式化：常规字段说明改为简短占位示例，仅为纯度及衬底规格等易误录字段保留必要说明；统一字段名称、中文标点和中英文术语</t>
+          <t>CAS号与数值纯度改为有来源才选填；删除同义名、标识符、商业规格JSON、纯度基准/来源及D50四字段；供应商规格或等级按标签原文照录</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02用户界面复核</t>
+          <t>2026-08-02供应商资料复核与减负</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.7</t>
+          <t>v4.0-alpha.6</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -12781,19 +12675,19 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>化学式复用目标产物输入控件并提示元素与语法；货号与批号直接对应包装上的 Cat./Product No. 和 Lot/Batch No.，说明两者的产品与实物批次分工</t>
+          <t>物料表单文案正式化：常规字段说明改为简短占位示例，仅为纯度及衬底规格等易误录字段保留必要说明；统一字段名称、中文标点和中英文术语</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06用户界面复核</t>
+          <t>2026-08-02用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.8</t>
+          <t>v4.0-alpha.7</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -12803,7 +12697,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>删除化学式格式说明，只保留示例与即时元素/语法反馈</t>
+          <t>化学式复用目标产物输入控件并提示元素与语法；货号与批号直接对应包装上的 Cat./Product No. 和 Lot/Batch No.，说明两者的产品与实物批次分工</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
@@ -12815,7 +12709,7 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.9</t>
+          <t>v4.0-alpha.8</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -12825,7 +12719,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>供应商“其他”改为明确的新增供应商与名称输入；供应商规格或等级改为产品等级（标签原文），说明资料未标注时留空</t>
+          <t>删除化学式格式说明，只保留示例与即时元素/语法反馈</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -12837,17 +12731,17 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.12</t>
+          <t>v4.0-alpha.9</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>§5 生长条件</t>
+          <t>实体/物料批次</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>统一实验时间零点与有效生长窗口；补齐气体批次、流量来源、绝对压力、受控降温速率、实际外场参数和多条异常事件，并自动覆盖生长后的实验过程</t>
+          <t>供应商“其他”改为明确的新增供应商与名称输入；供应商规格或等级改为产品等级（标签原文），说明资料未标注时留空</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
@@ -12859,7 +12753,7 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.13</t>
+          <t>v4.0-alpha.12</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -12869,19 +12763,19 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>将容易误解为管理制度的“压力制度/压力体系”统一改为“反应压力条件”，数据字段与校验规则不变</t>
+          <t>统一实验时间零点与有效生长窗口；补齐气体批次、流量来源、绝对压力、受控降温速率、实际外场参数和多条异常事件，并自动覆盖生长后的实验过程</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户界面复核</t>
+          <t>2026-08-06用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.14</t>
+          <t>v4.0-alpha.13</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
@@ -12891,7 +12785,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>改为按实际操作和持续时间录入，系统自动生成系统准备、升温与预处理、反应、反应后处理和降温时间轴；气体优先选择使用阶段，仅自定义时填写起止时间</t>
+          <t>将容易误解为管理制度的“压力制度/压力体系”统一改为“反应压力条件”，数据字段与校验规则不变</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -12903,7 +12797,7 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.15</t>
+          <t>v4.0-alpha.14</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
@@ -12913,51 +12807,51 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>删除缺乏统一文献定义且无法直接观测的反应计时起点、反应开始前用时、反应时长及重复的反应后处理；实际过程由温度步骤、气体时段、系统准备、压力与降温记录</t>
+          <t>改为按实际操作和持续时间录入，系统自动生成系统准备、升温与预处理、反应、反应后处理和降温时间轴；气体优先选择使用阶段，仅自定义时填写起止时间</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户界面复核与原始论文核对</t>
+          <t>2026-08-07用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.16</t>
+          <t>v4.0-alpha.15</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>§3 前驱体装载</t>
+          <t>§5 生长条件</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>删除偏TMDC的必填单选作用，改为选填多选工艺作用；一次旋涂支持多段转速；衬底表面装载关联稳定衬底片；旋涂物料可成对记录溶液浓度与受控单位</t>
+          <t>删除缺乏统一文献定义且无法直接观测的反应计时起点、反应开始前用时、反应时长及重复的反应后处理；实际过程由温度步骤、气体时段、系统准备、压力与降温记录</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-12师兄真实试填反馈</t>
+          <t>2026-08-07用户界面复核与原始论文核对</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.17</t>
+          <t>v4.0-alpha.16</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>§5 生长条件</t>
+          <t>§3 前驱体装载</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>气体词表增加二氧化碳，启动混合气与置换气源契约收口</t>
+          <t>删除偏TMDC的必填单选作用，改为选填多选工艺作用；一次旋涂支持多段转速；衬底表面装载关联稳定衬底片；旋涂物料可成对记录溶液浓度与受控单位</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -12969,240 +12863,262 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.18</t>
+          <t>v4.0-alpha.17</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>§1–§6科学修订契约·MaterialLot气瓶</t>
+          <t>§5 生长条件</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>气瓶版本结构化登记纯气或预混组成；置换引用实际气瓶版本；基本信息、目标材料、前驱体、过程事件与生长条件的发布字段改用当前不可变修订payload真实key和schema_path，旧扁平字段仅历史兼容</t>
+          <t>气体词表增加二氧化碳，启动混合气与置换气源契约收口</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13全链路契约复核</t>
+          <t>2026-08-12师兄真实试填反馈</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.19</t>
+          <t>v4.0-alpha.18</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>表征科学属性</t>
+          <t>§1–§6科学修订契约·MaterialLot气瓶</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>PropertyValue 补齐数值/文本表示类型与物理范围，并统一后端和前端的单一源校验</t>
+          <t>气瓶版本结构化登记纯气或预混组成；置换引用实际气瓶版本；基本信息、目标材料、前驱体、过程事件与生长条件的发布字段改用当前不可变修订payload真实key和schema_path，旧扁平字段仅历史兼容</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31表征全链路独立审查</t>
+          <t>2026-08-13全链路契约复核</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.20</t>
+          <t>v4.0-alpha.19</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>实体/物料批次</t>
+          <t>表征科学属性</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>云母衬底增加白云母、金云母和氟金云母类型选择，并由系统生成理想化学式，避免选择材料后在表单顶部突然出现手填化学式</t>
+          <t>PropertyValue 补齐数值/文本表示类型与物理范围，并统一后端和前端的单一源校验</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01用户试填反馈</t>
+          <t>2026-08-31表征全链路独立审查</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.21</t>
+          <t>v4.0-alpha.20</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>实体/制备/样品与表征流程</t>
+          <t>实体/物料批次</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>仪器能力改为勾选、日期改为日期控件、装置使用身份标签、异常改为显式确认、表征入口保留样品上下文，并在编辑后清除旧校验错误</t>
+          <t>云母衬底增加白云母、金云母和氟金云母类型选择，并由系统生成理想化学式，避免选择材料后在表单顶部突然出现手填化学式</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01全表单交互复核</t>
+          <t>2026-09-01用户试填反馈</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.22</t>
+          <t>v4.0-alpha.21</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>§3/§5 生长条件与装置履历</t>
+          <t>实体/制备/样品与表征流程</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>生长条件按实验前准备、温度、气体、反应压力、降温和异常分区；温度步骤移除待判断与初始温度伪时长；异常改为勾选框，并缩短温区和炉管履历文案</t>
+          <t>仪器能力改为勾选、日期改为日期控件、装置使用身份标签、异常改为显式确认、表征入口保留样品上下文，并在编辑后清除旧校验错误</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户界面复核</t>
+          <t>2026-09-01全表单交互复核</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.23</t>
+          <t>v4.0-alpha.22</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>§1b/§3/§4/§5 制备记录填写体验</t>
+          <t>§3/§5 生长条件与装置履历</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>缩短晶体结构、实验目标、相对测温点位置、使用前处理、衬底处理和压力条件文案；明确必填空状态与提交检查，并减少气体首段录入步骤</t>
+          <t>生长条件按实验前准备、温度、气体、反应压力、降温和异常分区；温度步骤移除待判断与初始温度伪时长；异常改为勾选框，并缩短温区和炉管履历文案</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户全流程复核</t>
+          <t>2026-09-02用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.24</t>
+          <t>v4.0-alpha.23</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>§5 实验前准备</t>
+          <t>§1b/§3/§4/§5 制备记录填写体验</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>抽真空优先记录终点绝对压力；有压力读数时持续时间改为选填，无压力读数时持续时间必填</t>
+          <t>缩短晶体结构、实验目标、相对测温点位置、使用前处理、衬底处理和压力条件文案；明确必填空状态与提交检查，并减少气体首段录入步骤</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户实验前准备复核</t>
+          <t>2026-09-02用户全流程复核</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.26</t>
+          <t>v4.0-alpha.24</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>§1b 目标材料</t>
+          <t>§5 实验前准备</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>单一材料改为本征材料，原子层数改为材料层数；删除无法预知的目标覆盖状态和语义混淆的目标生长取向，以目标产物形态和条件平面轮廓表达预期形态</t>
+          <t>抽真空优先记录终点绝对压力；有压力读数时持续时间改为选填，无压力读数时持续时间必填</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户目标材料复核</t>
+          <t>2026-09-02用户实验前准备复核</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.27</t>
+          <t>v4.0-alpha.26</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>装置与衬底</t>
+          <t>§1b 目标材料</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>外场能力增加具名其他；衬底批号改为按标签提供情况条件填写并补生产日期；衬底处理合并为可展开溶剂清洗，并以紫外/臭氧处理替代笼统亲水处理</t>
+          <t>单一材料改为本征材料，原子层数改为材料层数；删除无法预知的目标覆盖状态和语义混淆的目标生长取向，以目标产物形态和条件平面轮廓表达预期形态</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户装置与衬底复核</t>
+          <t>2026-09-03用户目标材料复核</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.35</t>
+          <t>v4.0-alpha.27</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>表征客观测量</t>
+          <t>装置与衬底</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>新表征不分区域、不录入材料判定；谱峰按编号记录峰位、半高全宽和强度，区分未分析与未检出；AFM、电子显微镜、元素定量按方法与模式显示，历史判定不再自动汇总成整片样品结论</t>
+          <t>外场能力增加具名其他；衬底批号改为按标签提供情况条件填写并补生产日期；衬底处理合并为可展开溶剂清洗，并以紫外/臭氧处理替代笼统亲水处理</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户表征复核</t>
+          <t>2026-09-03用户装置与衬底复核</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.35</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>表征客观测量</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>新表征不分区域、不录入材料判定；谱峰按编号记录峰位、半高全宽和强度，区分未分析与未检出；AFM、电子显微镜、元素定量按方法与模式显示，历史判定不再自动汇总成整片样品结论</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-04用户表征复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>最小可复现核心(27项，含条件必填)</t>
         </is>
       </c>
-      <c r="C95" s="11" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>过程R0以温度/气体/压力通道和降温条件为准；不再要求人工划分反应阶段或反应时长</t>
         </is>
       </c>
-      <c r="D95" s="11" t="inlineStr">
+      <c r="D96" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6574,7 +6574,7 @@
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>§7 旧扁平结果字段（未发布；由 MeasurementRun → AnalysisRun → PropertyValue / MaterialAssertion 替代）</t>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
         </is>
       </c>
       <c r="B119" s="8" t="n"/>
@@ -6591,27 +6591,27 @@
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>表征方法</t>
+          <t>靶材（批次）</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>本次使用的表征手段；仪器通过独立仪器引用选择</t>
+          <t>靶材化学身份 + 批次</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>引用</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
+          <t>批次库</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
@@ -6626,40 +6626,36 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>MoS₂ 靶-T01</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J120" s="15" t="inlineStr">
-        <is>
-          <t>★v3：长一批表征一批，拆成独立表编号关联；不要在此字段重复写仪器</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr"/>
       <c r="K120" s="11" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>测试条件</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>该表征的测试参数</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>文本/自由</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -6669,7 +6665,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
@@ -6679,50 +6675,50 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>激光532 nm；功率1 mW；物镜100×</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J121" s="11" t="inlineStr">
-        <is>
-          <t>随仪器导出</t>
-        </is>
-      </c>
-      <c r="K121" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="inlineStr"/>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>表征</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>原始数据</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>上传原始文件（留校验和）</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>附件</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
@@ -6732,12 +6728,12 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>raman.txt</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr"/>
@@ -6746,32 +6742,32 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>观察到的现象</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>光镜可判的客观现象（非成败判断）</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>下拉+多选</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>无生长/不连续覆盖/厚层区域/可见颗粒沾污/衬底破损/变色/其他</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
@@ -6781,7 +6777,7 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>不连续覆盖</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -6789,32 +6785,32 @@
           <t>复审</t>
         </is>
       </c>
-      <c r="J123" s="15" t="inlineStr">
-        <is>
-          <t>★失败炉次最小痕迹；终态无任何结果→『结果缺失』待办(标准§7/§10)</t>
-        </is>
-      </c>
-      <c r="K123" s="11" t="inlineStr"/>
+      <c r="J123" s="11" t="inlineStr"/>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>检出相、多型与堆垛</t>
+          <t>预溅射与挡板时序</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>测到的物相/多型/堆垛类型</t>
+          <t>预溅射时长、挡板开合时序</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
@@ -6824,7 +6820,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>min·s</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
@@ -6834,35 +6830,35 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>2H-MoS₂；AB堆垛</t>
+          <t>预溅 5 min</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J124" s="15" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(B76红字)：增记堆垛类型（可判粒度待与俊杰确认，或改下拉）；最小结构化结果</t>
-        </is>
-      </c>
-      <c r="K124" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J124" s="11" t="inlineStr"/>
+      <c r="K124" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>实测产物</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>实测层数</t>
+          <t>沉积速率</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>由表征方法判定的层数</t>
+          <t>速率（QCM 等）</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
@@ -6877,7 +6873,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>层</t>
+          <t>nm/s</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
@@ -6887,577 +6883,25 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J125" s="11" t="inlineStr">
-        <is>
-          <t>历史字段，保留原记录；新表征不录入层数判定，也不将未检出写成层数 0</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr"/>
       <c r="K125" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0,"type":"integer"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="11" t="inlineStr">
-        <is>
-          <t>实测产物</t>
-        </is>
-      </c>
-      <c r="B126" s="11" t="inlineStr">
-        <is>
-          <t>覆盖率</t>
-        </is>
-      </c>
-      <c r="C126" s="11" t="inlineStr">
-        <is>
-          <t>明确视场或统计区域内材料面积占比</t>
-        </is>
-      </c>
-      <c r="D126" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E126" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F126" s="11" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G126" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H126" s="11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I126" s="11" t="inlineStr">
-        <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J126" s="11" t="inlineStr">
-        <is>
-          <t>量化口径仍须随表征条件记录</t>
-        </is>
-      </c>
-      <c r="K126" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"le":100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t>实测产物</t>
-        </is>
-      </c>
-      <c r="B127" s="11" t="inlineStr">
-        <is>
-          <t>畴尺寸</t>
-        </is>
-      </c>
-      <c r="C127" s="11" t="inlineStr">
-        <is>
-          <t>由指定统计方法得到的代表性畴尺寸</t>
-        </is>
-      </c>
-      <c r="D127" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F127" s="11" t="inlineStr">
-        <is>
-          <t>μm</t>
-        </is>
-      </c>
-      <c r="G127" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H127" s="11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I127" s="11" t="inlineStr">
-        <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J127" s="11" t="inlineStr"/>
-      <c r="K127" s="11" t="inlineStr">
-        <is>
           <t>{"gt":0}</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>实测产物</t>
-        </is>
-      </c>
-      <c r="B128" s="11" t="inlineStr">
-        <is>
-          <t>成核密度</t>
-        </is>
-      </c>
-      <c r="C128" s="11" t="inlineStr">
-        <is>
-          <t>指定统计区域内单位面积成核点数量</t>
-        </is>
-      </c>
-      <c r="D128" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E128" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F128" s="11" t="inlineStr">
-        <is>
-          <t>cm⁻²</t>
-        </is>
-      </c>
-      <c r="G128" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H128" s="11" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="I128" s="11" t="inlineStr">
-        <is>
-          <t>复审/科学契约审查</t>
-        </is>
-      </c>
-      <c r="J128" s="11" t="inlineStr"/>
-      <c r="K128" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>实测产物</t>
-        </is>
-      </c>
-      <c r="B129" s="11" t="inlineStr">
-        <is>
-          <t>关键谱学指标</t>
-        </is>
-      </c>
-      <c r="C129" s="11" t="inlineStr">
-        <is>
-          <t>Raman峰位/峰宽/峰面积；PL峰位/峰宽；AFM厚度/粗糙度；SEM覆盖率(视场内材料面积占比,%)/尺寸</t>
-        </is>
-      </c>
-      <c r="D129" s="11" t="inlineStr">
-        <is>
-          <t>结构化指标数组</t>
-        </is>
-      </c>
-      <c r="E129" s="11" t="inlineStr">
-        <is>
-          <t>每条:{metric_code,value,unit}</t>
-        </is>
-      </c>
-      <c r="F129" s="11" t="inlineStr">
-        <is>
-          <t>按指标</t>
-        </is>
-      </c>
-      <c r="G129" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H129" s="11" t="inlineStr">
-        <is>
-          <t>[{"metric_code":"raman_e2g_peak","value":384.2,"unit":"cm-1"}]</t>
-        </is>
-      </c>
-      <c r="I129" s="11" t="inlineStr">
-        <is>
-          <t>复审/导师</t>
-        </is>
-      </c>
-      <c r="J129" s="15" t="inlineStr">
-        <is>
-          <t>★v3.4导师评审(C79红字/K79)：PL补峰宽；『SEM占比』改名『SEM覆盖率』并给定义；随技术选填</t>
-        </is>
-      </c>
-      <c r="K129" s="11" t="inlineStr">
-        <is>
-          <t>{"finite_value":true,"item_required":["metric_code","value","unit"]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B130" s="8" t="n"/>
-      <c r="C130" s="8" t="n"/>
-      <c r="D130" s="8" t="n"/>
-      <c r="E130" s="8" t="n"/>
-      <c r="F130" s="8" t="n"/>
-      <c r="G130" s="8" t="n"/>
-      <c r="H130" s="8" t="n"/>
-      <c r="I130" s="8" t="n"/>
-      <c r="J130" s="8" t="n"/>
-      <c r="K130" s="8" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B131" s="11" t="inlineStr">
-        <is>
-          <t>靶材（批次）</t>
-        </is>
-      </c>
-      <c r="C131" s="11" t="inlineStr">
-        <is>
-          <t>靶材化学身份 + 批次</t>
-        </is>
-      </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>批次库</t>
-        </is>
-      </c>
-      <c r="F131" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G131" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H131" s="11" t="inlineStr">
-        <is>
-          <t>MoS₂ 靶-T01</t>
-        </is>
-      </c>
-      <c r="I131" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J131" s="11" t="inlineStr"/>
-      <c r="K131" s="11" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B132" s="11" t="inlineStr">
-        <is>
-          <t>靶基距</t>
-        </is>
-      </c>
-      <c r="C132" s="11" t="inlineStr">
-        <is>
-          <t>靶到衬底距离</t>
-        </is>
-      </c>
-      <c r="D132" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E132" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F132" s="11" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G132" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H132" s="11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I132" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J132" s="11" t="inlineStr"/>
-      <c r="K132" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B133" s="11" t="inlineStr">
-        <is>
-          <t>功率与偏压</t>
-        </is>
-      </c>
-      <c r="C133" s="11" t="inlineStr">
-        <is>
-          <t>DC/RF 功率、基底偏压</t>
-        </is>
-      </c>
-      <c r="D133" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E133" s="11" t="inlineStr">
-        <is>
-          <t>DC/RF</t>
-        </is>
-      </c>
-      <c r="F133" s="11" t="inlineStr">
-        <is>
-          <t>W·V</t>
-        </is>
-      </c>
-      <c r="G133" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H133" s="11" t="inlineStr">
-        <is>
-          <t>RF 150W；偏压 -50V</t>
-        </is>
-      </c>
-      <c r="I133" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J133" s="11" t="inlineStr"/>
-      <c r="K133" s="11" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t>等离子体气氛与工作气压</t>
-        </is>
-      </c>
-      <c r="C134" s="11" t="inlineStr">
-        <is>
-          <t>溅射气体与气压</t>
-        </is>
-      </c>
-      <c r="D134" s="11" t="inlineStr">
-        <is>
-          <t>下拉+数值</t>
-        </is>
-      </c>
-      <c r="E134" s="11" t="inlineStr">
-        <is>
-          <t>Ar / Ar+N₂…</t>
-        </is>
-      </c>
-      <c r="F134" s="11" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G134" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H134" s="11" t="inlineStr">
-        <is>
-          <t>Ar，0.5 Pa</t>
-        </is>
-      </c>
-      <c r="I134" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J134" s="11" t="inlineStr"/>
-      <c r="K134" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B135" s="11" t="inlineStr">
-        <is>
-          <t>预溅射与挡板时序</t>
-        </is>
-      </c>
-      <c r="C135" s="11" t="inlineStr">
-        <is>
-          <t>预溅射时长、挡板开合时序</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F135" s="11" t="inlineStr">
-        <is>
-          <t>min·s</t>
-        </is>
-      </c>
-      <c r="G135" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H135" s="11" t="inlineStr">
-        <is>
-          <t>预溅 5 min</t>
-        </is>
-      </c>
-      <c r="I135" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J135" s="11" t="inlineStr"/>
-      <c r="K135" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B136" s="11" t="inlineStr">
-        <is>
-          <t>沉积速率</t>
-        </is>
-      </c>
-      <c r="C136" s="11" t="inlineStr">
-        <is>
-          <t>速率（QCM 等）</t>
-        </is>
-      </c>
-      <c r="D136" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E136" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F136" s="11" t="inlineStr">
-        <is>
-          <t>nm/s</t>
-        </is>
-      </c>
-      <c r="G136" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H136" s="11" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="I136" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J136" s="11" t="inlineStr"/>
-      <c r="K136" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A119:K119"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A130:K130"/>
     <mergeCell ref="A63:K63"/>
     <mergeCell ref="A47:K47"/>
     <mergeCell ref="A84:K84"/>
@@ -10624,7 +10068,7 @@
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他/低波数Raman</t>
+          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>其他附加能力名称（历史）</t>
+          <t>其他附加能力</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>所引用装置登记的其他外场能力名称，只读带出</t>
+          <t>装置具备的其他附加能力，每项独立具名；不局限于物理场</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本数组</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -2700,22 +2700,22 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>历史单名称兼容</t>
+          <t>选择其他时必填；旧单名称兼容</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>磁场</t>
+          <t>[磁场, 机械振动]</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户在线复核</t>
+          <t>2026-09-09用户制备字段复核</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>只读投影；实际使用时仍需记录时间区间和具名参数</t>
+          <t>名称非空且不重复；无与所有能力互斥。生长条件中按名称分别引用并记录时间与参数</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr"/>
@@ -2728,17 +2728,17 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>其他附加能力</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>装置具备的其他附加能力，每项独立具名；不局限于物理场</t>
+          <t>装置照片或示意图 + 文字批注</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>文本数组</t>
+          <t>附件+自由</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -2751,26 +2751,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>选择其他时必填；旧单名称兼容</t>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>[磁场, 机械振动]</t>
+          <t>setup.png + 卧式双温区</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09用户制备字段复核</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>名称非空且不重复；无与所有能力互斥。生长条件中按名称分别引用并记录时间与参数</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2781,116 +2777,120 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>装置示意图与描述</t>
+          <t>炉管使用履历</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>装置照片或示意图 + 文字批注</t>
+          <t>当前炉管的清洗或更换累计次数，以及本次是最近一次清洗或更换后的第几炉</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>附件+自由</t>
+          <t>使用履历对象</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{reset_count, use_number_since_reset}</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>setup.png + 卧式双温区</t>
+          <t>{reset_count: 1, use_number_since_reset: 7}</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr"/>
+          <t>6/24决定·用户复核2026-07-24</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>界面分为“清洗或更换累计次数”和“清洗或更换后第几炉”；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
+        </is>
+      </c>
       <c r="K45" s="11" t="inlineStr"/>
     </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>设备</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>炉管使用履历</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>当前炉管的清洗或更换累计次数，以及本次是最近一次清洗或更换后的第几炉</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>使用履历对象</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>{reset_count, use_number_since_reset}</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>次</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>{reset_count: 1, use_number_since_reset: 7}</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>6/24决定·用户复核2026-07-24</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>界面分为“清洗或更换累计次数”和“清洗或更换后第几炉”；清洗或更换炉管后累计次数加1，本次使用序号从1重新累计</t>
-        </is>
-      </c>
-      <c r="K46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>§3 前驱体装载（独立放置或涂覆在具体衬底片上，可多组）</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>前驱体</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>装载标识</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>每组前驱体装载在本炉内稳定且唯一的机器标识</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>load_*</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>必填（系统生成）</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>load_1</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>科学修订契约</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>排序或编辑不得改变，供关联、导出和修订对比使用</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -2900,22 +2900,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>装载标识</t>
+          <t>本次使用形态</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>每组前驱体装载在本炉内稳定且唯一的机器标识</t>
+          <t>本次实验实际使用时的形态；先据此筛选可引用的化学品或气瓶批次</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>load_*</t>
+          <t>固/气/液</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -2923,24 +2923,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>必填（系统生成）</t>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>未发布（旧表单兼容）</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>load_1</t>
+          <t>固</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>排序或编辑不得改变，供关联、导出和修订对比使用</t>
+          <t>新记录不再单独保存相态；气路供给引用气瓶批次，其他装载引用化学品批次</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr"/>
@@ -2953,22 +2953,22 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>本次使用形态</t>
+          <t>物料批次</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际使用时的形态；先据此筛选可引用的化学品或气瓶批次</t>
+          <t>所引用物料批次的稳定实体标识</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>实体引用</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>固/气/液</t>
+          <t>MaterialLot UUID</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -2976,24 +2976,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>未发布（旧表单兼容）</t>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>固</t>
+          <t>MoO₃-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>新记录不再单独保存相态；气路供给引用气瓶批次，其他装载引用化学品批次</t>
+          <t>与物料批次版本成对保存，锁定时由服务端冻结权威快照</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr"/>
@@ -3006,22 +3006,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>物料批次</t>
+          <t>物料批次版本</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>所引用物料批次的稳定实体标识</t>
+          <t>本次实验引用的物料批次版本</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>实体引用</t>
+          <t>系统锁定</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot UUID</t>
+          <t>正整数</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -3036,20 +3036,24 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>MoO₃-B202（锁 v1）</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>与物料批次版本成对保存，锁定时由服务端冻结权威快照</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr"/>
+          <t>用户选择批次时由系统自动带入</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -3059,52 +3063,52 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>物料批次版本</t>
+          <t>实际物料用量</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>本次实验引用的物料批次版本</t>
+          <t>本次投料量；溶液滴涂/旋涂在各处理步骤填写实际溶液用量，同一份混合溶液的体积只记录一次；旧物料条目用量兼容，不代表干燥后负载量</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>系统锁定</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>正整数</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mg 或 µL（按相态）</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>条件必填（非气路供给且非仅浸渍；复合条件由科学载荷校验）</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>用户选择批次时由系统自动带入</t>
+          <t>气路供给不填；仅浸渍（可含干燥）不要求用量；滴涂必须为体积单位μL、mL或L；其他非气态装载填写实际投料量</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>{"ge":1,"type":"integer"}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -3116,54 +3120,50 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>实际物料用量</t>
+          <t>使用量单位</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>本次投料量；溶液滴涂/旋涂在各处理步骤填写实际溶液用量，同一份混合溶液的体积只记录一次；旧物料条目用量兼容，不代表干燥后负载量</t>
+          <t>与使用量成对保存的实际计量单位</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mg·g·μL·mL等</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>mg 或 µL（按相态）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>条件必填（非气路供给且非仅浸渍；复合条件由科学载荷校验）</t>
+          <t>条件必填（填写使用量时；仅浸渍不要求使用量）</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>mg</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>气路供给不填；仅浸渍（可含干燥）不要求用量；滴涂必须为体积单位μL、mL或L；其他非气态装载填写实际投料量</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>数值和单位成对填写；仅浸渍不要求用量；滴涂限体积单位；气路供给的量由过程流量通道表达</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -3173,22 +3173,22 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>使用量单位</t>
+          <t>该组分在溶液中的浓度</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>与使用量成对保存的实际计量单位</t>
+          <t>本次旋涂、滴涂或浸渍所用该物料的溶液浓度</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>mg·g·μL·mL等</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -3196,27 +3196,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>条件必填（填写使用量时；仅浸渍不要求使用量）</t>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>滴涂或浸渍必填；旋涂选填；填写后单位必填</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>mg</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-08-12师兄试填复核</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>数值和单位成对填写；仅浸渍不要求用量；滴涂限体积单位；气路供给的量由过程流量通道表达</t>
-        </is>
-      </c>
-      <c r="K53" s="11" t="inlineStr"/>
+          <t>按物料记录浓度；不从浸渍浓度和时长推算实际负载量；溶剂记录在对应处理步骤</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -3226,22 +3230,22 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>该组分在溶液中的浓度</t>
+          <t>浓度单位</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>本次旋涂、滴涂或浸渍所用该物料的溶液浓度</t>
+          <t>溶液浓度的计量单位</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mol/L·mmol/L (mM)·g/L·mg/mL·wt%·vol%·其他</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -3249,14 +3253,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr">
-        <is>
-          <t>滴涂或浸渍必填；旋涂选填；填写后单位必填</t>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>条件必填（已填溶液浓度）</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -3266,14 +3270,10 @@
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>按物料记录浓度；不从浸渍浓度和时长推算实际负载量；溶剂记录在对应处理步骤</t>
-        </is>
-      </c>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>数值和单位必须同时填写或同时留空</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -3283,22 +3283,22 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>浓度单位</t>
+          <t>其他浓度单位</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>溶液浓度的计量单位</t>
+          <t>选择其他浓度单位时填写的具体单位</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>mol/L·mmol/L (mM)·g/L·mg/mL·wt%·vol%·其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
-          <t>条件必填（已填溶液浓度）</t>
+          <t>条件必填(浓度单位=其他)</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>mg metal/mL</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>数值和单位必须同时填写或同时留空</t>
+          <t>仅在选择其他单位时显示</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr"/>
@@ -3336,22 +3336,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>其他浓度单位</t>
+          <t>使用前状态</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>选择其他浓度单位时填写的具体单位</t>
+          <t>固态前驱体在本次使用前是否存在潮解、结块或变色等可观察变化</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>正常/结块或潮解/变色/其他</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -3359,24 +3359,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(浓度单位=其他)</t>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>未发布（旧载荷兼容）</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>mg metal/mL</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>2026-08-12师兄试填复核</t>
+          <t>导师·2026-07-28前驱体复核</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>仅在选择其他单位时显示</t>
+          <t>当前科学载荷不接受本旧字段；如后续确认会影响复现，再以强类型观察重新立项</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr"/>
@@ -3389,22 +3389,22 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>使用前状态</t>
+          <t>处理方式</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>固态前驱体在本次使用前是否存在潮解、结块或变色等可观察变化</t>
+          <t>前驱体准备与装载操作，按装载方式展开；本炉热处理记录在生长条件</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>前驱体处理步骤数组</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>正常/结块或潮解/变色/其他</t>
+          <t>{step_type: 直接加载|研磨|压片|熔融|旋涂|滴涂|浸渍|干燥|其他, sequence, parameters: 固定参数对象}</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -3414,22 +3414,22 @@
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧载荷兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>[{type: 旋涂, parameters: {stages: [{speed_rpm: 1000, duration_s: 10}, {speed_rpm: 6000, duration_s: 30}]}}]</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>导师·2026-07-28前驱体复核</t>
+          <t>2026-07-24导师走查·2026-07-28前驱体复核</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>当前科学载荷不接受本旧字段；如后续确认会影响复现，再以强类型观察重新立项</t>
+          <t>舟和坩埚可选直接加载/研磨/压片/熔融/干燥/其他；衬底可选直接加载/旋涂/滴涂/浸渍/干燥/其他；气路供给不显示；其他装载仅具名处理。有序可重复，直接加载互斥；滴涂/旋涂每个处理步骤记录实际溶液用量solution_volume_uL，单位μL；同一装载记录为一份配方，各组分分别记录浓度，不重复计算溶液体积；不同配方分装载记录。滴涂记录溶剂、物料浓度与实际溶液用量，浸渍记录溶剂、物料浓度与浸渍时长；干燥记录温度和时长；熔融记录温度及选填时长。旧混合/预退火读取为具名其他，保留原参数，不修改历史原文</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr"/>
@@ -3442,22 +3442,22 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>装载方式</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>前驱体准备与装载操作，按装载方式展开；本炉热处理记录在生长条件</t>
+          <t>前驱体实际进入反应器的方式，决定物料类别、用量和位置的适用规则</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>前驱体处理步骤数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>{step_type: 直接加载|研磨|压片|熔融|旋涂|滴涂|浸渍|干燥|其他, sequence, parameters: 固定参数对象}</t>
+          <t>舟/坩埚/衬底/气路供给/其他</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
@@ -3465,24 +3465,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>[{type: 旋涂, parameters: {stages: [{speed_rpm: 1000, duration_s: 10}, {speed_rpm: 6000, duration_s: 30}]}}]</t>
+          <t>舟</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-28前驱体复核</t>
+          <t>2026-07-28前驱体复核</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>舟和坩埚可选直接加载/研磨/压片/熔融/干燥/其他；衬底可选直接加载/旋涂/滴涂/浸渍/干燥/其他；气路供给不显示；其他装载仅具名处理。有序可重复，直接加载互斥；滴涂/旋涂每个处理步骤记录实际溶液用量solution_volume_uL，单位μL；同一装载记录为一份配方，各组分分别记录浓度，不重复计算溶液体积；不同配方分装载记录。滴涂记录溶剂、物料浓度与实际溶液用量，浸渍记录溶剂、物料浓度与浸渍时长；干燥记录温度和时长；熔融记录温度及选填时长。旧混合/预退火读取为具名其他，保留原参数，不修改历史原文</t>
+          <t>气路供给只引用气瓶批次且不重复填用量；衬底装载必须关联本炉具体衬底片；其他装载名称保存在attrs.loading_other</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
@@ -3495,22 +3495,22 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>装载方式</t>
+          <t>涂覆衬底片</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>前驱体实际进入反应器的方式，决定物料类别、用量和位置的适用规则</t>
+          <t>本装载涂覆的具体衬底片，使用本炉衬底的稳定来源标识关联</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>衬底稳定引用数组</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>舟/坩埚/衬底/气路供给/其他</t>
+          <t>本炉已填写的衬底片</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -3518,24 +3518,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(装载方式=衬底)</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>舟</t>
+          <t>衬底片 S1</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28前驱体复核</t>
+          <t>2026-08-12师兄试填复核</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>气路供给只引用气瓶批次且不重复填用量；衬底装载必须关联本炉具体衬底片；其他装载名称保存在attrs.loading_other</t>
+          <t>使用 source_id 关联，界面显示样片标记、温区和位置；删除或重排衬底时关联不得暗中转向其他片</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr"/>
@@ -3548,47 +3548,47 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>涂覆衬底片</t>
+          <t>相对测温点位置</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>本装载涂覆的具体衬底片，使用本炉衬底的稳定来源标识关联</t>
+          <t>独立前驱体源相对所选温区测温点的有符号轴向距离</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>衬底稳定引用数组</t>
+          <t>源位置对象</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>本炉已填写的衬底片</t>
+          <t>{reference: zone_thermocouple, axial_mm}</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>条件必填(装载方式=衬底)</t>
+          <t>条件必填(装载方式=舟/坩埚/其他)</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>衬底片 S1</t>
+          <t>{reference: zone_thermocouple, axial_mm: -20}</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>2026-08-12师兄试填复核</t>
+          <t>会议·科学修订契约</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>使用 source_id 关联，界面显示样片标记、温区和位置；删除或重排衬底时关联不得暗中转向其他片</t>
+          <t>温区由heating_zone_ref单独保存；zone_thermocouple 为保留的历史机器码，当前指所选温区测温点，不限定传感器类型</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
@@ -3601,27 +3601,27 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>相对测温点位置</t>
+          <t>前驱体所在温区</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>独立前驱体源相对所选温区测温点的有符号轴向距离</t>
+          <t>独立前驱体源所属的加热温区，同时是轴向位置的测温点参照</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>源位置对象</t>
+          <t>温区选择</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>{reference: zone_thermocouple, axial_mm}</t>
+          <t>zone_1·zone_2·…</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
@@ -3631,90 +3631,86 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>{reference: zone_thermocouple, axial_mm: -20}</t>
+          <t>zone_2</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>会议·科学修订契约</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>温区由heating_zone_ref单独保存；zone_thermocouple 为保留的历史机器码，当前指所选温区测温点，不限定传感器类型</t>
+          <t>选择涂覆在衬底表面时继承关联衬底的温区与位置</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr"/>
     </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>前驱体</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>前驱体所在温区</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>独立前驱体源所属的加热温区，同时是轴向位置的测温点参照</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>温区选择</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>zone_1·zone_2·…</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(装载方式=舟/坩埚/其他)</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>zone_2</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>选择涂覆在衬底表面时继承关联衬底的温区与位置</t>
-        </is>
-      </c>
-      <c r="K62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>§4 衬底（长在什么基底上，可多片）</t>
         </is>
       </c>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="8" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>衬底材料（来自批次）</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>下拉+其他</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>SiO₂/Si</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -3724,22 +3720,22 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>衬底材料（来自批次）</t>
+          <t>物料批次（引用）</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>引用衬底批号并冻结当时版本、规格与证据</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>实体版本引用</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>{entity_id, version, snapshot}</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -3754,15 +3750,19 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>Sapphire-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>必须引用衬底类别的不可变物料版本</t>
+        </is>
+      </c>
       <c r="K64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
@@ -3773,22 +3773,22 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>本次样片标记</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>引用衬底批号并冻结当时版本、规格与证据</t>
+          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>实体版本引用</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>{entity_id, version, snapshot}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Sapphire-B202（锁 v1）</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>必须引用衬底类别的不可变物料版本</t>
+          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>本次样片标记</t>
+          <t>衬底化学式（来自批次）</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
+          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>标准化学式</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>Al₂O₃</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
+          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr"/>
@@ -3879,22 +3879,22 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>衬底化学式（来自批次）</t>
+          <t>取向与抛光信息（来自批次）</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>标准化学式</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -3902,24 +3902,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G67" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Al₂O₃</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
+          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr"/>
@@ -3932,22 +3932,22 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光信息（来自批次）</t>
+          <t>标称晶面取向（来自批次）</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
+          <t>批次标称晶面、取向状态或供应商切型；SiO₂/Si指底层Si；历史混合文本保留原意</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>规范晶面指数或明确的未知/非晶/多晶状态</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -3957,22 +3957,22 @@
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填（批次有明确规格时只读带出）</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>(0 0 0 1)</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
+          <t>不与化学式或偏转角合并</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
@@ -3985,12 +3985,12 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>标称晶面取向（来自批次）</t>
+          <t>抛光状态（来自批次）</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>批次标称晶面、取向状态或供应商切型；SiO₂/Si指底层Si；历史混合文本保留原意</t>
+          <t>批次独立登记的抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>规范晶面指数或明确的未知/非晶/多晶状态</t>
+          <t>单面抛/双面抛/未抛光/未知</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>选填（批次有明确规格时只读带出）</t>
+          <t>选填（来自批次）</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>(0 0 0 1)</t>
+          <t>single_side_polished</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-09-09用户确认</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>不与化学式或偏转角合并</t>
+          <t>不从晶面或非晶状态推断抛光；旧记录的混合文本不重写</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr"/>
@@ -4038,22 +4038,22 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>抛光状态（来自批次）</t>
+          <t>偏切信息（来自批次）</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>批次独立登记的抛光规格；引用批次后只读</t>
+          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>单面抛/双面抛/未抛光/未知</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -4063,22 +4063,22 @@
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>选填（来自批次）</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>single_side_polished</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09用户确认</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>不从晶面或非晶状态推断抛光；旧记录的混合文本不重写</t>
+          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr"/>
@@ -4091,27 +4091,27 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>偏切信息（来自批次）</t>
+          <t>偏切角（相对标称晶面，来自批次）</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
+          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -4131,10 +4131,14 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
-        </is>
-      </c>
-      <c r="K71" s="11" t="inlineStr"/>
+          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -4144,17 +4148,17 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>偏切角（相对标称晶面，来自批次）</t>
+          <t>偏切方向（来自批次）</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
+          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -4164,7 +4168,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
@@ -4174,24 +4178,20 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>c面向a轴偏0.2°</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
-        </is>
-      </c>
-      <c r="K72" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -4201,50 +4201,50 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>偏切方向（来自批次）</t>
+          <t>氧化层厚度（来自批次）</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
+          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴偏0.2°</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="inlineStr">
-        <is>
-          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
-        </is>
-      </c>
-      <c r="K73" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -4254,22 +4254,22 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度（来自批次）</t>
+          <t>标称表面粗糙度（来自批次）</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
+          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>正数</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -4277,27 +4277,27 @@
           <t>nm</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr"/>
-      <c r="K74" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -4307,47 +4307,47 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>标称表面粗糙度（来自批次）</t>
+          <t>本片实际尺寸与姿态</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
+          <t>本次实验实际放入炉内的这一片衬底的本体尺寸与空间姿态；长度和宽度按样片自身尺寸记录，不随摆放方向换名</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, tilt_azimuth_deg?, upright_growth_face_direction?: 朝下游|朝上游|朝炉管左侧|朝炉管右侧, placement_other?}</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G75" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
+          <t>{length_mm: 10, width_mm: 5, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: -15, tilt_azimuth_deg: 180}</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-09-03用户复核</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；length_mm必须大于等于width_mm；placement=倾角时tilt_angle_deg和tilt_azimuth_deg同时条件必填，倾角大于-90°、小于90°且不等于0°，方位角大于等于0°且小于360°；placement=竖放时upright_growth_face_direction条件必填；placement=其他时placement_other条件必填</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr"/>
@@ -4360,22 +4360,22 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>本片实际尺寸与姿态</t>
+          <t>片间生长面相对关系</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际放入炉内的这一片衬底的本体尺寸与空间姿态；长度和宽度按样片自身尺寸记录，不随摆放方向换名</t>
+          <t>两片衬底的生长面相对摆放关系；与单片空间姿态分开记录</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>衬底尺寸放置对象</t>
+          <t>衬底片间关系数组</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, tilt_azimuth_deg?, upright_growth_face_direction?: 朝下游|朝上游|朝炉管左侧|朝炉管右侧, placement_other?}</t>
+          <t>[{piece_a_label, piece_b_label, gap_mm?}]</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
@@ -4383,14 +4383,14 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>选填（仅多片衬底且存在该关系时）</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>{length_mm: 10, width_mm: 5, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: -15, tilt_azimuth_deg: 180}</t>
+          <t>[{piece_a_label: S1, piece_b_label: S2, gap_mm: 0}]</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>每片可能经过切割，故不得用批次来料尺寸替代；length_mm必须大于等于width_mm；placement=倾角时tilt_angle_deg和tilt_azimuth_deg同时条件必填，倾角大于-90°、小于90°且不等于0°，方位角大于等于0°且小于360°；placement=竖放时upright_growth_face_direction条件必填；placement=其他时placement_other条件必填</t>
+          <t>只在衬底片数不少于2且确实生长面相对时记录；两端必须引用本炉次不同的piece_label，同一无序对不得重复；gap_mm选填且大于等于0，0表示接触</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr"/>
@@ -4413,47 +4413,47 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>片间生长面相对关系</t>
+          <t>衬底处理（有序步骤）</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>两片衬底的生长面相对摆放关系；与单片空间姿态分开记录</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>衬底片间关系数组</t>
+          <t>衬底预处理步骤数组</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>[{piece_a_label, piece_b_label, gap_mm?}]</t>
+          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外/臭氧表面处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外/臭氧表面处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>选填（仅多片衬底且存在该关系时）</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>[{piece_a_label: S1, piece_b_label: S2, gap_mm: 0}]</t>
+          <t>[{type: 溶剂清洗, parameters: {solvent: 丙酮, cleaning_method: 超声, duration_min: 10}}, {type: 溶剂清洗, parameters: {solvent: 异丙醇, cleaning_method: 冲洗}}, {type: 氮气吹干}]</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>只在衬底片数不少于2且确实生长面相对时记录；两端必须引用本炉次不同的piece_label，同一无序对不得重复；gap_mm选填且大于等于0，0表示接触</t>
+          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外/臭氧表面处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
@@ -4466,50 +4466,54 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>衬底处理（有序步骤）</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>衬底预处理步骤数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外/臭氧表面处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外/臭氧表面处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>[{type: 溶剂清洗, parameters: {solvent: 丙酮, cleaning_method: 超声, duration_min: 10}}, {type: 溶剂清洗, parameters: {solvent: 异丙醇, cleaning_method: 冲洗}}, {type: 氮气吹干}]</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外/臭氧表面处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
-        </is>
-      </c>
-      <c r="K78" s="11" t="inlineStr"/>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -4519,27 +4523,27 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>预处理后等待时间</t>
+          <t>暴露环境</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>预处理结束到放入实验装置的时间</t>
+          <t>处理完成到放入实验装置期间所处环境</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>空气/氮气/真空/其他</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -4549,24 +4553,20 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>空气</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>表面老化</t>
-        </is>
-      </c>
-      <c r="K79" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>与时间间隔独立保存</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -4576,47 +4576,47 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>暴露环境</t>
+          <t>所在温区与相对测温点位置</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>处理完成到放入实验装置期间所处环境</t>
+          <t>第几温区、距离(±)</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>温区距离对象</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>空气/氮气/真空/其他</t>
+          <t>{zone_index, distance_mm}</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>温区2，+15</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>与时间间隔独立保存</t>
+          <t>上游为负、下游为正</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr"/>
@@ -4629,22 +4629,22 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>所在温区与相对测温点位置</t>
+          <t>轴向位置</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>第几温区、距离(±)</t>
+          <t>本片衬底相对装置轴向原点的位置</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>温区距离对象</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>{zone_index, distance_mm}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -4652,24 +4652,24 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>温区2，+15</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-30产品简化</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>上游为负、下游为正</t>
+          <t>仅兼容旧记录；新记录统一填写所在温区与测温点距离，不再使用未定义物理原点的全局轴向位置</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr"/>
@@ -4682,17 +4682,17 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>轴向位置</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>本片衬底相对装置轴向原点的位置</t>
+          <t>本片衬底摆放或处理的补充说明</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -4702,17 +4702,17 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>靠近气体入口</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -4720,128 +4720,128 @@
           <t>2026-07-30产品简化</t>
         </is>
       </c>
-      <c r="J82" s="11" t="inlineStr">
-        <is>
-          <t>仅兼容旧记录；新记录统一填写所在温区与测温点距离，不再使用未定义物理原点的全局轴向位置</t>
-        </is>
-      </c>
+      <c r="J82" s="11" t="inlineStr"/>
       <c r="K82" s="11" t="inlineStr"/>
     </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>衬底</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="C83" s="11" t="inlineStr">
-        <is>
-          <t>本片衬底摆放或处理的补充说明</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H83" s="11" t="inlineStr">
-        <is>
-          <t>靠近气体入口</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-30产品简化</t>
-        </is>
-      </c>
-      <c r="J83" s="11" t="inlineStr"/>
-      <c r="K83" s="11" t="inlineStr"/>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
         </is>
       </c>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="8" t="n"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="8" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>过程步</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>过程阶段</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>兼容已有具名过程阶段；新记录可留空，实际时间由过程通道和操作派生</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>过程阶段数组</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>{segment_key, segment_type, sequence, start_s, end_s, label?, note?}</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G84" s="13" t="inlineStr">
+        <is>
+          <t>未发布（历史修订只读兼容）</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-07用户复核</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>不要求用户划分反应开始或手算阶段起止时间</t>
+        </is>
+      </c>
+      <c r="K84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>过程通道</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>过程阶段</t>
+          <t>温度、气体与压力程序</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>兼容已有具名过程阶段；新记录可留空，实际时间由过程通道和操作派生</t>
+          <t>以统一实验时间零点记录每温区设定温度、每个实际气瓶供气区间及需要时的工作绝对压力</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>过程阶段数组</t>
+          <t>强类型过程通道数组</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>{segment_key, segment_type, sequence, start_s, end_s, label?, note?}</t>
+          <t>{channel_key, channel_type: temperature|flow|pressure|…, source_type, subject_type, subject_ref, subject_instance_ref, unit, data_kind, scalar_value?|series?|file_asset_id?, gas_lot_id?, gas_lot_version?, measurement_source?}</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G85" s="13" t="inlineStr">
-        <is>
-          <t>未发布（历史修订只读兼容）</t>
+          <t>按通道</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{channel_type: temperature, subject_ref: zone_1, unit: ℃, data_kind: interval_series, series: [{start_s: 0, value: 25}, {start_s: 1800, value: 750}]}]</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户复核</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>不要求用户划分反应开始或手算阶段起止时间</t>
+          <t>每个Setup温区必须有且仅有一条设定温度通道；至少一条正流量气体通道</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr"/>
@@ -4854,50 +4854,54 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>温度、气体与压力程序</t>
+          <t>过程总时长</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>以统一实验时间零点记录每温区设定温度、每个实际气瓶供气区间及需要时的工作绝对压力</t>
+          <t>从统一实验开始时间到本次制备过程结束的总时长，包含记录的降温与供气</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>强类型过程通道数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>{channel_key, channel_type: temperature|flow|pressure|…, source_type, subject_type, subject_ref, subject_instance_ref, unit, data_kind, scalar_value?|series?|file_asset_id?, gas_lot_id?, gas_lot_version?, measurement_source?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>按通道</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>必填</t>
+          <t>必填（历史记录可缺省，不推算补值）</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>[{channel_type: temperature, subject_ref: zone_1, unit: ℃, data_kind: interval_series, series: [{start_s: 0, value: 25}, {start_s: 1800, value: 750}]}]</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-09-04用户确认</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>每个Setup温区必须有且仅有一条设定温度通道；至少一条正流量气体通道</t>
-        </is>
-      </c>
-      <c r="K86" s="11" t="inlineStr"/>
+          <t>全程供气的起止为0至该时长；温度、供气、外场和事件不得超出，不以最后一个温度步骤代替过程终点</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -4907,79 +4911,75 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>过程总时长</t>
+          <t>本炉发生过异常</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>从统一实验开始时间到本次制备过程结束的总时长，包含记录的降温与供气</t>
+          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>勾选框</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>勾选=是；未勾选=否</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>必填（历史记录可缺省，不推算补值）</t>
+          <t>必填</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>未勾选</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户确认</t>
+          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>全程供气的起止为0至该时长；温度、供气、外场和事件不得超出，不以最后一个温度步骤代替过程终点</t>
-        </is>
-      </c>
-      <c r="K87" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>勾选时至少填写一条过程异常事件</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>过程通道</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>本炉发生过异常</t>
+          <t>反应压力条件</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
+          <t>相对于当地环境大气压的减压、常压或加压条件</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>勾选框</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>勾选=是；未勾选=否</t>
+          <t>atmospheric/low_pressure/high_pressure</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>未勾选</t>
+          <t>low_pressure</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>勾选时至少填写一条过程异常事件</t>
+          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr"/>
@@ -5012,17 +5012,17 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件</t>
+          <t>降温方式</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>相对于当地环境大气压的减压、常压或加压条件</t>
+          <t>本炉实际采用的降温方式</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>atmospheric/low_pressure/high_pressure</t>
+          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/staged_cooling/other</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>low_pressure</t>
+          <t>furnace_cooling</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
+          <t>程序降温复用温度步骤；分段降温按cooling_sequence记录先后顺序；随炉冷却和移炉冷却不要求虚构速率</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr"/>
@@ -5070,22 +5070,22 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>降温方式</t>
+          <t>降温顺序</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>本炉实际采用的降温方式</t>
+          <t>两种或更多降温操作的实际先后顺序；程序降温的温度和时长仍只记录在温度程序</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>有序降温操作数组</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/staged_cooling/other</t>
+          <t>{method, lid_open_temperature_C?, other_name?}</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
@@ -5093,24 +5093,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=staged_cooling)</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling</t>
+          <t>[{method: controlled_cooling}, {method: furnace_cooling}]</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-09-04用户确认</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>程序降温复用温度步骤；分段降温按cooling_sequence记录先后顺序；随炉冷却和移炉冷却不要求虚构速率</t>
+          <t>至少两段；开盖段填写开盖温度，其他段填写名称；不自动推断未记录的自然冷却温度曲线</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr"/>
@@ -5123,22 +5123,22 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>降温顺序</t>
+          <t>其他降温方式</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>两种或更多降温操作的实际先后顺序；程序降温的温度和时长仍只记录在温度程序</t>
+          <t>降温方式选择其他时的具体操作</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>有序降温操作数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>{method, lid_open_temperature_C?, other_name?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="G91" s="17" t="inlineStr">
         <is>
-          <t>条件必填(降温方式=staged_cooling)</t>
+          <t>条件必填(降温方式=other)</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>[{method: controlled_cooling}, {method: furnace_cooling}]</t>
+          <t>打开保温层自然冷却</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户确认</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>至少两段；开盖段填写开盖温度，其他段填写名称；不自动推断未记录的自然冷却温度曲线</t>
+          <t>仅选择其他时保存</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr"/>
@@ -5176,17 +5176,17 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>其他降温方式</t>
+          <t>旧记录设定降温速率</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>降温方式选择其他时的具体操作</t>
+          <t>保留旧记录独立填写的设定降温速率；新记录按温度程序各降温段派生</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=other)</t>
+          <t>℃/min</t>
+        </is>
+      </c>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>未发布（历史兼容）</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>打开保温层自然冷却</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -5216,10 +5216,14 @@
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>仅选择其他时保存</t>
-        </is>
-      </c>
-      <c r="K92" s="11" t="inlineStr"/>
+          <t>不再要求新记录填写单一降温速率；旧记录保留，不解释为实测值</t>
+        </is>
+      </c>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -5229,12 +5233,12 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>旧记录设定降温速率</t>
+          <t>开盖温度</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>保留旧记录独立填写的设定降温速率；新记录按温度程序各降温段派生</t>
+          <t>开盖冷却时实际开盖的温度</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
@@ -5249,17 +5253,17 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>℃/min</t>
-        </is>
-      </c>
-      <c r="G93" s="13" t="inlineStr">
-        <is>
-          <t>未发布（历史兼容）</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=open_lid_cooling)</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -5269,64 +5273,60 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>不再要求新记录填写单一降温速率；旧记录保留，不解释为实测值</t>
-        </is>
-      </c>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>仅开盖冷却时保存</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>开盖温度</t>
+          <t>记录类型</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>开盖冷却时实际开盖的温度</t>
+          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>预处理/反应条件/其他记录</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G94" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=open_lid_cooling)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>反应条件</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>仅开盖冷却时保存</t>
+          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr"/>
@@ -5339,22 +5339,22 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>实验前准备操作</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>按实际添加抽真空、气氛置换或其他操作；检漏属于设备操作规程，不设状态或自动确认。气氛置换按连续通气或抽空—回填展开，引用实际气瓶版本</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>{operation_type: pump_down|gas_exchange|other, exchange_mode?: continuous_flow|evacuation_backfill, duration_min?, target_absolute_pressure_Pa?, backfill_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, flow_sccm?, snapshot?}], other_name?}</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -5364,22 +5364,22 @@
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>[{operation_type: gas_exchange, exchange_mode: continuous_flow, duration_min: 10, gas_sources: [{material_lot_id: UUID, material_lot_version: 2, flow_sccm: 100}]}]</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-08-13师兄试填复核</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
+          <t>抽真空终点压力与时长至少一项；连续通气要求总时长，不填循环次数；抽空—回填要求循环次数，总时长和两端绝对压力选填，已知回填压力应高于抽空压力。流量按每瓶记录且选填，混气组成不重复录入。旧检漏转为具名其他且保留时长；旧置换方式不推断，编辑时需确认</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr"/>
@@ -5387,52 +5387,52 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·温度</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>实验前准备操作</t>
+          <t>设定温度程序</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>按实际添加抽真空、气氛置换或其他操作；检漏属于设备操作规程，不设状态或自动确认。气氛置换按连续通气或抽空—回填展开，引用实际气瓶版本</t>
+          <t>各温区按实验起点计时的时间—设定温度点</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>预处理操作数组</t>
+          <t>分温区温度程序</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>{operation_type: pump_down|gas_exchange|other, exchange_mode?: continuous_flow|evacuation_backfill, duration_min?, target_absolute_pressure_Pa?, backfill_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, flow_sccm?, snapshot?}], other_name?}</t>
+          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>min·℃</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>[{operation_type: gas_exchange, exchange_mode: continuous_flow, duration_min: 10, gas_sources: [{material_lot_id: UUID, material_lot_version: 2, flow_sccm: 100}]}]</t>
+          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13师兄试填复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>抽真空终点压力与时长至少一项；连续通气要求总时长，不填循环次数；抽空—回填要求循环次数，总时长和两端绝对压力选填，已知回填压力应高于抽空压力。流量按每瓶记录且选填，混气组成不重复录入。旧检漏转为具名其他且保留时长；旧置换方式不推断，编辑时需确认</t>
+          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr"/>
@@ -5445,27 +5445,27 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>实测温度文件与通道</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>温度时序文件引用</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
+          <t>℃ 随时间</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr"/>
@@ -5493,32 +5493,32 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>步·气体</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>逐气体供气程序</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>逐气体供气数组</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
+          <t>min·sccm</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr"/>
@@ -5546,32 +5546,32 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>反应压力条件与工作绝对压力</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>常压、低压或超高真空类别及工作绝对压力</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>常压；或低压 500 Pa</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -5591,40 +5591,44 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
-        </is>
-      </c>
-      <c r="K99" s="11" t="inlineStr"/>
+          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件与工作绝对压力</t>
+          <t>反应持续时间</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>从统一实验时间零点起计的反应条件持续时间</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>时长循环对象</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>{duration_min；旧记录可含cycle_count}</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
@@ -5634,54 +5638,50 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>常压；或低压 500 Pa</t>
+          <t>{duration_min: 45}</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24导师走查·2026-07-27终版整改</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K100" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
-        </is>
-      </c>
+          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>反应持续时间</t>
+          <t>降温参数</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>从统一实验时间零点起计的反应条件持续时间</t>
+          <t>降温方式以及适用的开盖温度、降温速率</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>降温参数对象</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>{duration_min；旧记录可含cycle_count}</t>
+          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>℃·℃/min</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45}</t>
+          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
+          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr"/>
@@ -5709,42 +5709,42 @@
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>附加能力使用记录</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>实际外场数组</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>{field_type: 等离子体|光|电|其他, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；其他[capability_name, 至少一个具名参数]；other_parameters?}</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
+          <t>按参数</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
+          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数；自定义能力名称须来自Setup版本快照列表；旧单名称兼容，不按标点猜拆</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr"/>
@@ -5762,52 +5762,52 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>附加能力使用记录</t>
+          <t>其他记录名称</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电|其他, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；其他[capability_name, 至少一个具名参数]；other_parameters?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布（旧过程步兼容）</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>临时移动源舟</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数；自定义能力名称须来自Setup版本快照列表；旧单名称兼容，不按标点猜拆</t>
+          <t>禁止仅保存“其他”</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr"/>
@@ -5820,17 +5820,17 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>其他记录说明</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>说明该记录的时间、操作和必要参数</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>第30分钟将源舟向下游移动10 mm</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -5860,80 +5860,80 @@
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>必须持久化，绝不静默过滤</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr"/>
     </row>
-    <row r="105">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t>其他记录说明</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr">
-        <is>
-          <t>说明该记录的时间、操作和必要参数</t>
-        </is>
-      </c>
-      <c r="D105" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F105" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G105" s="13" t="inlineStr">
-        <is>
-          <t>未发布（旧过程步兼容）</t>
-        </is>
-      </c>
-      <c r="H105" s="11" t="inlineStr">
-        <is>
-          <t>第30分钟将源舟向下游移动10 mm</t>
-        </is>
-      </c>
-      <c r="I105" s="11" t="inlineStr">
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（记录异常、中断与计划变更等客观事件；只记客观事实，不判成败）</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="8" t="n"/>
+      <c r="G105" s="8" t="n"/>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>过程事件</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>事件标识</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>系统生成键</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>event_1</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>2026-07-24整改</t>
         </is>
       </c>
-      <c r="J105" s="11" t="inlineStr">
-        <is>
-          <t>必须持久化，绝不静默过滤</t>
-        </is>
-      </c>
-      <c r="K105" s="11" t="inlineStr"/>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（记录异常、中断与计划变更等客观事件；只记客观事实，不判成败）</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
-      <c r="E106" s="8" t="n"/>
-      <c r="F106" s="8" t="n"/>
-      <c r="G106" s="8" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="8" t="n"/>
-      <c r="J106" s="8" t="n"/>
-      <c r="K106" s="8" t="n"/>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>创建事件时生成，排序和编辑不得改变</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
@@ -5943,22 +5943,22 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>事件标识</t>
+          <t>观察到的偏差</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+          <t>过程中直接观察到的异常或计划变更；人工干预、人工停止统一归为计划变更</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>系统生成键</t>
+          <t>多选+其他</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/设备报警/信号异常/计划变更/其他</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -5973,17 +5973,17 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
+          <t>按供给中断、管路/压力、设备/信号、计划变更、其他排序；具体干预写采取的处理，是否终止写处理结果；旧类型读取时归并并保留原类型文字，不修改历史原文</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr"/>
@@ -5996,22 +5996,22 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差</t>
+          <t>受影响对象</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>过程中直接观察到的异常或计划变更；人工干预、人工停止统一归为计划变更</t>
+          <t>观察到的偏差涉及的实验对象</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>多选+其他</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/设备报警/信号异常/计划变更/其他</t>
+          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -6019,14 +6019,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G108" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G108" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>供气中断</t>
+          <t>气路</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>按供给中断、管路/压力、设备/信号、计划变更、其他排序；具体干预写采取的处理，是否终止写处理结果；旧类型读取时归并并保留原类型文字，不修改历史原文</t>
+          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr"/>
@@ -6049,37 +6049,37 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>受影响对象</t>
+          <t>开始时间</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差涉及的实验对象</t>
+          <t>相对本炉实验开始时刻的事件开始时间</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G109" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>气路</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
+          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr"/>
@@ -6102,12 +6102,12 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>开始时间</t>
+          <t>结束时间</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件开始时间</t>
+          <t>相对本炉实验开始时刻的事件结束时间</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
@@ -6125,14 +6125,14 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G110" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G110" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="J110" s="11" t="inlineStr">
         <is>
-          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
+          <t>填写时不得早于开始时间</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr"/>
@@ -6155,27 +6155,27 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>结束时间</t>
+          <t>处理结果</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件结束时间</t>
+          <t>异常发生后过程是否恢复或终止</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>已恢复/部分恢复/实验终止/未知</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>已恢复</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>填写时不得早于开始时间</t>
+          <t>未知可显式记录，不等同于对产物成败的判定</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr"/>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>处理结果</t>
+          <t>对数据有效性的影响</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>异常发生后过程是否恢复或终止</t>
+          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>已恢复/部分恢复/实验终止/未知</t>
+          <t>不影响/部分影响/数据无效/未知</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>已恢复</t>
+          <t>部分影响</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="J112" s="11" t="inlineStr">
         <is>
-          <t>未知可显式记录，不等同于对产物成败的判定</t>
+          <t>只判断过程数据有效性，不判定产物成败</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr"/>
@@ -6261,22 +6261,22 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>对数据有效性的影响</t>
+          <t>怀疑原因</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
+          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>不影响/部分影响/数据无效/未知</t>
+          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>部分影响</t>
+          <t>设备故障</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>只判断过程数据有效性，不判定产物成败</t>
+          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr"/>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>怀疑原因</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -6339,22 +6339,22 @@
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>选填；观察到的偏差包含其他时必填</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>设备故障</t>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr">
         <is>
-          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
+          <t>其他异常时必填；最多2048字符，容纳旧分类前缀。界面分开填写异常情况与采取的处理，保存沿用现有描述分隔格式；附件独立关联</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr"/>
@@ -6367,22 +6367,22 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明</t>
+          <t>干预动作</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>事件现象、涉及对象和上下文</t>
+          <t>事件发生后实际采取的操作</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -6392,22 +6392,22 @@
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>选填；观察到的偏差包含其他时必填</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
+          <t>恢复供应</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>其他异常时必填；最多2048字符，容纳旧分类前缀。界面分开填写异常情况与采取的处理，保存沿用现有描述分隔格式；附件独立关联</t>
+          <t>与事件说明独立保存</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr"/>
@@ -6420,27 +6420,27 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>干预动作</t>
+          <t>排除的数据时间范围</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>事件发生后实际采取的操作</t>
+          <t>因该事件不应参与后续分析的时间区间</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>时间区间数组</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
+          <t>[{start_s, end_s}]</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>恢复供应</t>
+          <t>[{start_s: 1680, end_s: 1800}]</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="J116" s="11" t="inlineStr">
         <is>
-          <t>与事件说明独立保存</t>
+          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr"/>
@@ -6473,27 +6473,27 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>排除的数据时间范围</t>
+          <t>事件附件</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>因该事件不应参与后续分析的时间区间</t>
+          <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>时间区间数组</t>
+          <t>FileAsset引用数组</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>[{start_s, end_s}]</t>
+          <t>FileAsset UUID列表</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
@@ -6503,90 +6503,86 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>[{start_s: 1680, end_s: 1800}]</t>
+          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
+          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr"/>
     </row>
-    <row r="118">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B118" s="11" t="inlineStr">
-        <is>
-          <t>事件附件</t>
-        </is>
-      </c>
-      <c r="C118" s="11" t="inlineStr">
-        <is>
-          <t>与本条事件直接关联的图片、日志或其他文件</t>
-        </is>
-      </c>
-      <c r="D118" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset引用数组</t>
-        </is>
-      </c>
-      <c r="E118" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset UUID列表</t>
-        </is>
-      </c>
-      <c r="F118" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G118" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H118" s="11" t="inlineStr">
-        <is>
-          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
-        </is>
-      </c>
-      <c r="I118" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J118" s="11" t="inlineStr">
-        <is>
-          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
-        </is>
-      </c>
-      <c r="K118" s="11" t="inlineStr"/>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="10" t="inlineStr">
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
         </is>
       </c>
-      <c r="B119" s="8" t="n"/>
-      <c r="C119" s="8" t="n"/>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="8" t="n"/>
-      <c r="F119" s="8" t="n"/>
-      <c r="G119" s="8" t="n"/>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="8" t="n"/>
-      <c r="J119" s="8" t="n"/>
-      <c r="K119" s="8" t="n"/>
+      <c r="B118" s="8" t="n"/>
+      <c r="C118" s="8" t="n"/>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="8" t="n"/>
+      <c r="G118" s="8" t="n"/>
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="8" t="n"/>
+      <c r="J118" s="8" t="n"/>
+      <c r="K118" s="8" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>靶材（批次）</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>靶材化学身份 + 批次</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>引用</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>批次库</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>MoS₂ 靶-T01</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr"/>
+      <c r="K119" s="11" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
@@ -6596,27 +6592,27 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>靶材（批次）</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>靶材化学身份 + 批次</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>引用</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>批次库</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
@@ -6626,7 +6622,7 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>MoS₂ 靶-T01</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
@@ -6635,7 +6631,11 @@
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr"/>
-      <c r="K120" s="11" t="inlineStr"/>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>靶基距</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>靶到衬底距离</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>W·V</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -6684,11 +6684,7 @@
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr"/>
-      <c r="K121" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+      <c r="K121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
@@ -6698,27 +6694,27 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>功率与偏压</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>DC/RF 功率、基底偏压</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>DC/RF</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>W·V</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
@@ -6728,7 +6724,7 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>RF 150W；偏压 -50V</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -6737,7 +6733,11 @@
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr"/>
-      <c r="K122" s="11" t="inlineStr"/>
+      <c r="K122" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -6747,27 +6747,27 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>等离子体气氛与工作气压</t>
+          <t>预溅射与挡板时序</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>溅射气体与气压</t>
+          <t>预溅射时长、挡板开合时序</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>Ar / Ar+N₂…</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>min·s</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Ar，0.5 Pa</t>
+          <t>预溅 5 min</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -6788,7 +6788,7 @@
       <c r="J123" s="11" t="inlineStr"/>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>{"gt":0,"require_value":true}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>预溅射与挡板时序</t>
+          <t>沉积速率</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>预溅射时长、挡板开合时序</t>
+          <t>速率（QCM 等）</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>min·s</t>
+          <t>nm/s</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>预溅 5 min</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -6845,69 +6845,16 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
-        <is>
-          <t>沉积速率</t>
-        </is>
-      </c>
-      <c r="C125" s="11" t="inlineStr">
-        <is>
-          <t>速率（QCM 等）</t>
-        </is>
-      </c>
-      <c r="D125" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F125" s="11" t="inlineStr">
-        <is>
-          <t>nm/s</t>
-        </is>
-      </c>
-      <c r="G125" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="I125" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J125" s="11" t="inlineStr"/>
-      <c r="K125" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A119:K119"/>
+    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A63:K63"/>
-    <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A46:K46"/>
     <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A118:K118"/>
     <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A106:K106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6919,7 +6866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9832,17 +9779,17 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>其他附加能力名称（历史）</t>
+          <t>其他附加能力</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>外场能力选择“其他”时填写可复用的能力名称</t>
+          <t>装置具备的其他附加能力，每项独立具名；不局限于物理场</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>文本数组</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -9857,22 +9804,22 @@
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>历史单名称兼容</t>
+          <t>选择其他时必填；旧单名称兼容</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>磁场</t>
+          <t>[磁场, 机械振动]</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户在线复核</t>
+          <t>2026-09-09用户制备字段复核</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>一个装置版本登记一个其他外场名称；不同能力需要分别登记时再扩展为结构化列表</t>
+          <t>名称非空且不重复；无与所有能力互斥。生长条件中按名称分别引用并记录时间与参数</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
@@ -9885,22 +9832,22 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>其他附加能力</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>装置具备的其他附加能力，每项独立具名；不局限于物理场</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>文本数组</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -9908,93 +9855,89 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>选择其他时必填；旧单名称兼容</t>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>[磁场, 机械振动]</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09用户制备字段复核</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="inlineStr">
-        <is>
-          <t>名称非空且不重复；无与所有能力互斥。生长条件中按名称分别引用并记录时间与参数</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr"/>
       <c r="K59" s="11" t="inlineStr"/>
     </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>装置示意图与描述</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>装置照片或示意图及文字说明</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset引用+自由</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>{file_asset_id, sha256, note}</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>setup.png</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr"/>
-      <c r="K60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
         </is>
       </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>仪器编号</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>唯一编号</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>RAMAN-1</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr"/>
+      <c r="K61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -10004,22 +9947,22 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -10034,15 +9977,19 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>API key 保持 name_type 以兼容现有数据；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
+        </is>
+      </c>
       <c r="K62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
@@ -10053,22 +10000,22 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>适用表征方法</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -10076,26 +10023,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
@@ -10106,12 +10049,12 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -10136,7 +10079,7 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -10155,12 +10098,12 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -10178,14 +10121,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -10204,12 +10147,12 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>仪器持久标识</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -10239,10 +10182,14 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr"/>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
       <c r="K66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
@@ -10253,12 +10200,12 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>所在实验室与位置</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>物理位置</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -10283,19 +10230,15 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A305</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr"/>
       <c r="K67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
@@ -10306,22 +10249,22 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>其他固定配置说明</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -10336,15 +10279,19 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
       <c r="K68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
@@ -10355,22 +10302,22 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>其他固定配置说明</t>
+          <t>支持的表征方法</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>[{code,configuration}]；configuration.presets=[{name,conditions}]；code=other 时另有 method_names</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -10378,24 +10325,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>[{"code":"Raman","configuration":{}}]</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+          <t>每种方法可维护最多50套命名预设；名称去空白后1–128字符，同方法内忽略大小写唯一。conditions复用该方法结构化采集字段、单位及校验，至少一项，不要求整套测试必填参数齐全。表征主动选用后复制为本次实际条件，可调整；预设修改产生新仪器版本，不改历史记录。其他方法继续通过method_names具名；保留历史configuration内容。</t>
         </is>
       </c>
       <c r="K69" s="11" t="inlineStr"/>
@@ -10408,22 +10355,22 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>支持的表征方法</t>
+          <t>最近校准或维护日期</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
+          <t>校准/维护日期</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>[{code,configuration}]；configuration.presets=[{name,conditions}]；code=other 时另有 method_names</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -10431,82 +10378,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>[{"code":"Raman","configuration":{}}]</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>每种方法可维护最多50套命名预设；名称去空白后1–128字符，同方法内忽略大小写唯一。conditions复用该方法结构化采集字段、单位及校验，至少一项，不要求整套测试必填参数齐全。表征主动选用后复制为本次实际条件，可调整；预设修改产生新仪器版本，不改历史记录。其他方法继续通过method_names具名；保留历史configuration内容。</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr"/>
       <c r="K70" s="11" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>最近校准或维护日期</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>校准/维护日期</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr"/>
-      <c r="K71" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A60:K60"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/standard/字段草案-v3.xlsx
+++ b/docs/standard/字段草案-v3.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>片/膜状且目标成膜形式为分立片状时显示；连续膜不要求预设晶畴轮廓。旧 continuous_film/discrete_planar_crystal 读取兼容，旧轮廓编码保留</t>
+          <t>片/膜状且目标成膜形式为分立片状时显示；连续膜不要求预设晶畴轮廓</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>选择其他时必填；旧单名称兼容</t>
+          <t>选择其他时必填</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -2900,22 +2900,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>本次使用形态</t>
+          <t>物料批次</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际使用时的形态；先据此筛选可引用的化学品或气瓶批次</t>
+          <t>所引用物料批次的稳定实体标识</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>实体引用</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>固/气/液</t>
+          <t>MaterialLot UUID</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -2923,24 +2923,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>未发布（旧表单兼容）</t>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>固</t>
+          <t>MoO₃-B202（锁 v1）</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>新记录不再单独保存相态；气路供给引用气瓶批次，其他装载引用化学品批次</t>
+          <t>与物料批次版本成对保存，锁定时由服务端冻结权威快照</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr"/>
@@ -2953,22 +2953,22 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>物料批次</t>
+          <t>物料批次版本</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>所引用物料批次的稳定实体标识</t>
+          <t>本次实验引用的物料批次版本</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>实体引用</t>
+          <t>系统锁定</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>MaterialLot UUID</t>
+          <t>正整数</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -2983,20 +2983,24 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>MoO₃-B202（锁 v1）</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>与物料批次版本成对保存，锁定时由服务端冻结权威快照</t>
-        </is>
-      </c>
-      <c r="K49" s="11" t="inlineStr"/>
+          <t>用户选择批次时由系统自动带入</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -3006,52 +3010,52 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>物料批次版本</t>
+          <t>实际物料用量</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>本次实验引用的物料批次版本</t>
+          <t>本次投料量；溶液滴涂/旋涂在各处理步骤填写实际溶液用量，同一份混合溶液的体积只记录一次，不代表干燥后负载量</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>系统锁定</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>正整数</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mg 或 µL（按相态）</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>条件必填（非气路供给且非溶液涂覆；复合条件由科学载荷校验）</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>会议/复审</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>用户选择批次时由系统自动带入</t>
+          <t>气路供给和溶液涂覆（滴涂、旋涂、浸渍）不填；其他非气态装载填写实际投料量</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>{"ge":1,"type":"integer"}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -3063,54 +3067,50 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>实际物料用量</t>
+          <t>使用量单位</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>本次投料量；溶液滴涂/旋涂在各处理步骤填写实际溶液用量，同一份混合溶液的体积只记录一次；旧物料条目用量兼容，不代表干燥后负载量</t>
+          <t>与使用量成对保存的实际计量单位</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mg·g·μL·mL等</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>mg 或 µL（按相态）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr">
         <is>
-          <t>条件必填（非气路供给且非仅浸渍；复合条件由科学载荷校验）</t>
+          <t>条件必填（填写使用量时；仅浸渍不要求使用量）</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>mg</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>会议/复审</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>气路供给不填；仅浸渍（可含干燥）不要求用量；滴涂必须为体积单位μL、mL或L；其他非气态装载填写实际投料量</t>
-        </is>
-      </c>
-      <c r="K51" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>数值和单位成对填写；仅浸渍不要求用量；滴涂限体积单位；气路供给的量由过程流量通道表达</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -3120,22 +3120,22 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>使用量单位</t>
+          <t>该组分在溶液中的浓度</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>与使用量成对保存的实际计量单位</t>
+          <t>本次旋涂、滴涂或浸渍所用该物料的溶液浓度</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>mg·g·μL·mL等</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -3143,27 +3143,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>条件必填（填写使用量时；仅浸渍不要求使用量）</t>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>滴涂或浸渍必填；旋涂选填；填写后单位必填</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>mg</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
+          <t>2026-08-12师兄试填复核</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>数值和单位成对填写；仅浸渍不要求用量；滴涂限体积单位；气路供给的量由过程流量通道表达</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr"/>
+          <t>按物料记录浓度；不从浸渍浓度和时长推算实际负载量；溶剂记录在对应处理步骤</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -3173,22 +3177,22 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>该组分在溶液中的浓度</t>
+          <t>浓度单位</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>本次旋涂、滴涂或浸渍所用该物料的溶液浓度</t>
+          <t>溶液浓度的计量单位</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mol/L·mmol/L (mM)·g/L·mg/mL·wt%·vol%·其他</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -3196,14 +3200,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr">
-        <is>
-          <t>滴涂或浸渍必填；旋涂选填；填写后单位必填</t>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>条件必填（已填溶液浓度）</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -3213,14 +3217,10 @@
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>按物料记录浓度；不从浸渍浓度和时长推算实际负载量；溶剂记录在对应处理步骤</t>
-        </is>
-      </c>
-      <c r="K53" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>数值和单位必须同时填写或同时留空</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -3230,22 +3230,22 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>浓度单位</t>
+          <t>其他浓度单位</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>溶液浓度的计量单位</t>
+          <t>选择其他浓度单位时填写的具体单位</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>mol/L·mmol/L (mM)·g/L·mg/mL·wt%·vol%·其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>条件必填（已填溶液浓度）</t>
+          <t>条件必填(浓度单位=其他)</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>mg metal/mL</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>数值和单位必须同时填写或同时留空</t>
+          <t>仅在选择其他单位时显示</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
@@ -3283,22 +3283,22 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>其他浓度单位</t>
+          <t>处理方式</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>选择其他浓度单位时填写的具体单位</t>
+          <t>前驱体准备与装载操作，按装载方式展开；本炉热处理记录在生长条件</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>前驱体处理步骤数组</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{step_type: 直接加载|研磨|压片|熔融|旋涂|滴涂|浸渍|干燥|其他, sequence, parameters: 固定参数对象}</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -3306,24 +3306,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(浓度单位=其他)</t>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>mg metal/mL</t>
+          <t>[{type: 旋涂, parameters: {stages: [{speed_rpm: 1000, duration_s: 10}, {speed_rpm: 6000, duration_s: 30}]}}]</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-12师兄试填复核</t>
+          <t>2026-07-24导师走查·2026-07-28前驱体复核</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>仅在选择其他单位时显示</t>
+          <t>舟和坩埚可选直接加载/研磨/压片/熔融/干燥/其他；衬底可选直接加载/旋涂/滴涂/浸渍/干燥/其他；气路供给不显示；其他装载仅具名处理。有序可重复，直接加载互斥；滴涂/旋涂每个处理步骤记录实际溶液用量solution_volume_uL，单位μL；同一装载记录为一份配方，各组分分别记录浓度，不重复计算溶液体积；不同配方分装载记录。滴涂记录溶剂、物料浓度与实际溶液用量，浸渍记录溶剂、物料浓度与浸渍时长；干燥记录温度和时长；熔融记录温度及选填时长</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr"/>
@@ -3336,22 +3336,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>使用前状态</t>
+          <t>装载方式</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>固态前驱体在本次使用前是否存在潮解、结块或变色等可观察变化</t>
+          <t>前驱体实际进入反应器的方式，决定物料类别、用量和位置的适用规则</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>正常/结块或潮解/变色/其他</t>
+          <t>舟/坩埚/衬底/气路供给/其他</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -3359,24 +3359,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="13" t="inlineStr">
-        <is>
-          <t>未发布（旧载荷兼容）</t>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>舟</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>导师·2026-07-28前驱体复核</t>
+          <t>2026-07-28前驱体复核</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>当前科学载荷不接受本旧字段；如后续确认会影响复现，再以强类型观察重新立项</t>
+          <t>气路供给只引用气瓶批次且不重复填用量；衬底装载必须关联本炉具体衬底片；其他装载名称保存在attrs.loading_other</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr"/>
@@ -3389,22 +3389,22 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>处理方式</t>
+          <t>涂覆衬底片</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>前驱体准备与装载操作，按装载方式展开；本炉热处理记录在生长条件</t>
+          <t>本装载涂覆的具体衬底片，使用本炉衬底的稳定来源标识关联</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>前驱体处理步骤数组</t>
+          <t>衬底稳定引用数组</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>{step_type: 直接加载|研磨|压片|熔融|旋涂|滴涂|浸渍|干燥|其他, sequence, parameters: 固定参数对象}</t>
+          <t>本炉已填写的衬底片</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -3412,24 +3412,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(装载方式=衬底)</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>[{type: 旋涂, parameters: {stages: [{speed_rpm: 1000, duration_s: 10}, {speed_rpm: 6000, duration_s: 30}]}}]</t>
+          <t>衬底片 S1</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-28前驱体复核</t>
+          <t>2026-08-12师兄试填复核</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>舟和坩埚可选直接加载/研磨/压片/熔融/干燥/其他；衬底可选直接加载/旋涂/滴涂/浸渍/干燥/其他；气路供给不显示；其他装载仅具名处理。有序可重复，直接加载互斥；滴涂/旋涂每个处理步骤记录实际溶液用量solution_volume_uL，单位μL；同一装载记录为一份配方，各组分分别记录浓度，不重复计算溶液体积；不同配方分装载记录。滴涂记录溶剂、物料浓度与实际溶液用量，浸渍记录溶剂、物料浓度与浸渍时长；干燥记录温度和时长；熔融记录温度及选填时长。旧混合/预退火读取为具名其他，保留原参数，不修改历史原文</t>
+          <t>使用 source_id 关联，界面显示样片标记、温区和位置；删除或重排衬底时关联不得暗中转向其他片</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr"/>
@@ -3442,47 +3442,47 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>装载方式</t>
+          <t>相对测温点位置</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>前驱体实际进入反应器的方式，决定物料类别、用量和位置的适用规则</t>
+          <t>独立前驱体源相对所选温区测温点的有符号轴向距离</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>源位置对象</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>舟/坩埚/衬底/气路供给/其他</t>
+          <t>{reference: zone_thermocouple, axial_mm}</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(装载方式=舟/坩埚/其他)</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>舟</t>
+          <t>{reference: zone_thermocouple, axial_mm: -20}</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28前驱体复核</t>
+          <t>会议·科学修订契约</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>气路供给只引用气瓶批次且不重复填用量；衬底装载必须关联本炉具体衬底片；其他装载名称保存在attrs.loading_other</t>
+          <t>温区由heating_zone_ref单独保存；zone_thermocouple 指所选温区测温点，不限定传感器类型</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
@@ -3495,22 +3495,22 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>涂覆衬底片</t>
+          <t>前驱体所在温区</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>本装载涂覆的具体衬底片，使用本炉衬底的稳定来源标识关联</t>
+          <t>独立前驱体源所属的加热温区，同时是轴向位置的测温点参照</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>衬底稳定引用数组</t>
+          <t>温区选择</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>本炉已填写的衬底片</t>
+          <t>zone_1·zone_2·…</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -3520,103 +3520,67 @@
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
-          <t>条件必填(装载方式=衬底)</t>
+          <t>条件必填(装载方式=舟/坩埚/其他)</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>衬底片 S1</t>
+          <t>zone_2</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-12师兄试填复核</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>使用 source_id 关联，界面显示样片标记、温区和位置；删除或重排衬底时关联不得暗中转向其他片</t>
+          <t>选择涂覆在衬底表面时继承关联衬底的温区与位置</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr"/>
     </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>前驱体</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>相对测温点位置</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>独立前驱体源相对所选温区测温点的有符号轴向距离</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>源位置对象</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>{reference: zone_thermocouple, axial_mm}</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(装载方式=舟/坩埚/其他)</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>{reference: zone_thermocouple, axial_mm: -20}</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>会议·科学修订契约</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>温区由heating_zone_ref单独保存；zone_thermocouple 为保留的历史机器码，当前指所选温区测温点，不限定传感器类型</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>§4 衬底（长在什么基底上，可多片）</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>前驱体</t>
+          <t>衬底</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>前驱体所在温区</t>
+          <t>衬底材料（来自批次）</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>独立前驱体源所属的加热温区，同时是轴向位置的测温点参照</t>
+          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>温区选择</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>zone_1·zone_2·…</t>
+          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -3624,44 +3588,76 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(装载方式=舟/坩埚/其他)</t>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>zone_2</t>
+          <t>SiO₂/Si</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr">
-        <is>
-          <t>选择涂覆在衬底表面时继承关联衬底的温区与位置</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr"/>
       <c r="K61" s="11" t="inlineStr"/>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>§4 衬底（长在什么基底上，可多片）</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>衬底</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>物料批次（引用）</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>引用衬底批号并冻结当时版本、规格与证据</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>实体版本引用</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>{entity_id, version, snapshot}</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>Sapphire-B202（锁 v1）</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>必须引用衬底类别的不可变物料版本</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -3671,22 +3667,22 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>衬底材料（来自批次）</t>
+          <t>本次样片标记</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>衬底种类；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si·蓝宝石(Al₂O₃)·石英·云母·Cu箔·Au箔·h-BN·其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -3701,15 +3697,19 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>SiO₂/Si</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr"/>
+          <t>2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
+        </is>
+      </c>
       <c r="K63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
@@ -3720,22 +3720,22 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>物料批次（引用）</t>
+          <t>衬底化学式（来自批次）</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>引用衬底批号并冻结当时版本、规格与证据</t>
+          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>实体版本引用</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>{entity_id, version, snapshot}</t>
+          <t>标准化学式</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Sapphire-B202（锁 v1）</t>
+          <t>Al₂O₃</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>必须引用衬底类别的不可变物料版本</t>
+          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr"/>
@@ -3773,22 +3773,22 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>本次样片标记</t>
+          <t>取向与抛光信息（来自批次）</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>区分同一物料批次在本炉次中放入的不同衬底片</t>
+          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -3796,24 +3796,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>有规格数值</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>2026-07-27终版整改</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>只需在同一炉次内唯一；例如S1、S2或左、右</t>
+          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>衬底化学式（来自批次）</t>
+          <t>标称晶面取向（来自批次）</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>衬底材料的化学式；引用批次后从冻结快照带出且不可在炉次中覆盖</t>
+          <t>批次标称晶面、取向状态或供应商切型；SiO₂/Si指底层Si</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>标准化学式</t>
+          <t>规范晶面指数或明确的未知/非晶/多晶状态</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
@@ -3849,14 +3849,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>选填（批次有明确规格时只读带出）</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>Al₂O₃</t>
+          <t>(0 0 0 1)</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>与晶向和偏转角分开保存；允许常见圆括号与结晶水点号</t>
+          <t>不与化学式或偏转角合并</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr"/>
@@ -3879,22 +3879,22 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光信息（来自批次）</t>
+          <t>抛光状态（来自批次）</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用晶面取向与抛光规格；引用批次后只读</t>
+          <t>批次独立登记的抛光规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>单面抛/双面抛/未抛光/未知</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -3904,22 +3904,22 @@
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填（来自批次）</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>有规格数值</t>
+          <t>single_side_polished</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-09-09用户确认</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>Cu/Au箔等不适用时明确选择不适用；未知不得用虚构晶向代替</t>
+          <t>不从晶面或非晶状态推断抛光</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr"/>
@@ -3932,22 +3932,22 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>标称晶面取向（来自批次）</t>
+          <t>偏切信息（来自批次）</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>批次标称晶面、取向状态或供应商切型；SiO₂/Si指底层Si；历史混合文本保留原意</t>
+          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>规范晶面指数或明确的未知/非晶/多晶状态</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -3957,22 +3957,22 @@
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>选填（批次有明确规格时只读带出）</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>(0 0 0 1)</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>不与化学式或偏转角合并</t>
+          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
@@ -3985,50 +3985,54 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>抛光状态（来自批次）</t>
+          <t>偏切角（相对标称晶面，来自批次）</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>批次独立登记的抛光规格；引用批次后只读</t>
+          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>单面抛/双面抛/未抛光/未知</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>选填（来自批次）</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>single_side_polished</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09用户确认</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>不从晶面或非晶状态推断抛光；旧记录的混合文本不重写</t>
-        </is>
-      </c>
-      <c r="K69" s="11" t="inlineStr"/>
+          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -4038,22 +4042,22 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>偏切信息（来自批次）</t>
+          <t>偏切方向（来自批次）</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>批次是否提供且是否适用相对标称晶面的偏切规格；引用批次后只读</t>
+          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
@@ -4068,17 +4072,17 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>c面向a轴偏0.2°</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>只有明确有规格数值时才填写角度；0表示已报告无偏切，不表示未知</t>
+          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr"/>
@@ -4091,12 +4095,12 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>偏切角（相对标称晶面，来自批次）</t>
+          <t>氧化层厚度（来自批次）</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角；引用批次后只读</t>
+          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -4106,37 +4110,33 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>正数</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(仅SiO₂/Si)</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr">
-        <is>
-          <t>批次明确报告无偏切时填0；大于0时必须同时填写偏切方向</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr"/>
       <c r="K71" s="11" t="inlineStr">
         <is>
-          <t>{"ge":0,"lt":90}</t>
+          <t>{"gt":0}</t>
         </is>
       </c>
     </row>
@@ -4148,27 +4148,27 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>偏切方向（来自批次）</t>
+          <t>标称表面粗糙度（来自批次）</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向；引用批次后只读</t>
+          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
@@ -4178,17 +4178,17 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴偏0.2°</t>
+          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>miscut_angle_deg大于0时由跨字段校验强制填写</t>
+          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；引用批次后只读</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr"/>
@@ -4201,50 +4201,50 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>氧化层厚度（来自批次）</t>
+          <t>本片实际尺寸与姿态</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>SiO₂ 层厚度（决定光学判层数）；引用批次后只读</t>
+          <t>本次实验实际放入炉内的这一片衬底的本体尺寸与空间姿态；长度和宽度按样片自身尺寸记录，不随摆放方向换名</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>衬底尺寸放置对象</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>正数</t>
+          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, tilt_azimuth_deg?, upright_growth_face_direction?: 朝下游|朝上游|朝炉管左侧|朝炉管右侧, placement_other?}</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
-        </is>
-      </c>
-      <c r="G73" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(仅SiO₂/Si)</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>{length_mm: 10, width_mm: 5, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: -15, tilt_azimuth_deg: 180}</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="inlineStr"/>
-      <c r="K73" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>2026-09-03用户复核</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>每片可能经过切割，故不得用批次来料尺寸替代；length_mm必须大于等于width_mm；placement=倾角时tilt_angle_deg和tilt_azimuth_deg同时条件必填，倾角大于-90°、小于90°且不等于0°，方位角大于等于0°且小于360°；placement=竖放时upright_growth_face_direction条件必填；placement=其他时placement_other条件必填</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -4254,47 +4254,47 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>标称表面粗糙度（来自批次）</t>
+          <t>片间生长面相对关系</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度；本片实测粗糙度应记录在AFM结果</t>
+          <t>两片衬底的生长面相对摆放关系；与单片空间姿态分开记录</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>衬底片间关系数组</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>[{piece_a_label, piece_b_label, gap_mm?}]</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>未发布</t>
+          <t>选填（仅多片衬底且存在该关系时）</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>{availability: reported, metric: RMS, value_nm: 0.5}</t>
+          <t>[{piece_a_label: S1, piece_b_label: S2, gap_mm: 0}]</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-09-03用户复核</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>reported时value_nm必须大于等于0且Ra/RMS不可省略；not_provided不得伪填数值；历史无availability对象按reported兼容；引用批次后只读</t>
+          <t>只在衬底片数不少于2且确实生长面相对时记录；两端必须引用本炉次不同的piece_label，同一无序对不得重复；gap_mm选填且大于等于0，0表示接触</t>
         </is>
       </c>
       <c r="K74" s="11" t="inlineStr"/>
@@ -4307,47 +4307,47 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>本片实际尺寸与姿态</t>
+          <t>衬底处理（有序步骤）</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>本次实验实际放入炉内的这一片衬底的本体尺寸与空间姿态；长度和宽度按样片自身尺寸记录，不随摆放方向换名</t>
+          <t>预处理步骤序列（记顺序，展开参数）</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>衬底尺寸放置对象</t>
+          <t>衬底预处理步骤数组</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>{length_mm, width_mm, thickness_mm?, placement: 正放|倒扣|倾角|竖放|其他, tilt_angle_deg?, tilt_azimuth_deg?, upright_growth_face_direction?: 朝下游|朝上游|朝炉管左侧|朝炉管右侧, placement_other?}</t>
+          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外/臭氧表面处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外/臭氧表面处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>{length_mm: 10, width_mm: 5, thickness_mm: 0.5, placement: 倾角, tilt_angle_deg: -15, tilt_azimuth_deg: 180}</t>
+          <t>[{type: 溶剂清洗, parameters: {solvent: 丙酮, cleaning_method: 超声, duration_min: 10}}, {type: 溶剂清洗, parameters: {solvent: 异丙醇, cleaning_method: 冲洗}}, {type: 氮气吹干}]</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户复核</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>每片可能经过切割，故不得用批次来料尺寸替代；length_mm必须大于等于width_mm；placement=倾角时tilt_angle_deg和tilt_azimuth_deg同时条件必填，倾角大于-90°、小于90°且不等于0°，方位角大于等于0°且小于360°；placement=竖放时upright_growth_face_direction条件必填；placement=其他时placement_other条件必填</t>
+          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外/臭氧表面处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr"/>
@@ -4360,50 +4360,54 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>片间生长面相对关系</t>
+          <t>预处理后等待时间</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>两片衬底的生长面相对摆放关系；与单片空间姿态分开记录</t>
+          <t>预处理结束到放入实验装置的时间</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>衬底片间关系数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>[{piece_a_label, piece_b_label, gap_mm?}]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>选填（仅多片衬底且存在该关系时）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>[{piece_a_label: S1, piece_b_label: S2, gap_mm: 0}]</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户复核</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>只在衬底片数不少于2且确实生长面相对时记录；两端必须引用本炉次不同的piece_label，同一无序对不得重复；gap_mm选填且大于等于0，0表示接触</t>
-        </is>
-      </c>
-      <c r="K76" s="11" t="inlineStr"/>
+          <t>表面老化</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0}</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -4413,22 +4417,22 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>衬底处理（有序步骤）</t>
+          <t>暴露环境</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>预处理步骤序列（记顺序，展开参数）</t>
+          <t>处理完成到放入实验装置期间所处环境</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>衬底预处理步骤数组</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>{type: 溶剂清洗|氮气吹干|退火|等离子体|紫外/臭氧表面处理|其他, other_name?, parameters: 溶剂清洗[solvent: 丙酮|异丙醇|乙醇|甲醇|去离子水|其他, solvent_other?, cleaning_method: 超声|浸泡|冲洗|擦拭|其他, cleaning_method_other?, duration_min?, temperature_C?, wiping_material?, equipment_name?, ultrasonic_frequency_kHz?, ultrasonic_power_W?]；紫外/臭氧表面处理[duration_min, mode?, equipment_name?, source_distance_mm?, atmosphere?, temperature_C?, wavelength_nm?, irradiance_mW_cm2?, ozone_concentration_ppm?, gas_flow_sccm?]；其余为对应参数对象}</t>
+          <t>空气/氮气/真空/其他</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4436,24 +4440,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G77" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>[{type: 溶剂清洗, parameters: {solvent: 丙酮, cleaning_method: 超声, duration_min: 10}}, {type: 溶剂清洗, parameters: {solvent: 异丙醇, cleaning_method: 冲洗}}, {type: 氮气吹干}]</t>
+          <t>空气</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>有序可重复且每步只记录一种溶剂；连续使用多种溶剂应拆成多步。溶剂清洗选择超声或浸泡时duration_min必填，冲洗或擦拭时选填；紫外/臭氧表面处理duration_min必填，模式可明确为联合/仅紫外/仅臭氧；其余参数按实际设置或资料选填，擦拭材料仅擦拭适用，超声频率/功率仅超声适用；等离子体展开power_W、gas_species、pressure_Pa和duration_min；其他步骤必须具名并至少填写一个参数</t>
+          <t>与时间间隔独立保存</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr"/>
@@ -4466,54 +4470,50 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>预处理后等待时间</t>
+          <t>所在温区与相对测温点位置</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>预处理结束到放入实验装置的时间</t>
+          <t>第几温区、距离(±)</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>温区距离对象</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{zone_index, distance_mm}</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>温区2，+15</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>会议</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>表面老化</t>
-        </is>
-      </c>
-      <c r="K78" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0}</t>
-        </is>
-      </c>
+          <t>上游为负、下游为正</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -4523,22 +4523,22 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>暴露环境</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>处理完成到放入实验装置期间所处环境</t>
+          <t>本片衬底摆放或处理的补充说明</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>空气/氮气/真空/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -4553,123 +4553,83 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>空气</t>
+          <t>靠近气体入口</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
-        </is>
-      </c>
-      <c r="J79" s="11" t="inlineStr">
-        <is>
-          <t>与时间间隔独立保存</t>
-        </is>
-      </c>
+          <t>2026-07-30产品简化</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr"/>
       <c r="K79" s="11" t="inlineStr"/>
     </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t>衬底</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t>所在温区与相对测温点位置</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>第几温区、距离(±)</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>温区距离对象</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>{zone_index, distance_mm}</t>
-        </is>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="H80" s="11" t="inlineStr">
-        <is>
-          <t>温区2，+15</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J80" s="11" t="inlineStr">
-        <is>
-          <t>上游为负、下游为正</t>
-        </is>
-      </c>
-      <c r="K80" s="11" t="inlineStr"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="8" t="n"/>
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="8" t="n"/>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>衬底</t>
+          <t>过程通道</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>轴向位置</t>
+          <t>温度、气体与压力程序</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>本片衬底相对装置轴向原点的位置</t>
+          <t>以统一实验时间零点记录每温区设定温度、每个实际气瓶供气区间及需要时的工作绝对压力</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>强类型过程通道数组</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{channel_key, channel_type: temperature|flow|pressure|…, source_type, subject_type, subject_ref, subject_instance_ref, unit, data_kind, scalar_value?|series?|file_asset_id?, gas_lot_id?, gas_lot_version?, measurement_source?}</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>按通道</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>[{channel_type: temperature, subject_ref: zone_1, unit: ℃, data_kind: interval_series, series: [{start_s: 0, value: 25}, {start_s: 1800, value: 750}]}]</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>2026-07-30产品简化</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>仅兼容旧记录；新记录统一填写所在温区与测温点距离，不再使用未定义物理原点的全局轴向位置</t>
+          <t>每个Setup温区必须有且仅有一条设定温度通道；至少一条正流量气体通道</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr"/>
@@ -4677,22 +4637,22 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>衬底</t>
+          <t>过程通道</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>过程总时长</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>本片衬底摆放或处理的补充说明</t>
+          <t>从统一实验开始时间到本次制备过程结束的总时长，包含记录的降温与供气</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -4702,93 +4662,137 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>靠近气体入口</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>2026-07-30产品简化</t>
-        </is>
-      </c>
-      <c r="J82" s="11" t="inlineStr"/>
-      <c r="K82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>§5 实验过程（有序记录预处理、反应条件；具名其他记录仅作不丢信息的兜底）</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="n"/>
-      <c r="J83" s="8" t="n"/>
-      <c r="K83" s="8" t="n"/>
+          <t>2026-09-04用户确认</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>全程供气的起止为0至该时长；温度、供气、外场和事件不得超出，不以最后一个温度步骤代替过程终点</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>过程通道</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>本炉发生过异常</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>勾选框</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>勾选=是；未勾选=否</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>未勾选</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>勾选时至少填写一条过程异常事件</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>步·压力</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>过程阶段</t>
+          <t>反应压力条件</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>兼容已有具名过程阶段；新记录可留空，实际时间由过程通道和操作派生</t>
+          <t>相对于当地环境大气压的减压、常压或加压条件</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>过程阶段数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>{segment_key, segment_type, sequence, start_s, end_s, label?, note?}</t>
+          <t>atmospheric/low_pressure/high_pressure</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G84" s="13" t="inlineStr">
-        <is>
-          <t>未发布（历史修订只读兼容）</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>low_pressure</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户复核</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>不要求用户划分反应开始或手算阶段起止时间</t>
+          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr"/>
@@ -4796,32 +4800,32 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>过程通道</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>温度、气体与压力程序</t>
+          <t>降温方式</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>以统一实验时间零点记录每温区设定温度、每个实际气瓶供气区间及需要时的工作绝对压力</t>
+          <t>本炉实际采用的降温方式</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>强类型过程通道数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>{channel_key, channel_type: temperature|flow|pressure|…, source_type, subject_type, subject_ref, subject_instance_ref, unit, data_kind, scalar_value?|series?|file_asset_id?, gas_lot_id?, gas_lot_version?, measurement_source?}</t>
+          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/staged_cooling/other</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>按通道</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -4831,7 +4835,7 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>[{channel_type: temperature, subject_ref: zone_1, unit: ℃, data_kind: interval_series, series: [{start_s: 0, value: 25}, {start_s: 1800, value: 750}]}]</t>
+          <t>furnace_cooling</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -4841,7 +4845,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>每个Setup温区必须有且仅有一条设定温度通道；至少一条正流量气体通道</t>
+          <t>程序降温复用温度步骤；分段降温按cooling_sequence记录先后顺序；随炉冷却和移炉冷却不要求虚构速率</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr"/>
@@ -4849,42 +4853,42 @@
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>过程通道</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>过程总时长</t>
+          <t>降温顺序</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>从统一实验开始时间到本次制备过程结束的总时长，包含记录的降温与供气</t>
+          <t>两种或更多降温操作的实际先后顺序；程序降温的温度和时长仍只记录在温度程序</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>有序降温操作数组</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{method, lid_open_temperature_C?, other_name?}</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G86" s="12" t="inlineStr">
-        <is>
-          <t>必填（历史记录可缺省，不推算补值）</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=staged_cooling)</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>[{method: controlled_cooling}, {method: furnace_cooling}]</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -4894,39 +4898,35 @@
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>全程供气的起止为0至该时长；温度、供气、外场和事件不得超出，不以最后一个温度步骤代替过程终点</t>
-        </is>
-      </c>
-      <c r="K86" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>至少两段；开盖段填写开盖温度，其他段填写名称；不自动推断未记录的自然冷却温度曲线</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>过程通道</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>本炉发生过异常</t>
+          <t>其他降温方式</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>勾选表示本炉发生过异常，未勾选表示本炉无异常</t>
+          <t>降温方式选择其他时的具体操作</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>勾选框</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>勾选=是；未勾选=否</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -4934,24 +4934,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G87" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=other)</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>未勾选</t>
+          <t>打开保温层自然冷却</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01用户试填反馈·2026-09-02交互复核</t>
+          <t>2026-08-13现行科学契约校对</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>勾选时至少填写一条过程异常事件</t>
+          <t>仅选择其他时保存</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr"/>
@@ -4959,42 +4959,42 @@
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>步·降温</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件</t>
+          <t>开盖温度</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>相对于当地环境大气压的减压、常压或加压条件</t>
+          <t>开盖冷却时实际开盖的温度</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>atmospheric/low_pressure/high_pressure</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G88" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(降温方式=open_lid_cooling)</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>low_pressure</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>常压不保存精确压力通道；非常压必须在channels中保存一个正的绝对压力设定值</t>
+          <t>仅开盖冷却时保存</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr"/>
@@ -5012,27 +5012,27 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程步</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>降温方式</t>
+          <t>实验前准备操作</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>本炉实际采用的降温方式</t>
+          <t>按实际添加抽真空、气氛置换或其他操作；检漏属于设备操作规程，不设状态或自动确认。气氛置换按连续通气或抽空—回填展开，引用实际气瓶版本</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>预处理操作数组</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling/open_lid_cooling/rapid_furnace_move_cooling/controlled_cooling/staged_cooling/other</t>
+          <t>{operation_type: pump_down|gas_exchange|other, exchange_mode?: continuous_flow|evacuation_backfill, duration_min?, target_absolute_pressure_Pa?, backfill_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, flow_sccm?, snapshot?}], other_name?}</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -5040,24 +5040,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G89" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G89" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>furnace_cooling</t>
+          <t>[{operation_type: gas_exchange, exchange_mode: continuous_flow, duration_min: 10, gas_sources: [{material_lot_id: UUID, material_lot_version: 2, flow_sccm: 100}]}]</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-08-13师兄试填复核</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>程序降温复用温度步骤；分段降温按cooling_sequence记录先后顺序；随炉冷却和移炉冷却不要求虚构速率</t>
+          <t>抽真空终点压力与时长至少一项；连续通气要求总时长，不填循环次数；抽空—回填要求循环次数，总时长和两端绝对压力选填，已知回填压力应高于抽空压力。流量按每瓶记录且选填，混气组成不重复录入。旧检漏转为具名其他且保留时长；旧置换方式不推断，编辑时需确认</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr"/>
@@ -5065,215 +5065,175 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>步·外场</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>降温顺序</t>
+          <t>附加能力使用记录</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>两种或更多降温操作的实际先后顺序；程序降温的温度和时长仍只记录在温度程序</t>
+          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>有序降温操作数组</t>
+          <t>实际外场数组</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>{method, lid_open_temperature_C?, other_name?}</t>
+          <t>{field_type: 等离子体|光|电|其他, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；其他[capability_name, 至少一个具名参数]；other_parameters?}</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G90" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=staged_cooling)</t>
+          <t>按参数</t>
+        </is>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>[{method: controlled_cooling}, {method: furnace_cooling}]</t>
+          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户确认</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>至少两段；开盖段填写开盖温度，其他段填写名称；不自动推断未记录的自然冷却温度曲线</t>
+          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数；自定义能力名称须来自Setup版本快照列表</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr"/>
     </row>
-    <row r="91">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>步·降温</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>其他降温方式</t>
-        </is>
-      </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>降温方式选择其他时的具体操作</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=other)</t>
-        </is>
-      </c>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>打开保温层自然冷却</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-13现行科学契约校对</t>
-        </is>
-      </c>
-      <c r="J91" s="11" t="inlineStr">
-        <is>
-          <t>仅选择其他时保存</t>
-        </is>
-      </c>
-      <c r="K91" s="11" t="inlineStr"/>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>§6 过程事件 Process Events（记录异常、中断与计划变更等客观事件；只记客观事实，不判成败）</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="8" t="n"/>
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>旧记录设定降温速率</t>
+          <t>事件标识</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>保留旧记录独立填写的设定降温速率；新记录按温度程序各降温段派生</t>
+          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>系统生成键</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>℃/min</t>
-        </is>
-      </c>
-      <c r="G92" s="13" t="inlineStr">
-        <is>
-          <t>未发布（历史兼容）</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>2026-07-24整改</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>不再要求新记录填写单一降温速率；旧记录保留，不解释为实测值</t>
-        </is>
-      </c>
-      <c r="K92" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
+          <t>创建事件时生成，排序和编辑不得改变</t>
+        </is>
+      </c>
+      <c r="K92" s="11" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>开盖温度</t>
+          <t>观察到的偏差</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>开盖冷却时实际开盖的温度</t>
+          <t>过程中直接观察到的异常或计划变更；人工干预、人工停止统一归为计划变更</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>多选+其他</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/设备报警/信号异常/计划变更/其他</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
-        </is>
-      </c>
-      <c r="G93" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(降温方式=open_lid_cooling)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>供气中断</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13现行科学契约校对</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>仅开盖冷却时保存</t>
+          <t>按供给中断、管路/压力、设备/信号、计划变更、其他排序；具体干预写采取的处理，是否终止写处理结果</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr"/>
@@ -5281,27 +5241,27 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>记录类型</t>
+          <t>受影响对象</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>本条过程记录属于预处理、反应条件或具名其他记录</t>
+          <t>观察到的偏差涉及的实验对象</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>预处理/反应条件/其他记录</t>
+          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -5311,22 +5271,22 @@
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>反应条件</t>
+          <t>气路</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>数组顺序即过程顺序；不再重复拆成升温、稳定、生长、退火、降温和卸样</t>
+          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr"/>
@@ -5334,52 +5294,52 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>实验前准备操作</t>
+          <t>开始时间</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>按实际添加抽真空、气氛置换或其他操作；检漏属于设备操作规程，不设状态或自动确认。气氛置换按连续通气或抽空—回填展开，引用实际气瓶版本</t>
+          <t>相对本炉实验开始时刻的事件开始时间</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>预处理操作数组</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>{operation_type: pump_down|gas_exchange|other, exchange_mode?: continuous_flow|evacuation_backfill, duration_min?, target_absolute_pressure_Pa?, backfill_absolute_pressure_Pa?, cycle_count?, gas_sources?: [{material_lot_id, material_lot_version, flow_sccm?, snapshot?}], other_name?}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>[{operation_type: gas_exchange, exchange_mode: continuous_flow, duration_min: 10, gas_sources: [{material_lot_id: UUID, material_lot_version: 2, flow_sccm: 100}]}]</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13师兄试填复核</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>抽真空终点压力与时长至少一项；连续通气要求总时长，不填循环次数；抽空—回填要求循环次数，总时长和两端绝对压力选填，已知回填压力应高于抽空压力。流量按每瓶记录且选填，混气组成不重复录入。旧检漏转为具名其他且保留时长；旧置换方式不推断，编辑时需确认</t>
+          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr"/>
@@ -5387,52 +5347,52 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>设定温度程序</t>
+          <t>结束时间</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>各温区按实验起点计时的时间—设定温度点</t>
+          <t>相对本炉实验开始时刻的事件结束时间</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>分温区温度程序</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index, points: [{elapsed_min, setpoint_C}]}]}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>min·℃</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>{zones: [{zone_index: 1, points: [{elapsed_min: 0, setpoint_C: 25}, {elapsed_min: 30, setpoint_C: 750}, {elapsed_min: 45, setpoint_C: 750}]}]}</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>每温区时间严格递增且不得超过Setup温区数；相邻同温点表示保温；拒绝任意字符串</t>
+          <t>填写时不得早于开始时间</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr"/>
@@ -5440,52 +5400,52 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>步·温度</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>实测温度文件与通道</t>
+          <t>处理结果</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>控温实测曲线文件及时间列、温区通道映射；不是估算衬底真温</t>
+          <t>异常发生后过程是否恢复或终止</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>温度时序文件引用</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id, time_column, channels: [{zone_index, column_name}]}</t>
+          <t>已恢复/部分恢复/实验终止/未知</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>℃ 随时间</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>{file_asset_id: UUID, time_column: elapsed_min, channels: [{zone_index: 1, column_name: zone1_C}]}</t>
+          <t>已恢复</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>文件使用现有FileAsset保存SHA与炉次关联；传感器和不确定度从Setup快照只读带出</t>
+          <t>未知可显式记录，不等同于对产物成败的判定</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr"/>
@@ -5493,52 +5453,52 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>步·气体</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气程序</t>
+          <t>对数据有效性的影响</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>每种气体独立引用气瓶批次并记录一个或多个供气区间</t>
+          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>逐气体供气数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>{species, other_name?, lot_ref, measurement_source: MFC|转子|其他, measurement_source_other?, intervals: [{start_min, end_min, flow_sccm}]}</t>
+          <t>不影响/部分影响/数据无效/未知</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>min·sccm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>[{species: Ar, lot_ref: Ar-B01, intervals: [{start_min: 0, end_min: 30, flow_sccm: 80}, {start_min: 45, end_min: 50, flow_sccm: 80}]}]</t>
+          <t>部分影响</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>lot_ref与measurement_source必填，purity从lot_ref.snapshot带出；end_min必须大于start_min且flow_sccm&gt;0；同一气体的区间不得重叠；同时间段体积流量占比由各气体流量派生</t>
+          <t>只判断过程数据有效性，不判定产物成败</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr"/>
@@ -5546,109 +5506,105 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>步·压力</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>反应压力条件与工作绝对压力</t>
+          <t>怀疑原因</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>常压、低压或超高真空类别及工作绝对压力</t>
+          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>下拉+数值</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>常压(APCVD)/低压(LPCVD)/超高真空</t>
+          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>常压；或低压 500 Pa</t>
+          <t>设备故障</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>常压可只记录反应压力条件；低压与超高真空必须填写绝对压力，不填相对大气压的表压</t>
-        </is>
-      </c>
-      <c r="K99" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"option_ranges":{"atmospheric_pressure":{"ge":80000,"le":120000},"low_pressure":{"gt":1e-06,"lt":80000},"ultra_high_vacuum":{"gt":0,"le":1e-06}},"require_option":true,"require_value":false,"require_value_options":["low_pressure","ultra_high_vacuum"]}</t>
-        </is>
-      </c>
+          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>反应持续时间</t>
+          <t>事件具体说明</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>从统一实验时间零点起计的反应条件持续时间</t>
+          <t>事件现象、涉及对象和上下文</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>时长循环对象</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>{duration_min；旧记录可含cycle_count}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填；观察到的偏差包含其他时必填</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>{duration_min: 45}</t>
+          <t>Ar气瓶压力不足，供气中断约2分钟</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>duration_min&gt;0；历史cycle_count只读兼容，新记录不再把供气区间数解释为反应循环次数</t>
+          <t>其他异常时必填；最多2048字符，容纳旧分类前缀。界面分开填写异常情况与采取的处理，保存沿用现有描述分隔格式；附件独立关联</t>
         </is>
       </c>
       <c r="K100" s="11" t="inlineStr"/>
@@ -5656,52 +5612,52 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>步·降温</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>降温参数</t>
+          <t>干预动作</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>降温方式以及适用的开盖温度、降温速率</t>
+          <t>事件发生后实际采取的操作</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>降温参数对象</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>{method: 随炉冷却|开盖冷却|移炉快速冷却|受控降温|其他, lid_open_temperature_C?, cooling_rate_C_per_min?, method_other?}</t>
+          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>℃·℃/min</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>{method: 开盖冷却, lid_open_temperature_C: 580, cooling_rate_C_per_min: 20}</t>
+          <t>恢复供应</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>method=开盖冷却时开盖温度必填；method=受控降温时降温速率必填；method=其他时method_other必填</t>
+          <t>与事件说明独立保存</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr"/>
@@ -5709,32 +5665,32 @@
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>步·外场</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>附加能力使用记录</t>
+          <t>排除的数据时间范围</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>本炉实际启用的外场、时间区间与按类型展开的参数</t>
+          <t>因该事件不应参与后续分析的时间区间</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>实际外场数组</t>
+          <t>时间区间数组</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>{field_type: 等离子体|光|电|其他, start_min, end_min, parameters: 等离子体[power_W, gas_species, pressure_Pa]；光[wavelength_nm, power_mW或irradiance_mW_cm2, source_distance_mm]；电[voltage_V或field_strength_V_cm, electrode_gap_mm, direction]；其他[capability_name, 至少一个具名参数]；other_parameters?}</t>
+          <t>[{start_s, end_s}]</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>按参数</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
@@ -5744,17 +5700,17 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>[{field_type: 等离子体, start_min: 10, end_min: 40, parameters: [{name: power_W, value: 50, unit: W}, {name: gas_species, value: Ar, unit: —}, {name: pressure_Pa, value: 50, unit: Pa}]}]</t>
+          <t>[{start_s: 1680, end_s: 1800}]</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>科学修订契约</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>未添加表示本炉未使用外场；添加后field_type必须属于Setup能力，并填写时间区间及对应类型的必要参数；自定义能力名称须来自Setup版本快照列表；旧单名称兼容，不按标点猜拆</t>
+          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr"/>
@@ -5762,27 +5718,27 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>过程步</t>
+          <t>过程事件</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>其他记录名称</t>
+          <t>事件附件</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>具名说明未被预处理或反应条件覆盖的过程记录</t>
+          <t>与本条事件直接关联的图片、日志或其他文件</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>FileAsset引用数组</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FileAsset UUID列表</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -5792,269 +5748,261 @@
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>未发布（旧过程步兼容）</t>
+          <t>选填</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>临时移动源舟</t>
+          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>禁止仅保存“其他”</t>
+          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr"/>
     </row>
-    <row r="104">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>过程步</t>
-        </is>
-      </c>
-      <c r="B104" s="11" t="inlineStr">
-        <is>
-          <t>其他记录说明</t>
-        </is>
-      </c>
-      <c r="C104" s="11" t="inlineStr">
-        <is>
-          <t>说明该记录的时间、操作和必要参数</t>
-        </is>
-      </c>
-      <c r="D104" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E104" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G104" s="13" t="inlineStr">
-        <is>
-          <t>未发布（旧过程步兼容）</t>
-        </is>
-      </c>
-      <c r="H104" s="11" t="inlineStr">
-        <is>
-          <t>第30分钟将源舟向下游移动10 mm</t>
-        </is>
-      </c>
-      <c r="I104" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24整改</t>
-        </is>
-      </c>
-      <c r="J104" s="11" t="inlineStr">
-        <is>
-          <t>必须持久化，绝不静默过滤</t>
-        </is>
-      </c>
-      <c r="K104" s="11" t="inlineStr"/>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="10" t="inlineStr">
-        <is>
-          <t>§6 过程事件 Process Events（记录异常、中断与计划变更等客观事件；只记客观事实，不判成败）</t>
-        </is>
-      </c>
-      <c r="B105" s="8" t="n"/>
-      <c r="C105" s="8" t="n"/>
-      <c r="D105" s="8" t="n"/>
-      <c r="E105" s="8" t="n"/>
-      <c r="F105" s="8" t="n"/>
-      <c r="G105" s="8" t="n"/>
-      <c r="H105" s="8" t="n"/>
-      <c r="I105" s="8" t="n"/>
-      <c r="J105" s="8" t="n"/>
-      <c r="K105" s="8" t="n"/>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="8" t="n"/>
+      <c r="G104" s="8" t="n"/>
+      <c r="H104" s="8" t="n"/>
+      <c r="I104" s="8" t="n"/>
+      <c r="J104" s="8" t="n"/>
+      <c r="K104" s="8" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>靶材（批次）</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>靶材化学身份 + 批次</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>引用</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>批次库</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>MoS₂ 靶-T01</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr"/>
+      <c r="K105" s="11" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>事件标识</t>
+          <t>靶基距</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>每条事件稳定且不可重复的标识，用于关联附件</t>
+          <t>靶到衬底距离</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>系统生成键</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G106" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24整改</t>
-        </is>
-      </c>
-      <c r="J106" s="11" t="inlineStr">
-        <is>
-          <t>创建事件时生成，排序和编辑不得改变</t>
-        </is>
-      </c>
-      <c r="K106" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr"/>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差</t>
+          <t>功率与偏压</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>过程中直接观察到的异常或计划变更；人工干预、人工停止统一归为计划变更</t>
+          <t>DC/RF 功率、基底偏压</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>多选+其他</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>供电中断/供水中断/供气中断/管路堵塞/压力突变/设备报警/信号异常/计划变更/其他</t>
+          <t>DC/RF</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G107" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>W·V</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>供气中断</t>
+          <t>RF 150W；偏压 -50V</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J107" s="11" t="inlineStr">
-        <is>
-          <t>按供给中断、管路/压力、设备/信号、计划变更、其他排序；具体干预写采取的处理，是否终止写处理结果；旧类型读取时归并并保留原类型文字，不修改历史原文</t>
-        </is>
-      </c>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr"/>
       <c r="K107" s="11" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>受影响对象</t>
+          <t>等离子体气氛与工作气压</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>观察到的偏差涉及的实验对象</t>
+          <t>溅射气体与气压</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>下拉+数值</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>前驱体装载/气路/炉体/衬底/样品/过程通道/仪器/其他</t>
+          <t>Ar / Ar+N₂…</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>气路</t>
+          <t>Ar，0.5 Pa</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J108" s="11" t="inlineStr">
-        <is>
-          <t>对象与异常类型分开，支持一个事件涉及多个对象</t>
-        </is>
-      </c>
-      <c r="K108" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr"/>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0,"require_value":true}</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>开始时间</t>
+          <t>预溅射与挡板时序</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件开始时间</t>
+          <t>预溅射时长、挡板开合时序</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
@@ -6069,45 +6017,45 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G109" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>min·s</t>
+        </is>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>预溅 5 min</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J109" s="11" t="inlineStr">
-        <is>
-          <t>t0取basic_info.started_at；时间轴内统一使用秒</t>
-        </is>
-      </c>
-      <c r="K109" s="11" t="inlineStr"/>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr"/>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>{"gt":0}</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>过程事件</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>结束时间</t>
+          <t>沉积速率</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>相对本炉实验开始时刻的事件结束时间</t>
+          <t>速率（QCM 等）</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
@@ -6122,724 +6070,26 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>nm/s</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>选填</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J110" s="11" t="inlineStr">
-        <is>
-          <t>填写时不得早于开始时间</t>
-        </is>
-      </c>
-      <c r="K110" s="11" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t>处理结果</t>
-        </is>
-      </c>
-      <c r="C111" s="11" t="inlineStr">
-        <is>
-          <t>异常发生后过程是否恢复或终止</t>
-        </is>
-      </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>下拉</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>已恢复/部分恢复/实验终止/未知</t>
-        </is>
-      </c>
-      <c r="F111" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G111" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H111" s="11" t="inlineStr">
-        <is>
-          <t>已恢复</t>
-        </is>
-      </c>
-      <c r="I111" s="11" t="inlineStr">
-        <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J111" s="11" t="inlineStr">
-        <is>
-          <t>未知可显式记录，不等同于对产物成败的判定</t>
-        </is>
-      </c>
-      <c r="K111" s="11" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t>对数据有效性的影响</t>
-        </is>
-      </c>
-      <c r="C112" s="11" t="inlineStr">
-        <is>
-          <t>该事件是否影响本炉部分或全部过程数据的可用性</t>
-        </is>
-      </c>
-      <c r="D112" s="11" t="inlineStr">
-        <is>
-          <t>下拉</t>
-        </is>
-      </c>
-      <c r="E112" s="11" t="inlineStr">
-        <is>
-          <t>不影响/部分影响/数据无效/未知</t>
-        </is>
-      </c>
-      <c r="F112" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G112" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H112" s="11" t="inlineStr">
-        <is>
-          <t>部分影响</t>
-        </is>
-      </c>
-      <c r="I112" s="11" t="inlineStr">
-        <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J112" s="11" t="inlineStr">
-        <is>
-          <t>只判断过程数据有效性，不判定产物成败</t>
-        </is>
-      </c>
-      <c r="K112" s="11" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B113" s="11" t="inlineStr">
-        <is>
-          <t>怀疑原因</t>
-        </is>
-      </c>
-      <c r="C113" s="11" t="inlineStr">
-        <is>
-          <t>对已观察偏差的当时原因判断，可多选或保持未知</t>
-        </is>
-      </c>
-      <c r="D113" s="11" t="inlineStr">
-        <is>
-          <t>多选</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>管路堵塞/设备故障/公用工程中断/操作员动作/过程不稳定/未知/其他</t>
-        </is>
-      </c>
-      <c r="F113" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G113" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H113" s="11" t="inlineStr">
-        <is>
-          <t>设备故障</t>
-        </is>
-      </c>
-      <c r="I113" s="11" t="inlineStr">
-        <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J113" s="11" t="inlineStr">
-        <is>
-          <t>怀疑原因与观察到的偏差分开，避免将推断写成事实</t>
-        </is>
-      </c>
-      <c r="K113" s="11" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t>事件具体说明</t>
-        </is>
-      </c>
-      <c r="C114" s="11" t="inlineStr">
-        <is>
-          <t>事件现象、涉及对象和上下文</t>
-        </is>
-      </c>
-      <c r="D114" s="11" t="inlineStr">
-        <is>
-          <t>自由</t>
-        </is>
-      </c>
-      <c r="E114" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F114" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G114" s="13" t="inlineStr">
-        <is>
-          <t>选填；观察到的偏差包含其他时必填</t>
-        </is>
-      </c>
-      <c r="H114" s="11" t="inlineStr">
-        <is>
-          <t>Ar气瓶压力不足，供气中断约2分钟</t>
-        </is>
-      </c>
-      <c r="I114" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J114" s="11" t="inlineStr">
-        <is>
-          <t>其他异常时必填；最多2048字符，容纳旧分类前缀。界面分开填写异常情况与采取的处理，保存沿用现有描述分隔格式；附件独立关联</t>
-        </is>
-      </c>
-      <c r="K114" s="11" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B115" s="11" t="inlineStr">
-        <is>
-          <t>干预动作</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="inlineStr">
-        <is>
-          <t>事件发生后实际采取的操作</t>
-        </is>
-      </c>
-      <c r="D115" s="11" t="inlineStr">
-        <is>
-          <t>多选</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>调整流量/调整压力/调整温度/恢复供应/检查设备/停止实验/其他</t>
-        </is>
-      </c>
-      <c r="F115" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G115" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H115" s="11" t="inlineStr">
-        <is>
-          <t>恢复供应</t>
-        </is>
-      </c>
-      <c r="I115" s="11" t="inlineStr">
-        <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J115" s="11" t="inlineStr">
-        <is>
-          <t>与事件说明独立保存</t>
-        </is>
-      </c>
-      <c r="K115" s="11" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B116" s="11" t="inlineStr">
-        <is>
-          <t>排除的数据时间范围</t>
-        </is>
-      </c>
-      <c r="C116" s="11" t="inlineStr">
-        <is>
-          <t>因该事件不应参与后续分析的时间区间</t>
-        </is>
-      </c>
-      <c r="D116" s="11" t="inlineStr">
-        <is>
-          <t>时间区间数组</t>
-        </is>
-      </c>
-      <c r="E116" s="11" t="inlineStr">
-        <is>
-          <t>[{start_s, end_s}]</t>
-        </is>
-      </c>
-      <c r="F116" s="11" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G116" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H116" s="11" t="inlineStr">
-        <is>
-          <t>[{start_s: 1680, end_s: 1800}]</t>
-        </is>
-      </c>
-      <c r="I116" s="11" t="inlineStr">
-        <is>
-          <t>科学修订契约</t>
-        </is>
-      </c>
-      <c r="J116" s="11" t="inlineStr">
-        <is>
-          <t>只在有明确排除范围时填写，不自动扩大到整炉</t>
-        </is>
-      </c>
-      <c r="K116" s="11" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t>过程事件</t>
-        </is>
-      </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t>事件附件</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr">
-        <is>
-          <t>与本条事件直接关联的图片、日志或其他文件</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset引用数组</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset UUID列表</t>
-        </is>
-      </c>
-      <c r="F117" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G117" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H117" s="11" t="inlineStr">
-        <is>
-          <t>[550e8400-e29b-41d4-a716-446655440001]</t>
-        </is>
-      </c>
-      <c r="I117" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-24导师走查</t>
-        </is>
-      </c>
-      <c r="J117" s="11" t="inlineStr">
-        <is>
-          <t>文件必须属于同一炉次且asset_role=process_event_attachment</t>
-        </is>
-      </c>
-      <c r="K117" s="11" t="inlineStr"/>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>§8 PVD 专用（若合成方法选 PVD 类才启用；延后实现，先占位）</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="n"/>
-      <c r="C118" s="8" t="n"/>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="8" t="n"/>
-      <c r="F118" s="8" t="n"/>
-      <c r="G118" s="8" t="n"/>
-      <c r="H118" s="8" t="n"/>
-      <c r="I118" s="8" t="n"/>
-      <c r="J118" s="8" t="n"/>
-      <c r="K118" s="8" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t>靶材（批次）</t>
-        </is>
-      </c>
-      <c r="C119" s="11" t="inlineStr">
-        <is>
-          <t>靶材化学身份 + 批次</t>
-        </is>
-      </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>批次库</t>
-        </is>
-      </c>
-      <c r="F119" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G119" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H119" s="11" t="inlineStr">
-        <is>
-          <t>MoS₂ 靶-T01</t>
-        </is>
-      </c>
-      <c r="I119" s="11" t="inlineStr">
-        <is>
           <t>复审</t>
         </is>
       </c>
-      <c r="J119" s="11" t="inlineStr"/>
-      <c r="K119" s="11" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t>靶基距</t>
-        </is>
-      </c>
-      <c r="C120" s="11" t="inlineStr">
-        <is>
-          <t>靶到衬底距离</t>
-        </is>
-      </c>
-      <c r="D120" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F120" s="11" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G120" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H120" s="11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I120" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J120" s="11" t="inlineStr"/>
-      <c r="K120" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t>功率与偏压</t>
-        </is>
-      </c>
-      <c r="C121" s="11" t="inlineStr">
-        <is>
-          <t>DC/RF 功率、基底偏压</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>DC/RF</t>
-        </is>
-      </c>
-      <c r="F121" s="11" t="inlineStr">
-        <is>
-          <t>W·V</t>
-        </is>
-      </c>
-      <c r="G121" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H121" s="11" t="inlineStr">
-        <is>
-          <t>RF 150W；偏压 -50V</t>
-        </is>
-      </c>
-      <c r="I121" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J121" s="11" t="inlineStr"/>
-      <c r="K121" s="11" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B122" s="11" t="inlineStr">
-        <is>
-          <t>等离子体气氛与工作气压</t>
-        </is>
-      </c>
-      <c r="C122" s="11" t="inlineStr">
-        <is>
-          <t>溅射气体与气压</t>
-        </is>
-      </c>
-      <c r="D122" s="11" t="inlineStr">
-        <is>
-          <t>下拉+数值</t>
-        </is>
-      </c>
-      <c r="E122" s="11" t="inlineStr">
-        <is>
-          <t>Ar / Ar+N₂…</t>
-        </is>
-      </c>
-      <c r="F122" s="11" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="G122" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H122" s="11" t="inlineStr">
-        <is>
-          <t>Ar，0.5 Pa</t>
-        </is>
-      </c>
-      <c r="I122" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J122" s="11" t="inlineStr"/>
-      <c r="K122" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0,"require_value":true}</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t>预溅射与挡板时序</t>
-        </is>
-      </c>
-      <c r="C123" s="11" t="inlineStr">
-        <is>
-          <t>预溅射时长、挡板开合时序</t>
-        </is>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F123" s="11" t="inlineStr">
-        <is>
-          <t>min·s</t>
-        </is>
-      </c>
-      <c r="G123" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H123" s="11" t="inlineStr">
-        <is>
-          <t>预溅 5 min</t>
-        </is>
-      </c>
-      <c r="I123" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J123" s="11" t="inlineStr"/>
-      <c r="K123" s="11" t="inlineStr">
-        <is>
-          <t>{"gt":0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t>沉积速率</t>
-        </is>
-      </c>
-      <c r="C124" s="11" t="inlineStr">
-        <is>
-          <t>速率（QCM 等）</t>
-        </is>
-      </c>
-      <c r="D124" s="11" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="E124" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F124" s="11" t="inlineStr">
-        <is>
-          <t>nm/s</t>
-        </is>
-      </c>
-      <c r="G124" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
-        </is>
-      </c>
-      <c r="H124" s="11" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="I124" s="11" t="inlineStr">
-        <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J124" s="11" t="inlineStr"/>
-      <c r="K124" s="11" t="inlineStr">
+      <c r="J110" s="11" t="inlineStr"/>
+      <c r="K110" s="11" t="inlineStr">
         <is>
           <t>{"gt":0}</t>
         </is>
@@ -6847,13 +6097,13 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A105:K105"/>
-    <mergeCell ref="A83:K83"/>
-    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="A91:K91"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A104:K104"/>
+    <mergeCell ref="A60:K60"/>
     <mergeCell ref="A46:K46"/>
     <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A118:K118"/>
+    <mergeCell ref="A80:K80"/>
     <mergeCell ref="A27:K27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6866,7 +6116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8302,22 +7552,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·晶向与抛光</t>
+          <t>▸衬底·偏切信息</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>取向与抛光面</t>
+          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>文本+下拉</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>晶向；单面抛/双面抛</t>
+          <t>有规格数值·供应商未提供·不适用</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -8327,29 +7577,25 @@
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>未发布(历史兼容)</t>
+          <t>未发布</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Si(100)；单面抛</t>
+          <t>供应商未提供</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>历史合并记录保留原文与导出；新录入使用独立的substrate_crystal_plane和substrate_polish</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>{"require_option":true,"require_value":true}</t>
-        </is>
-      </c>
+          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -8359,27 +7605,27 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切信息</t>
+          <t>▸衬底·偏切角</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>供应商是否提供且该衬底是否适用相对标称晶面的偏切规格</t>
+          <t>实际晶面相对标称晶面的偏切角</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>有规格数值·供应商未提供·不适用</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
@@ -8389,20 +7635,24 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>供应商未提供</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>2026-07-24用户走查</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>0仅表示供应商明确报告无偏切，不能表示未知或不适用</t>
-        </is>
-      </c>
-      <c r="K30" s="11" t="inlineStr"/>
+          <t>大于0时必须同时填写substrate_miscut_direction</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":0,"lt":90}</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -8412,17 +7662,17 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切角</t>
+          <t>▸衬底·偏切方向</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>实际晶面相对标称晶面的偏切角</t>
+          <t>偏切角所指的晶轴或晶向</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -8432,7 +7682,7 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -8442,7 +7692,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>c面向a轴</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -8452,14 +7702,10 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>大于0时必须同时填写substrate_miscut_direction</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":0,"lt":90}</t>
-        </is>
-      </c>
+          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -8469,27 +7715,27 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·偏切方向</t>
+          <t>▸衬底·标称表面粗糙度</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>偏切角所指的晶轴或晶向</t>
+          <t>供应商或批次规格中的标称粗糙度</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>粗糙度对象</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
@@ -8499,17 +7745,17 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>c面向a轴</t>
+          <t>{availability: not_provided}</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24用户走查</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>substrate_miscut_angle_deg大于0时由跨字段校验强制填写</t>
+          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；本片AFM实测值属于表征结果</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -8522,27 +7768,27 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·标称表面粗糙度</t>
+          <t>▸衬底·来料尺寸规格</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>供应商或批次规格中的标称粗糙度</t>
+          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>粗糙度对象</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>{availability: 有规格数值|供应商未提供；有规格数值时 metric: Ra|RMS, value_nm}</t>
+          <t>长×宽×厚</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
@@ -8552,17 +7798,17 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>{availability: not_provided}</t>
+          <t>10×10×0.5</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>reported时metric与value_nm必填；not_provided时二者禁止填写；历史无availability对象按reported兼容；本片AFM实测值属于表征结果</t>
+          <t>不替代每次实验的本片实际尺寸</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr"/>
@@ -8575,27 +7821,27 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·来料尺寸规格</t>
+          <t>▸衬底·层堆栈</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>供应商标称或该批次来料的原始几何；切割后本次实际单片尺寸属于实验记录</t>
+          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>长×宽×厚</t>
+          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
@@ -8605,17 +7851,17 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>10×10×0.5</t>
+          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>不替代每次实验的本片实际尺寸</t>
+          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -8628,27 +7874,27 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·层堆栈</t>
+          <t>▸衬底·顶表面</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>从体材料到顶表面逐层记录供应商交付的衬底结构</t>
+          <t>实验放样时实际暴露的最上层表面</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>[{material_name,chemical_formula?,thickness_nm?,orientation?,supplier_lot_id?}]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -8658,7 +7904,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>[{"material_name":"Si"},{"material_name":"SiO2","thickness_nm":285}]</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -8668,7 +7914,7 @@
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>按数组顺序生成SubstrateStack；不得用单个字符串拼层</t>
+          <t>与层堆栈配套</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr"/>
@@ -8681,50 +7927,54 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>▸衬底·顶表面</t>
+          <t>▸气瓶·气体组成</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>实验放样时实际暴露的最上层表面</t>
+          <t>气瓶标签或CoA声明的固定组成；单组分100%表示纯气，多组分表示供应商预混气</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[{species: 气体词表|other, other_name?, volume_percent}]</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>未发布</t>
+          <t>vol%</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>条件必填(气瓶)</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>[{"species":"H2","volume_percent":5},{"species":"Ar","volume_percent":95}]</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
+          <t>2026-08-13真实试填反馈</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>与层堆栈配套</t>
-        </is>
-      </c>
-      <c r="K36" s="11" t="inlineStr"/>
+          <t>依标签或CoA登记一次；实验只引用该气瓶版本，不重复填配比</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>{"item_required":["species","volume_percent"],"sum":100,"tolerance":0.01,"unique_by":["species","other_name"]}</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -8734,54 +7984,50 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·气体组成</t>
+          <t>▸气瓶·纯度等级</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>气瓶标签或CoA声明的固定组成；单组分100%表示纯气，多组分表示供应商预混气</t>
+          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>[{species: 气体词表|other, other_name?, volume_percent}]</t>
+          <t>6N/5N/4N/工业级</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>vol%</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>条件必填(气瓶)</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>[{"species":"H2","volume_percent":5},{"species":"Ar","volume_percent":95}]</t>
+          <t>5N</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13真实试填反馈</t>
+          <t>review</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>依标签或CoA登记一次；实验只引用该气瓶版本，不重复填配比</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>{"item_required":["species","volume_percent"],"sum":100,"tolerance":0.01,"unique_by":["species","other_name"]}</t>
-        </is>
-      </c>
+          <t>有供应商等级标签可照录；没有则留空</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -8791,22 +8037,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>▸气瓶·纯度等级</t>
+          <t>▸气瓶·气瓶编号</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>子类(批次类别=气瓶)；与base『纯度』分工</t>
+          <t>钢瓶追溯号</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>6N/5N/4N/工业级</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -8821,7 +8067,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>5N</t>
+          <t>GC-Ar-07</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -8829,78 +8075,74 @@
           <t>review</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>有供应商等级标签可照录；没有则留空</t>
-        </is>
-      </c>
+      <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>MaterialLot</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>▸气瓶·气瓶编号</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>钢瓶追溯号</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>装置Setup</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>装置名称</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>人读名</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>GC-Ar-07</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr"/>
-      <c r="K39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>实体② 装置库 Setup（一台炉登记一次，实验 §2 引用；坐标系随引用冻结）</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>1号双温区管式炉</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -8910,17 +8152,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>装置名称</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>人读名</t>
+          <t>每次修改+1；引用时冻结此版本</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -8933,22 +8175,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>定义项（实体版本外层元数据）</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>1号双温区管式炉</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr"/>
+          <t>★锁版使能(Fable三轮B2)</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>对标 v1 setup_version_snapshot</t>
+        </is>
+      </c>
       <c r="K41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
@@ -8959,22 +8205,22 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>装置来源</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>每次修改+1；引用时冻结此版本</t>
+          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>商业设备/实验室自制/改造设备</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -8982,26 +8228,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>定义项（实体版本外层元数据）</t>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>商业设备</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>★锁版使能(Fable三轮B2)</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr">
-        <is>
-          <t>对标 v1 setup_version_snapshot</t>
-        </is>
-      </c>
+          <t>2026-07-28用户逐项复核</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
@@ -9012,22 +8254,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>装置来源</t>
+          <t>制造商或品牌</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>装置是商业购买、实验室自制还是在既有设备上改造</t>
+          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>商业设备/实验室自制/改造设备</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -9035,14 +8277,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>条件选填(商业设备或改造设备)</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>商业设备</t>
+          <t>合肥科晶</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -9061,12 +8303,12 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>制造商或品牌</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>设备制造商或品牌，独立于型号保存以支持筛选和统计</t>
+          <t>制造商给出的设备型号</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -9091,7 +8333,7 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>合肥科晶</t>
+          <t>OTF-1200X</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
@@ -9110,12 +8352,12 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>设计或建造单位</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>制造商给出的设备型号</t>
+          <t>实验室自制装置的设计或建造单位</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -9135,12 +8377,12 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>条件选填(商业设备或改造设备)</t>
+          <t>条件选填(实验室自制)</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>OTF-1200X</t>
+          <t>二维材料课题组</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -9159,12 +8401,12 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>设计或建造单位</t>
+          <t>内部型号</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置的设计或建造单位</t>
+          <t>实验室自制装置使用的内部型号或版本名称</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -9189,7 +8431,7 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>二维材料课题组</t>
+          <t>CVD-LAB-A</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -9208,12 +8450,12 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>内部型号</t>
+          <t>改造内容</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>实验室自制装置使用的内部型号或版本名称</t>
+          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -9233,12 +8475,12 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>条件选填(实验室自制)</t>
+          <t>条件选填(改造设备)</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>CVD-LAB-A</t>
+          <t>更换三温区加热模块并增加独立控温</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -9257,12 +8499,12 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>改造内容</t>
+          <t>实验室装置编号（资产编号）</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>相对原设备发生变化且会影响实验条件或复现的改造</t>
+          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -9280,22 +8522,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>条件选填(改造设备)</t>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>更换三温区加热模块并增加独立控温</t>
+          <t>CVD-炉1</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr"/>
+          <t>review§4.1B·2026-07-27终版整改</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
+        </is>
+      </c>
       <c r="K48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
@@ -9306,17 +8552,17 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>实验室装置编号（资产编号）</t>
+          <t>温区数</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>课题组用于识别这台装置的唯一业务编号；系统内部身份使用不可变UUID</t>
+          <t>独立控温区数</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -9326,7 +8572,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -9336,20 +8582,20 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>CVD-炉1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>review§4.1B·2026-07-27终版整改</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>要求唯一；仅管理员可通过新版本纠正录入错误，历史版本保留原编号</t>
-        </is>
-      </c>
-      <c r="K49" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>{"ge":1,"type":"integer"}</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -9359,27 +8605,27 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>温区数</t>
+          <t>各温区温度传感器</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>独立控温区数</t>
+          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>温度传感器数组</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -9389,20 +8635,20 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr"/>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>{"ge":1,"type":"integer"}</t>
-        </is>
-      </c>
+          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -9412,27 +8658,27 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>各温区温度传感器</t>
+          <t>炉体方向</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>装置每个温区的传感器类别，以及设备资料明确给出时的标称测温精度</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>温度传感器数组</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>{sensor_type: thermocouple|rtd|infrared_thermometer|fiber_optic_temperature_sensor|thermistor|other, sensor_type_other?, zone_index, nominal_accuracy_C?}</t>
+          <t>水平/垂直</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -9442,19 +8688,15 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>[{sensor_type: 热电偶, zone_index: 1, nominal_accuracy_C: 1}]</t>
+          <t>水平</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查·2026-07-27终版整改·2026-07-28用户复核</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr">
-        <is>
-          <t>温区数决定卡片数量；传感器类别必填；标称测温精度仅在设备资料明确提供时填写，不要求用户估算</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
@@ -9465,22 +8707,22 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>炉体方向</t>
+          <t>炉管材质与截面</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>炉管材料与截面</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>管材质形状对象</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>水平/垂直</t>
+          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -9495,15 +8737,19 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>{material: 石英, shape: 圆形}</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr"/>
+          <t>2026-07-24导师走查</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+        </is>
+      </c>
       <c r="K52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
@@ -9514,47 +8760,47 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>炉管材质与截面</t>
+          <t>炉管尺寸</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>炉管材料与截面</t>
+          <t>按截面形状记录外部尺寸和壁厚</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>管材质形状对象</t>
+          <t>炉管尺寸对象</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英|刚玉|其他, material_other?, shape: 圆形|方形|矩形|其他, shape_other?}</t>
+          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>必填</t>
+          <t>必填；按炉管截面填写</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>{material: 石英, shape: 圆形}</t>
+          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>会议·用户复核2026-07-24</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>材质与截面形状独立保存，禁止把“刚玉；圆”当作一个选项</t>
+          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr"/>
@@ -9567,47 +8813,47 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸</t>
+          <t>反应器类型（热壁/冷壁）</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>按截面形状记录外部尺寸和壁厚</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>炉管尺寸对象</t>
+          <t>下拉</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>{圆形: outer_diameter_mm+wall_thickness_mm; 方形: outer_side_mm+wall_thickness_mm; 矩形: outer_width_mm+outer_height_mm+wall_thickness_mm; 其他: dimension_description}</t>
+          <t>热壁/冷壁</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>必填；按炉管截面填写</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>{outer_width_mm: 50, outer_height_mm: 30, wall_thickness_mm: 2}</t>
+          <t>热壁</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>会议·用户复核2026-07-24</t>
+          <t>复审</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>选择材质与截面后必须按形状完整填写；圆形填外径+壁厚，方形填外边长+壁厚，矩形填外宽+外高+壁厚，其他截面填写具名尺寸说明</t>
+          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
@@ -9620,22 +8866,22 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>反应器类型（热壁/冷壁）</t>
+          <t>坐标系定义</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>下拉</t>
+          <t>固定定义</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>热壁/冷壁</t>
+          <t>上游为负；下游为正；原点固定</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -9643,24 +8889,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>定义项</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>热壁</t>
+          <t>上游(-)←原点→下游(+)</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
+          <t>2026-07-24导师走查</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>放在装置身份、温区与炉管结构之后，避免打断由粗到细的登记顺序</t>
+          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr"/>
@@ -9673,22 +8919,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>坐标系定义</t>
+          <t>装置附加能力</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>系统统一采用上游为负、下游为正的固定坐标定义</t>
+          <t>装置具备的光照、电场、等离子体或其他外场能力</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>固定定义</t>
+          <t>多选</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>上游为负；下游为正；原点固定</t>
+          <t>无/光照/电场/等离子体/其他</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -9696,14 +8942,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="16" t="inlineStr">
-        <is>
-          <t>定义项</t>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>上游(-)←原点→下游(+)</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -9713,7 +8959,7 @@
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>服务端写入固定机器码，管理员和成员均不可编辑</t>
+          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr"/>
@@ -9726,22 +8972,22 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>装置附加能力</t>
+          <t>其他附加能力</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>装置具备的光照、电场、等离子体或其他外场能力</t>
+          <t>装置具备的其他附加能力，每项独立具名；不局限于物理场</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>多选</t>
+          <t>文本数组</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>无/光照/电场/等离子体/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -9749,24 +8995,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>选择其他时必填</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>[磁场, 机械振动]</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>2026-07-24导师走查</t>
+          <t>2026-09-09用户制备字段复核</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>这里只登记能力；每炉实际使用情况在反应条件中记录</t>
+          <t>名称非空且不重复；无与所有能力互斥。生长条件中按名称分别引用并记录时间与参数</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr"/>
@@ -9779,22 +9025,22 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>其他附加能力</t>
+          <t>装置示意图与描述</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>装置具备的其他附加能力，每项独立具名；不局限于物理场</t>
+          <t>装置照片或示意图及文字说明</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>文本数组</t>
+          <t>FileAsset引用+自由</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{file_asset_id, sha256, note}</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
@@ -9802,93 +9048,89 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>选择其他时必填；旧单名称兼容</t>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>[磁场, 机械振动]</t>
+          <t>setup.png</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09用户制备字段复核</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>名称非空且不重复；无与所有能力互斥。生长条件中按名称分别引用并记录时间与参数</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr"/>
     </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>装置Setup</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>装置示意图与描述</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>装置照片或示意图及文字说明</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>FileAsset引用+自由</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>{file_asset_id, sha256, note}</t>
-        </is>
-      </c>
-      <c r="F59" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="H59" s="11" t="inlineStr">
-        <is>
-          <t>setup.png</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="inlineStr"/>
-      <c r="K59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>实体③ 表征仪器 Instrument（实验 §7 表征引用；对标 NeXus NXfabrication 仪器溯源）</t>
         </is>
       </c>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="8" t="n"/>
-      <c r="J60" s="8" t="n"/>
-      <c r="K60" s="8" t="n"/>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>表征仪器</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>仪器编号</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>唯一编号</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>RAMAN-1</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>复审</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -9898,22 +9140,22 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>仪器编号</t>
+          <t>适用表征方法</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>唯一编号</t>
+          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>下拉+其他</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -9928,15 +9170,19 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>RAMAN-1</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>复审</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>API key 为 name_type；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
+        </is>
+      </c>
       <c r="K61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
@@ -9947,22 +9193,22 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>适用表征方法</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>该仪器适用的表征方法，用于结果录入时筛选仪器</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>下拉+其他</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>OM/Raman/PL/SHG/AFM/SEM/TEM/XRD/其他</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -9970,26 +9216,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Horiba</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>API key 保持 name_type 以兼容现有数据；UI 不重复展示，由“支持的表征方法”首项自动派生</t>
-        </is>
-      </c>
+          <t>★NXfabrication</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
@@ -10000,12 +9242,12 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
@@ -10030,7 +9272,7 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Horiba</t>
+          <t>LabRAM HR</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -10049,12 +9291,12 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>序列号</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>型号</t>
+          <t>设备序列号</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -10072,14 +9314,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G64" s="14" t="inlineStr">
-        <is>
-          <t>推荐</t>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>LabRAM HR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -10098,12 +9340,12 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>序列号</t>
+          <t>仪器持久标识</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>设备序列号</t>
+          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -10133,10 +9375,14 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="inlineStr"/>
+          <t>★NXfabrication/PIDINST</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
+        </is>
+      </c>
       <c r="K65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
@@ -10147,12 +9393,12 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>仪器持久标识</t>
+          <t>所在实验室与位置</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>可长期稳定指向该仪器的公开或机构标识，不等同于设备序列号</t>
+          <t>物理位置</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -10177,19 +9423,15 @@
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A305</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>★NXfabrication/PIDINST</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>PID 是 Persistent Identifier 的缩写；没有机构标识时可留空</t>
-        </is>
-      </c>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr"/>
       <c r="K66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
@@ -10200,22 +9442,22 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>所在实验室与位置</t>
+          <t>其他固定配置说明</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>物理位置</t>
+          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>自由</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -10230,15 +9472,19 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>A305</t>
+          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr"/>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+        </is>
+      </c>
       <c r="K67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
@@ -10249,22 +9495,22 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>其他固定配置说明</t>
+          <t>支持的表征方法</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>随仪器长期固定的硬件或能力；本次实际使用参数在表征结果的测试条件中填写</t>
+          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>JSON数组</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>如探测器型号、光栅范围、可用激光与物镜范围</t>
+          <t>[{code,configuration}]；configuration.presets=[{name,conditions}]；code=other 时另有 method_names</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
@@ -10272,24 +9518,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>CCD探测器；300、600、1800 lines·mm⁻¹光栅</t>
+          <t>[{"code":"Raman","configuration":{}}]</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>会议</t>
+          <t>2026-07-28深度审查</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>不在此重复本次实际使用的波长、物镜、功率或积分时间</t>
+          <t>每种方法可维护最多50套命名预设；名称去空白后1–128字符，同方法内忽略大小写唯一。conditions复用该方法结构化采集字段、单位及校验，至少一项，不要求整套测试必填参数齐全。表征主动选用后复制为本次实际条件，可调整；预设修改产生新仪器版本，不改历史记录。其他方法继续通过method_names具名；保留历史configuration内容。</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
@@ -10302,22 +9548,22 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>支持的表征方法</t>
+          <t>最近校准或维护日期</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>选择该仪器支持的表征方法，供结果录入时筛选</t>
+          <t>校准/维护日期</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>JSON数组</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>[{code,configuration}]；configuration.presets=[{name,conditions}]；code=other 时另有 method_names</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -10325,82 +9571,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G69" s="12" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>选填</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>[{"code":"Raman","configuration":{}}]</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr">
-        <is>
-          <t>每种方法可维护最多50套命名预设；名称去空白后1–128字符，同方法内忽略大小写唯一。conditions复用该方法结构化采集字段、单位及校验，至少一项，不要求整套测试必填参数齐全。表征主动选用后复制为本次实际条件，可调整；预设修改产生新仪器版本，不改历史记录。其他方法继续通过method_names具名；保留历史configuration内容。</t>
-        </is>
-      </c>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
       <c r="K69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>表征仪器</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>最近校准或维护日期</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>校准/维护日期</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>选填</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>会议</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr"/>
-      <c r="K70" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A59:K59"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10413,7 +9606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10447,17 +9640,17 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.49</t>
+          <t>v4.0-alpha.50</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>前驱体源容器、装置部件绑定</t>
+          <t>旧格式读取与材料结论</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>删除无录入入口的源容器实例引用与装置可更换部件绑定，以及仪器校准事件快照。</t>
+          <t>删除旧过程步字段组与过程阶段、旧降温速率、前驱体相态/外观/工艺作用、衬底轴向位置、合并晶向抛光、材料结论与样品结论投影、中文写入别名及全部旧载荷读取适配；溶液涂覆只记录每步溶液体积；过程总时长与气氛置换方式必填。</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -10469,17 +9662,17 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.41</t>
+          <t>v4.0-alpha.49</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>制备目标、附加能力与溶液/衬底处理</t>
+          <t>前驱体源容器、装置部件绑定</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>目标按区域独立组成、掺杂、晶相和层数；几何形态与成膜形式分开；附加能力逐项具名并引用到使用参数；溶液用量按处理步骤记录一次，衬底补适用的可选参数。实验字段125、实体字段63；新增20260909_0016仅增形态投影列，旧载荷保留。</t>
+          <t>删除无录入入口的源容器实例引用与装置可更换部件绑定，以及仪器校准事件快照。</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -10491,17 +9684,17 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.40</t>
+          <t>v4.0-alpha.41</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>制备实验记录文案</t>
+          <t>制备目标、附加能力与溶液/衬底处理</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>删除重复提示，统一处理方式、外场和放置名称；明确设定温度与CSV时间原点，区分未选批次和批次未记录，按实际错误提示。仅调整界面文案，保留字段、校验规则和历史数据。</t>
+          <t>目标按区域独立组成、掺杂、晶相和层数；几何形态与成膜形式分开；附加能力逐项具名并引用到使用参数；溶液用量按处理步骤记录一次，衬底补适用的可选参数。实验字段125、实体字段63；新增20260909_0016仅增形态投影列，旧载荷保留。</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
@@ -10513,17 +9706,17 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.39</t>
+          <t>v4.0-alpha.40</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>表征仪器与峰参数</t>
+          <t>制备实验记录文案</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>仪器其他方法支持名称列表；峰状态下拉移除，空白不生成峰结果，仅显式勾选记录未检出，历史数据保留。</t>
+          <t>删除重复提示，统一处理方式、外场和放置名称；明确设定温度与CSV时间原点，区分未选批次和批次未记录，按实际错误提示。仅调整界面文案，保留字段、校验规则和历史数据。</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -10535,17 +9728,17 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.37</t>
+          <t>v4.0-alpha.39</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>界面文案</t>
+          <t>表征仪器与峰参数</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>去掉重复选填标识和功能说明；统一表征仪器、数据处理记录、统计方式与检出限依据文案；保留单位与参照定义，补齐现有条件必填标识，不改变必填规则和历史数据。</t>
+          <t>仪器其他方法支持名称列表；峰状态下拉移除，空白不生成峰结果，仅显式勾选记录未检出，历史数据保留。</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -10557,17 +9750,17 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.34</t>
+          <t>v4.0-alpha.37</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>§5–6 流量名称与异常分类</t>
+          <t>界面文案</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>流量测量方式统一显示浮子流量计（转子流量计）；异常选项按类别排序，人工干预和人工停止并入计划变更，复用采取的处理与处理结果，不增加填写字段；旧记录原类型保留可追溯文字。</t>
+          <t>去掉重复选填标识和功能说明；统一表征仪器、数据处理记录、统计方式与检出限依据文案；保留单位与参照定义，补齐现有条件必填标识，不改变必填规则和历史数据。</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -10579,17 +9772,17 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.31</t>
+          <t>v4.0-alpha.34</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>§3 前驱体</t>
+          <t>§5–6 流量名称与异常分类</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>删除工艺作用及其他工艺作用说明；新保存和常规导出不含推断性作用标签，历史原文保留。</t>
+          <t>流量测量方式统一显示浮子流量计（转子流量计）；异常选项按类别排序，人工干预和人工停止并入计划变更，复用采取的处理与处理结果，不增加填写字段；旧记录原类型保留可追溯文字。</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -10601,17 +9794,17 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.33</t>
+          <t>v4.0-alpha.31</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>§5 气体、压力与降温</t>
+          <t>§3 前驱体</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>气体程序、压力和降温按用户确认修改：浮子流量计保留原始读数与单位；预混气引用商用气瓶组成及总流量；过程总时长明确全程供气边界；减压包含真空并新增加压；程序降温复用温度步骤，分段降温保存有序操作，不将设定速率当实测值</t>
+          <t>删除工艺作用及其他工艺作用说明；新保存和常规导出不含推断性作用标签，历史原文保留。</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -10623,17 +9816,17 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.32</t>
+          <t>v4.0-alpha.33</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>§5 实验前准备</t>
+          <t>§5 气体、压力与降温</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>气路置换改为气氛置换，按连续通气/抽空—回填展开；检漏移出可选操作，不新增检漏状态或确认；精简提示，旧记录保留可追溯语义。</t>
+          <t>气体程序、压力和降温按用户确认修改：浮子流量计保留原始读数与单位；预混气引用商用气瓶组成及总流量；过程总时长明确全程供气边界；减压包含真空并新增加压；程序降温复用温度步骤，分段降温保存有序操作，不将设定速率当实测值</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -10645,29 +9838,29 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>v4.0-alpha.32</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>§1 基本信息</t>
+          <t>§5 实验前准备</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>新增「合成方法」字段（顶层 CVD/PVD 选择器，必填，决定PVD模块是否出现）</t>
+          <t>气路置换改为气氛置换，按连续通气/抽空—回填展开；检漏移出可选操作，不新增检漏状态或确认；精简提示，旧记录保留可追溯语义。</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>新增(我补)</t>
+          <t>用户确认</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -10677,41 +9870,41 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>环境湿度 选填→推荐</t>
+          <t>新增「合成方法」字段（顶层 CVD/PVD 选择器，必填，决定PVD模块是否出现）</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>必填级</t>
+          <t>新增(我补)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>§1b 目标产物</t>
+          <t>§1 基本信息</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>对称性字段落实批注：空间群系→体相空间群，选项简化为空间群号+单层结构说明</t>
+          <t>环境湿度 选填→推荐</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>落实批注</t>
+          <t>必填级</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -10721,7 +9914,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>手性/扭转角/堆垛类型 明确放『备注』</t>
+          <t>对称性字段落实批注：空间群系→体相空间群，选项简化为空间群号+单层结构说明</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -10733,29 +9926,29 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>§2 设备</t>
+          <t>§1b 目标产物</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>坐标系：逐次填『原点+轴向』→ 全局固定、不可编辑的定义项（上游负/下游正）</t>
+          <t>手性/扭转角/堆垛类型 明确放『备注』</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>会议决定</t>
+          <t>落实批注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -10765,73 +9958,73 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>炉管/舟履历：自由文本 → 重置次数 + 重置后使用次数（两个结构化数字）</t>
+          <t>坐标系：逐次填『原点+轴向』→ 全局固定、不可编辑的定义项（上游负/下游正）</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>落实批注</t>
+          <t>会议决定</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>§3 前驱体</t>
+          <t>§2 设备</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>用量 推荐→必填（纳入R0）</t>
+          <t>炉管/舟履历：自由文本 → 重置次数 + 重置后使用次数（两个结构化数字）</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>必填级</t>
+          <t>落实批注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>§5 反应条件</t>
+          <t>§3 前驱体</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>删除『估算衬底真温』行，温度只留 设定温度 + 实测温度</t>
+          <t>用量 推荐→必填（纳入R0）</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>会议决定</t>
+          <t>必填级</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>§6 过程事件</t>
+          <t>§5 反应条件</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>事件类型 与 关联对象 合并为一个细化下拉</t>
+          <t>删除『估算衬底真温』行，温度只留 设定温度 + 实测温度</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -10843,17 +10036,17 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>§7 表征</t>
+          <t>§6 过程事件</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>产物表征拆成独立表、用编号与实验记录关联</t>
+          <t>事件类型 与 关联对象 合并为一个细化下拉</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -10865,56 +10058,56 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
+          <t>§7 表征</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>产物表征拆成独立表、用编号与实验记录关联</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>会议决定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
           <t>回退保留v2</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>§3『舟/坩埚』仍长×宽×高（未拆高）</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>未改</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr"/>
-      <c r="B22" s="11" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>── 2026-07-06 表头定稿修订 ──</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr"/>
-      <c r="D22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>v3.1</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>§1b</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>掺杂/合金/异质结自由文本 → 新增『结构类型』下拉多选（本征/掺杂/合金/垂直·横向异质结）；明细走化学式标准写法</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>定稿修订</t>
-        </is>
-      </c>
+      <c r="C23" s="11" t="inlineStr"/>
+      <c r="D23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -10924,12 +10117,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>§6</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>模块定名『过程事件 Process Events』；『事件类型(含关联对象)』→『事件/部位』</t>
+          <t>掺杂/合金/异质结自由文本 → 新增『结构类型』下拉多选（本征/掺杂/合金/垂直·横向异质结）；明细走化学式标准写法</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -10946,51 +10139,51 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>§6</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>模块定名『过程事件 Process Events』；『事件类型(含关联对象)』→『事件/部位』</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>定稿修订</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>v3.1</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
           <t>§1b</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>目标性能保持轻量自由文本（性能+衡量方法）；严格『数值绑测试方法』落在§7实测侧</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>定稿修订</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr"/>
-      <c r="B26" s="11" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr"/>
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>── 2026-07-06 v3.2 评审回炉（Fable 独立评审）──</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr"/>
-      <c r="D26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>v3.2</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>§7</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>新增『观察到的现象』客观多选词表——录入端仍不判成败，但保留光镜可判的客观负结果（失败炉次最小结构化痕迹）</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>评审回炉</t>
-        </is>
-      </c>
+      <c r="C27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -11000,12 +10193,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>§7</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>化学式升R0；新增『组成明细 components[]』结构化掺杂/异质结，替代字符串承载；结构类型保留为判别器</t>
+          <t>新增『观察到的现象』客观多选词表——录入端仍不判成败，但保留光镜可判的客观负结果（失败炉次最小结构化痕迹）</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -11022,12 +10215,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>§5</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>补回降温段参数（方式/开盖温度/速率），条件必填(降温段)——review头部隐变量勿再漏</t>
+          <t>化学式升R0；新增『组成明细 components[]』结构化掺杂/异质结，替代字符串承载；结构类型保留为判别器</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -11044,12 +10237,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>R0</t>
+          <t>§5</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>按合成方法条件化：前驱体用量→条件必填(固态源)，气态源/PVD不逼填mg</t>
+          <t>补回降温段参数（方式/开盖温度/速率），条件必填(降温段)——review头部隐变量勿再漏</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -11066,51 +10259,51 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
+          <t>R0</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>按合成方法条件化：前驱体用量→条件必填(固态源)，气态源/PVD不逼填mg</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>评审回炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>v3.2</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
           <t>数据模型</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>记录最小单元拍板：炉次=记录单元、样品=关联主键、表征外键指向样品</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>评审回炉</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr"/>
-      <c r="B32" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr"/>
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>── v3.2b 二轮复审再修（Fable 第二轮）──</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr"/>
-      <c r="D32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>v3.2b</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>§3</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>新增前驱体『相态(固/气/液)』字段，为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>复审再修</t>
-        </is>
-      </c>
+      <c r="C33" s="11" t="inlineStr"/>
+      <c r="D33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -11120,12 +10313,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>§3</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>组成明细升为权威+条件必填(结构类型≠本征)、化学式复合体系以其为准；数量拆『浓度(at%)』『层序』；结构类型改必填（复审N2/③）</t>
+          <t>新增前驱体『相态(固/气/液)』字段，为『用量条件必填(固态源)』提供机器判别位（复审N1）</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -11142,12 +10335,12 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>§7/§10</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>加生命周期规则：炉次终态而无任何现象/表征行→『结果缺失』待办，堵『失败炉次零痕迹』（复审①）</t>
+          <t>组成明细升为权威+条件必填(结构类型≠本征)、化学式复合体系以其为准；数量拆『浓度(at%)』『层序』；结构类型改必填（复审N2/③）</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -11164,51 +10357,51 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
+          <t>§7/§10</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>加生命周期规则：炉次终态而无任何现象/表征行→『结果缺失』待办，堵『失败炉次零痕迹』（复审①）</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>复审再修</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>v3.2b</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
           <t>§8/§10</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>PVD 暂不纳入 v2.0 合规判定（占位），R0 不校验 PVD 炉次，待 profile 落地（复审N3）</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>复审再修</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr"/>
-      <c r="B37" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr"/>
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>── v3.3 一等实体补齐（复审⑤/must-fix4-5）──</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr"/>
-      <c r="D37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>v3.3</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>实体表</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>新增『一等实体字段表』sheet：MaterialLot/装置Setup/表征仪器三张权威字段表（补齐半个数据模型）；§10 合规纳入（PVD 仍排除）</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>实体补齐</t>
-        </is>
-      </c>
+      <c r="C38" s="11" t="inlineStr"/>
+      <c r="D38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -11218,12 +10411,12 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>§5/§8.1</t>
+          <t>实体表</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>AP/LP 冗余二选一敲定：保留合成方法 AP/LP，以校验规则强制与反应压力条件一致（不再悬置）</t>
+          <t>新增『一等实体字段表』sheet：MaterialLot/装置Setup/表征仪器三张权威字段表（补齐半个数据模型）；§10 合规纳入（PVD 仍排除）</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -11235,56 +10428,56 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
+          <t>v3.3</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>§5/§8.1</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>AP/LP 冗余二选一敲定：保留合成方法 AP/LP，以校验规则强制与反应压力条件一致（不再悬置）</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>实体补齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
           <t>v3.3b</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>冻结前收尾</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Fable三轮B1-B4：MaterialLot/Setup 加『版本号』(锁版使能)；§2属性=Setup快照【只读投影】声明；用量含液态(非气态条件、µL)；气瓶纯度与base分工注</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>冻结前收尾</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr"/>
-      <c r="B41" s="11" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr"/>
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>── 2026-07-07 导师书面评审回改（v3.4，FSS Re-副本 标黄9处+红字2处）──</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr"/>
-      <c r="D41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>v3.4</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>§1b</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>目标性能：可选项列补示例引导『光学属性-高荧光量子效率 / 电属性-高迁移率』（导师标黄E18）</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>导师评审</t>
-        </is>
-      </c>
+      <c r="C42" s="11" t="inlineStr"/>
+      <c r="D42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -11294,12 +10487,12 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>§3</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>新增『外观描述』字段：使用时性状，溯源判断潮解/变质；推荐(固态源)；放每炉次而非MaterialLot（导师批注K35）</t>
+          <t>目标性能：可选项列补示例引导『光学属性-高荧光量子效率 / 电属性-高迁移率』（导师标黄E18）</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -11316,12 +10509,12 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>§5</t>
+          <t>§3</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>外场参数 选填→条件必填(Setup有外场)；判别位=Setup.外场装置≠无，机器可校验（导师批注K65）</t>
+          <t>新增『外观描述』字段：使用时性状，溯源判断潮解/变质；推荐(固态源)；放每炉次而非MaterialLot（导师批注K35）</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -11338,12 +10531,12 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>§7</t>
+          <t>§5</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>检出相/多型→检出相/多型/堆垛，增记堆垛类型；示例加『AB堆垛』（导师红字B76）</t>
+          <t>外场参数 选填→条件必填(Setup有外场)；判别位=Setup.外场装置≠无，机器可校验（导师批注K65）</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -11365,7 +10558,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>关键谱学指标：PL补峰宽；『SEM占比』改名『SEM覆盖率(视场内材料面积占比,%)』并给定义（导师红字C79/问询K79）</t>
+          <t>检出相/多型→检出相/多型/堆垛，增记堆垛类型；示例加『AB堆垛』（导师红字B76）</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -11382,51 +10575,51 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
+          <t>§7</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>关键谱学指标：PL补峰宽；『SEM占比』改名『SEM覆盖率(视场内材料面积占比,%)』并给定义（导师红字C79/问询K79）</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>导师评审</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>v3.4</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
           <t>全表</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>表头下加必填级别图例行；必填/条件必填字体加粗着色（导师提醒B93）</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>导师评审</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr"/>
-      <c r="B48" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr"/>
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>── review→v3 回退存档（每条给去向）──</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr"/>
-      <c r="D48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>存档</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>湿度</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>回退备案</t>
-        </is>
-      </c>
+      <c r="C49" s="11" t="inlineStr"/>
+      <c r="D49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -11436,12 +10629,12 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>装置加热区长/泵型号/MFC配置/PID</t>
+          <t>湿度</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
+          <t>review建议升必填(有DOI)；v3=推荐(6/24未升)。保留推荐，复议是否升R0</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -11458,12 +10651,12 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>炉管履历</t>
+          <t>装置加热区长/泵型号/MFC配置/PID</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
+          <t>review §4.1B承诺；v3暂缺。留待『装置』实体字段表（下一轮）</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -11480,12 +10673,12 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>时序四元组</t>
+          <t>炉管履历</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
+          <t>review想自动累加；6/24定为手填两数字。保留手填+加重置口径说明（手填有漂移风险）</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -11497,44 +10690,44 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>v3.5a</t>
+          <t>存档</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>时序四元组</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>结构类型由下拉多选纠正为单选判别器；选择值驱动填写提示及组成明细显隐/条件必填</t>
+          <t>review对标NOMAD；v3仅一行导入。落地设计见标准§4时序小节：走FileAsset+通道注册，不进payload</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复</t>
+          <t>回退备案</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>v3.6</t>
+          <t>v3.5a</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>全表/实体</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>科学契约加固：结构类型与组成明细纳入R0；补衬底批次引用、具名几何、其他气体名称、sccm参考状态及字段级数值边界</t>
+          <t>结构类型由下拉多选纠正为单选判别器；选择值驱动填写提示及组成明细显隐/条件必填</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>全库审查修复</t>
+          <t>用户走查修复</t>
         </is>
       </c>
     </row>
@@ -11546,12 +10739,12 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>§6–§7</t>
+          <t>全表/实体</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>过程事件改为带UTC offset的绝对日期时间；实测层数、覆盖率、畴尺寸、成核密度拆为独立量，关键谱学指标改为带单位的结构化数组</t>
+          <t>科学契约加固：结构类型与组成明细纳入R0；补衬底批次引用、具名几何、其他气体名称、sccm参考状态及字段级数值边界</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -11563,22 +10756,22 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>v3.7</t>
+          <t>v3.6</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>§1–§4</t>
+          <t>§6–§7</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>按2026-07-24导师走查：温湿度与预检、目标形态升必填；删除粒子占位；批次引用升必填；前驱体与衬底处理改具名有序数组；衬底晶向、粗糙度、尺寸与倾角结构化</t>
+          <t>过程事件改为带UTC offset的绝对日期时间；实测层数、覆盖率、畴尺寸、成核密度拆为独立量，关键谱学指标改为带单位的结构化数组</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>导师走查整改</t>
+          <t>全库审查修复</t>
         </is>
       </c>
     </row>
@@ -11590,12 +10783,12 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>§5–§6</t>
+          <t>§1–§4</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>11阶段收敛为预处理、反应条件、具名其他记录；温度程序、实测文件、多气体时序、时长、降温、实际外场与事件附件全部改为可校验结构</t>
+          <t>按2026-07-24导师走查：温湿度与预检、目标形态升必填；删除粒子占位；批次引用升必填；前驱体与衬底处理改具名有序数组；衬底晶向、粗糙度、尺寸与倾角结构化</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -11612,12 +10805,12 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>实体</t>
+          <t>§5–§6</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Setup删除sccm参考值、加热区长度、泵、MFC和PID，坐标系固定，新增温度传感器；炉管材质与形状拆入具名对象；MaterialLot新增瓶身或包装标签附件</t>
+          <t>11阶段收敛为预处理、反应条件、具名其他记录；温度程序、实测文件、多气体时序、时长、降温、实际外场与事件附件全部改为可校验结构</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -11629,22 +10822,22 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>v3.8</t>
+          <t>v3.7</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>§1–§5</t>
+          <t>实体</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复：炉管和各舟履历改为每炉手填；炉管尺寸按圆/方/矩形条件展开；前驱体源温改为可选位置温度及依据；外场按等离子体/光/电展开明确参数</t>
+          <t>Setup删除sccm参考值、加热区长度、泵、MFC和PID，坐标系固定，新增温度传感器；炉管材质与形状拆入具名对象；MaterialLot新增瓶身或包装标签附件</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>用户走查修复</t>
+          <t>导师走查整改</t>
         </is>
       </c>
     </row>
@@ -11656,12 +10849,12 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>§4/实体</t>
+          <t>§1–§5</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>衬底稳定规格归MaterialLot：晶向抛光、偏切角与方向、氧化层及标称粗糙度由批次冻结带出；本片尺寸、放置、预处理和位置留在炉次；气瓶等级改为供应商原始标签选填</t>
+          <t>用户走查修复：炉管和各舟履历改为每炉手填；炉管尺寸按圆/方/矩形条件展开；前驱体源温改为可选位置温度及依据；外场按等离子体/光/电展开明确参数</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -11678,12 +10871,12 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>术语/表征</t>
+          <t>§4/实体</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>装置与实际外场统一显示“等离子体”；体相空间群改用内置230项检索；“表征方法”与仪器引用分开，固定配置只记录稳定硬件能力</t>
+          <t>衬底稳定规格归MaterialLot：晶向抛光、偏切角与方向、氧化层及标称粗糙度由批次冻结带出；本片尺寸、放置、预处理和位置留在炉次；气瓶等级改为供应商原始标签选填</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -11695,127 +10888,127 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>v3.9</t>
+          <t>v3.8</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>§1/§4/实体</t>
+          <t>术语/表征</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>按会议逐字稿删除悬浮粒子浓度；粗糙度允许明确记录供应商未提供；旧批次缺稳定字段时禁止在实验回填；区分来料尺寸与本次实际切片尺寸</t>
+          <t>装置与实际外场统一显示“等离子体”；体相空间群改用内置230项检索；“表征方法”与仪器引用分开，固定配置只记录稳定硬件能力</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25用户复核</t>
+          <t>用户走查修复</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>v3.10</t>
+          <t>v3.9</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>§3/§4/实体</t>
+          <t>§1/§4/实体</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>补齐温区距离参照、条件不适用后端约束与旧等离子别名；粒径/形态按物料类别展开；晶向抛光和偏切以有规格、未提供、不适用三态记录，禁止用伪值或0代替未知</t>
+          <t>按会议逐字稿删除悬浮粒子浓度；粗糙度允许明确记录供应商未提供；旧批次缺稳定字段时禁止在实验回填；区分来料尺寸与本次实际切片尺寸</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25终审收口</t>
+          <t>2026-07-25用户复核</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>v3.11</t>
+          <t>v3.10</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>§6/实体</t>
+          <t>§3/§4/实体</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>事件具体说明始终可选填写、终止原因=其他时升级为必填；仪器字段改称“适用表征方法”；补明热电偶距离与前驱体温区、炉管截面与尺寸的联动必填规则</t>
+          <t>补齐温区距离参照、条件不适用后端约束与旧等离子别名；粒径/形态按物料类别展开；晶向抛光和偏切以有规格、未提供、不适用三态记录，禁止用伪值或0代替未知</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>2026-07-25逐字稿与语义终审</t>
+          <t>2026-07-25终审收口</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>v3.12</t>
+          <t>v3.11</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>§1–§5/实体</t>
+          <t>§6/实体</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>制备终版整改：新记录固定CVD顶层方法；目标产物按掺杂、合金、材料层和区域填写；Setup逐温区只填传感器类型与温度测量误差；前驱体角色与样片标记必填；压力类别和值成对；反应删除伪循环派生</t>
+          <t>事件具体说明始终可选填写、终止原因=其他时升级为必填；仪器字段改称“适用表征方法”；补明热电偶距离与前驱体温区、炉管截面与尺寸的联动必填规则</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>2026-07-27终版整改</t>
+          <t>2026-07-25逐字稿与语义终审</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>v3.13</t>
+          <t>v3.12</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>§1b</t>
+          <t>§1–§5/实体</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>目标产物复核：化学式示例按结构类型变化；删除“普通数字”用户文案；掺杂区只显示掺杂元素；空间群按化学式给出经核对的常见体相候选并保留230项搜索；异质结构逐层或逐区域填写空间群</t>
+          <t>制备终版整改：新记录固定CVD顶层方法；目标产物按掺杂、合金、材料层和区域填写；Setup逐温区只填传感器类型与温度测量误差；前驱体角色与样片标记必填；压力类别和值成对；反应删除伪循环派生</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28用户逐项复核</t>
+          <t>2026-07-27终版整改</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>v3.15</t>
+          <t>v3.13</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>实体/设备</t>
+          <t>§1b</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>温度传感器由热电偶分型号改为按测温原理选择类别：热电偶、热电阻（RTD）、红外测温仪、光纤温度传感器、热敏电阻、其他</t>
+          <t>目标产物复核：化学式示例按结构类型变化；删除“普通数字”用户文案；掺杂区只显示掺杂元素；空间群按化学式给出经核对的常见体相候选并保留230项搜索；异质结构逐层或逐区域填写空间群</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -11827,7 +11020,7 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>v3.16</t>
+          <t>v3.15</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -11837,7 +11030,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Setup拆分制造商或品牌与型号，增加装置来源；实验室装置编号保持唯一但允许管理员通过新版本纠错；温区标称测温精度改为选填</t>
+          <t>温度传感器由热电偶分型号改为按测温原理选择类别：热电偶、热电阻（RTD）、红外测温仪、光纤温度传感器、热敏电阻、其他</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -11849,7 +11042,7 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>v3.17</t>
+          <t>v3.16</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -11859,7 +11052,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>装置来源改为必填；商业设备显示制造商与型号，实验室自制显示设计或建造单位与内部型号，改造设备显示原设备制造商、原设备型号与改造内容；公共技术字段不变</t>
+          <t>Setup拆分制造商或品牌与型号，增加装置来源；实验室装置编号保持唯一但允许管理员通过新版本纠错；温区标称测温精度改为选填</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -11871,105 +11064,105 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>v3.18</t>
+          <t>v3.17</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>§3/实体</t>
+          <t>实体/设备</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>前驱体先选本次使用形态再筛选批次；删除炉次中重复的名称化学式和CAS；用途、使用量、使用前状态、处理步骤按实际语义收敛；非气态按舟、坩埚、衬底表面或其他容器展开容器尺寸、履历与炉内位置</t>
+          <t>装置来源改为必填；商业设备显示制造商与型号，实验室自制显示设计或建造单位与内部型号，改造设备显示原设备制造商、原设备型号与改造内容；公共技术字段不变</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28前驱体首版复核</t>
+          <t>2026-07-28用户逐项复核</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>v4.0-rc.1</t>
+          <t>v3.18</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>科学对象/实体/结果</t>
+          <t>§3/实体</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>引入正交TargetSpec、物理SourceLoad、统一ProcessTimeline、不可变RunRevision、样品转换图及MeasurementRun→AnalysisRun→PropertyValue/MaterialAssertion溯源链；物料、装置部件和仪器能力补齐归一化字段；PVD不进入发布契约</t>
+          <t>前驱体先选本次使用形态再筛选批次；删除炉次中重复的名称化学式和CAS；用途、使用量、使用前状态、处理步骤按实际语义收敛；非气态按舟、坩埚、衬底表面或其他容器展开容器尺寸、履历与炉内位置</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>2026-07-28深度审查整改</t>
+          <t>2026-07-28前驱体首版复核</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.2</t>
+          <t>v4.0-rc.1</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>科学完整性复核</t>
+          <t>科学对象/实体/结果</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>关闭旧结果写入与手工派生入口；收紧审阅和转化权限；修正跨炉次转化溯源、过程单位归一化、不可变修订导出及数据集查询语义；冻结装料容器、测量时校准和样品—修订关联快照；状态降为内部验证</t>
+          <t>引入正交TargetSpec、物理SourceLoad、统一ProcessTimeline、不可变RunRevision、样品转换图及MeasurementRun→AnalysisRun→PropertyValue/MaterialAssertion溯源链；物料、装置部件和仪器能力补齐归一化字段；PVD不进入发布契约</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>2026-07-29二次复核整改</t>
+          <t>2026-07-28深度审查整改</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.3</t>
+          <t>v4.0-alpha.2</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>§4 衬底</t>
+          <t>科学完整性复核</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>产品简化界面增加本片轴向位置与备注；轴向位置为普通用户提交前必填，不暴露三维坐标</t>
+          <t>关闭旧结果写入与手工派生入口；收紧审阅和转化权限；修正跨炉次转化溯源、过程单位归一化、不可变修订导出及数据集查询语义；冻结装料容器、测量时校准和样品—修订关联快照；状态降为内部验证</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>2026-07-30产品简化</t>
+          <t>2026-07-29二次复核整改</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.4</t>
+          <t>v4.0-alpha.3</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>§7 表征</t>
+          <t>§4 衬底</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>表征方法拆分最小必填与更多测量参数，固定各方法常用结果项，并增加“其他”方法说明；科学对象仍由后端统一落库</t>
+          <t>产品简化界面增加本片轴向位置与备注；轴向位置为普通用户提交前必填，不暴露三维坐标</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
@@ -11981,29 +11174,29 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.5</t>
+          <t>v4.0-alpha.4</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>实体/物料批次</t>
+          <t>§7 表征</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>CAS号与数值纯度改为有来源才选填；删除同义名、标识符、商业规格JSON、纯度基准/来源及D50四字段；供应商规格或等级按标签原文照录</t>
+          <t>表征方法拆分最小必填与更多测量参数，固定各方法常用结果项，并增加“其他”方法说明；科学对象仍由后端统一落库</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02供应商资料复核与减负</t>
+          <t>2026-07-30产品简化</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.6</t>
+          <t>v4.0-alpha.5</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -12013,19 +11206,19 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>物料表单文案正式化：常规字段说明改为简短占位示例，仅为纯度及衬底规格等易误录字段保留必要说明；统一字段名称、中文标点和中英文术语</t>
+          <t>CAS号与数值纯度改为有来源才选填；删除同义名、标识符、商业规格JSON、纯度基准/来源及D50四字段；供应商规格或等级按标签原文照录</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>2026-08-02用户界面复核</t>
+          <t>2026-08-02供应商资料复核与减负</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.7</t>
+          <t>v4.0-alpha.6</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -12035,19 +11228,19 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>化学式复用目标产物输入控件并提示元素与语法；货号与批号直接对应包装上的 Cat./Product No. 和 Lot/Batch No.，说明两者的产品与实物批次分工</t>
+          <t>物料表单文案正式化：常规字段说明改为简短占位示例，仅为纯度及衬底规格等易误录字段保留必要说明；统一字段名称、中文标点和中英文术语</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06用户界面复核</t>
+          <t>2026-08-02用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.8</t>
+          <t>v4.0-alpha.7</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -12057,7 +11250,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>删除化学式格式说明，只保留示例与即时元素/语法反馈</t>
+          <t>化学式复用目标产物输入控件并提示元素与语法；货号与批号直接对应包装上的 Cat./Product No. 和 Lot/Batch No.，说明两者的产品与实物批次分工</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -12069,7 +11262,7 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.9</t>
+          <t>v4.0-alpha.8</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -12079,7 +11272,7 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>供应商“其他”改为明确的新增供应商与名称输入；供应商规格或等级改为产品等级（标签原文），说明资料未标注时留空</t>
+          <t>删除化学式格式说明，只保留示例与即时元素/语法反馈</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
@@ -12091,17 +11284,17 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.12</t>
+          <t>v4.0-alpha.9</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>§5 生长条件</t>
+          <t>实体/物料批次</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>统一实验时间零点与有效生长窗口；补齐气体批次、流量来源、绝对压力、受控降温速率、实际外场参数和多条异常事件，并自动覆盖生长后的实验过程</t>
+          <t>供应商“其他”改为明确的新增供应商与名称输入；供应商规格或等级改为产品等级（标签原文），说明资料未标注时留空</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -12113,7 +11306,7 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.13</t>
+          <t>v4.0-alpha.12</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
@@ -12123,19 +11316,19 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>将容易误解为管理制度的“压力制度/压力体系”统一改为“反应压力条件”，数据字段与校验规则不变</t>
+          <t>统一实验时间零点与有效生长窗口；补齐气体批次、流量来源、绝对压力、受控降温速率、实际外场参数和多条异常事件，并自动覆盖生长后的实验过程</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户界面复核</t>
+          <t>2026-08-06用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.14</t>
+          <t>v4.0-alpha.13</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
@@ -12145,7 +11338,7 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>改为按实际操作和持续时间录入，系统自动生成系统准备、升温与预处理、反应、反应后处理和降温时间轴；气体优先选择使用阶段，仅自定义时填写起止时间</t>
+          <t>将容易误解为管理制度的“压力制度/压力体系”统一改为“反应压力条件”，数据字段与校验规则不变</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -12157,7 +11350,7 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.15</t>
+          <t>v4.0-alpha.14</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
@@ -12167,51 +11360,51 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>删除缺乏统一文献定义且无法直接观测的反应计时起点、反应开始前用时、反应时长及重复的反应后处理；实际过程由温度步骤、气体时段、系统准备、压力与降温记录</t>
+          <t>改为按实际操作和持续时间录入，系统自动生成系统准备、升温与预处理、反应、反应后处理和降温时间轴；气体优先选择使用阶段，仅自定义时填写起止时间</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-07用户界面复核与原始论文核对</t>
+          <t>2026-08-07用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.16</t>
+          <t>v4.0-alpha.15</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>§3 前驱体装载</t>
+          <t>§5 生长条件</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>删除偏TMDC的必填单选作用，改为选填多选工艺作用；一次旋涂支持多段转速；衬底表面装载关联稳定衬底片；旋涂物料可成对记录溶液浓度与受控单位</t>
+          <t>删除缺乏统一文献定义且无法直接观测的反应计时起点、反应开始前用时、反应时长及重复的反应后处理；实际过程由温度步骤、气体时段、系统准备、压力与降温记录</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>2026-08-12师兄真实试填反馈</t>
+          <t>2026-08-07用户界面复核与原始论文核对</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.17</t>
+          <t>v4.0-alpha.16</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>§5 生长条件</t>
+          <t>§3 前驱体装载</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>气体词表增加二氧化碳，启动混合气与置换气源契约收口</t>
+          <t>删除偏TMDC的必填单选作用，改为选填多选工艺作用；一次旋涂支持多段转速；衬底表面装载关联稳定衬底片；旋涂物料可成对记录溶液浓度与受控单位</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
@@ -12223,240 +11416,262 @@
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.18</t>
+          <t>v4.0-alpha.17</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>§1–§6科学修订契约·MaterialLot气瓶</t>
+          <t>§5 生长条件</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>气瓶版本结构化登记纯气或预混组成；置换引用实际气瓶版本；基本信息、目标材料、前驱体、过程事件与生长条件的发布字段改用当前不可变修订payload真实key和schema_path，旧扁平字段仅历史兼容</t>
+          <t>气体词表增加二氧化碳，启动混合气与置换气源契约收口</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>2026-08-13全链路契约复核</t>
+          <t>2026-08-12师兄真实试填反馈</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.19</t>
+          <t>v4.0-alpha.18</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>表征科学属性</t>
+          <t>§1–§6科学修订契约·MaterialLot气瓶</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>PropertyValue 补齐数值/文本表示类型与物理范围，并统一后端和前端的单一源校验</t>
+          <t>气瓶版本结构化登记纯气或预混组成；置换引用实际气瓶版本；基本信息、目标材料、前驱体、过程事件与生长条件的发布字段改用当前不可变修订payload真实key和schema_path，旧扁平字段仅历史兼容</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31表征全链路独立审查</t>
+          <t>2026-08-13全链路契约复核</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.20</t>
+          <t>v4.0-alpha.19</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>实体/物料批次</t>
+          <t>表征科学属性</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>云母衬底增加白云母、金云母和氟金云母类型选择，并由系统生成理想化学式，避免选择材料后在表单顶部突然出现手填化学式</t>
+          <t>PropertyValue 补齐数值/文本表示类型与物理范围，并统一后端和前端的单一源校验</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01用户试填反馈</t>
+          <t>2026-08-31表征全链路独立审查</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.21</t>
+          <t>v4.0-alpha.20</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>实体/制备/样品与表征流程</t>
+          <t>实体/物料批次</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>仪器能力改为勾选、日期改为日期控件、装置使用身份标签、异常改为显式确认、表征入口保留样品上下文，并在编辑后清除旧校验错误</t>
+          <t>云母衬底增加白云母、金云母和氟金云母类型选择，并由系统生成理想化学式，避免选择材料后在表单顶部突然出现手填化学式</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01全表单交互复核</t>
+          <t>2026-09-01用户试填反馈</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.22</t>
+          <t>v4.0-alpha.21</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>§3/§5 生长条件与装置履历</t>
+          <t>实体/制备/样品与表征流程</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>生长条件按实验前准备、温度、气体、反应压力、降温和异常分区；温度步骤移除待判断与初始温度伪时长；异常改为勾选框，并缩短温区和炉管履历文案</t>
+          <t>仪器能力改为勾选、日期改为日期控件、装置使用身份标签、异常改为显式确认、表征入口保留样品上下文，并在编辑后清除旧校验错误</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户界面复核</t>
+          <t>2026-09-01全表单交互复核</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.23</t>
+          <t>v4.0-alpha.22</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>§1b/§3/§4/§5 制备记录填写体验</t>
+          <t>§3/§5 生长条件与装置履历</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>缩短晶体结构、实验目标、相对测温点位置、使用前处理、衬底处理和压力条件文案；明确必填空状态与提交检查，并减少气体首段录入步骤</t>
+          <t>生长条件按实验前准备、温度、气体、反应压力、降温和异常分区；温度步骤移除待判断与初始温度伪时长；异常改为勾选框，并缩短温区和炉管履历文案</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户全流程复核</t>
+          <t>2026-09-02用户界面复核</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.24</t>
+          <t>v4.0-alpha.23</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>§5 实验前准备</t>
+          <t>§1b/§3/§4/§5 制备记录填写体验</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>抽真空优先记录终点绝对压力；有压力读数时持续时间改为选填，无压力读数时持续时间必填</t>
+          <t>缩短晶体结构、实验目标、相对测温点位置、使用前处理、衬底处理和压力条件文案；明确必填空状态与提交检查，并减少气体首段录入步骤</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02用户实验前准备复核</t>
+          <t>2026-09-02用户全流程复核</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.26</t>
+          <t>v4.0-alpha.24</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>§1b 目标材料</t>
+          <t>§5 实验前准备</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>单一材料改为本征材料，原子层数改为材料层数；删除无法预知的目标覆盖状态和语义混淆的目标生长取向，以目标产物形态和条件平面轮廓表达预期形态</t>
+          <t>抽真空优先记录终点绝对压力；有压力读数时持续时间改为选填，无压力读数时持续时间必填</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户目标材料复核</t>
+          <t>2026-09-02用户实验前准备复核</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.27</t>
+          <t>v4.0-alpha.26</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>装置与衬底</t>
+          <t>§1b 目标材料</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>外场能力增加具名其他；衬底批号改为按标签提供情况条件填写并补生产日期；衬底处理合并为可展开溶剂清洗，并以紫外/臭氧处理替代笼统亲水处理</t>
+          <t>单一材料改为本征材料，原子层数改为材料层数；删除无法预知的目标覆盖状态和语义混淆的目标生长取向，以目标产物形态和条件平面轮廓表达预期形态</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03用户装置与衬底复核</t>
+          <t>2026-09-03用户目标材料复核</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>v4.0-alpha.35</t>
+          <t>v4.0-alpha.27</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>表征客观测量</t>
+          <t>装置与衬底</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>新表征不分区域、不录入材料判定；谱峰按编号记录峰位、半高全宽和强度，区分未分析与未检出；AFM、电子显微镜、元素定量按方法与模式显示，历史判定不再自动汇总成整片样品结论</t>
+          <t>外场能力增加具名其他；衬底批号改为按标签提供情况条件填写并补生产日期；衬底处理合并为可展开溶剂清洗，并以紫外/臭氧处理替代笼统亲水处理</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04用户表征复核</t>
+          <t>2026-09-03用户装置与衬底复核</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
+          <t>v4.0-alpha.35</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>表征客观测量</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>新表征不分区域、不录入材料判定；谱峰按编号记录峰位、半高全宽和强度，区分未分析与未检出；AFM、电子显微镜、元素定量按方法与模式显示，历史判定不再自动汇总成整片样品结论</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-04用户表征复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>最小可复现核心(27项，含条件必填)</t>
         </is>
       </c>
-      <c r="C96" s="11" t="inlineStr">
+      <c r="C97" s="11" t="inlineStr">
         <is>
           <t>过程R0以温度/气体/压力通道和降温条件为准；不再要求人工划分反应阶段或反应时长</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>必填集</t>
         </is>
